--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2527,7 +2527,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发1次</t>
+          <t>累计未发1次，迟发2次</t>
         </is>
       </c>
     </row>
@@ -3927,6 +3927,11 @@
           <t>是</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
     </row>
     <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="58" t="inlineStr">
@@ -3942,6 +3947,11 @@
       <c r="C56" s="60" t="inlineStr">
         <is>
           <t>是</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
         </is>
       </c>
     </row>
@@ -4064,6 +4074,46 @@
     <row r="157"/>
     <row r="158"/>
     <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2527,7 +2527,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3313,7 +3313,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D26" s="33" t="n"/>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
     </row>
     <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
@@ -3355,7 +3359,7 @@
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发2次</t>
+          <t>累计未发1次，迟发3次</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3785,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D48" s="36" t="n"/>
+      <c r="D48" s="36" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
     </row>
     <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
@@ -3927,7 +3935,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>累计未发1次</t>
         </is>
@@ -3949,7 +3957,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>累计未发1次</t>
         </is>
@@ -4114,6 +4122,26 @@
     <row r="197"/>
     <row r="198"/>
     <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2527,7 +2527,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3918,6 +3918,11 @@
           <t>是</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
     </row>
     <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="58" t="inlineStr">
@@ -3980,168 +3985,6 @@
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发4次</t>
+          <t>累计未发2次，迟发5次</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>累计未发1次</t>
         </is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D52" s="73" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E52" s="72" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46123</v>
+        <v>46126</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="D24" s="74" t="inlineStr">
         <is>
-          <t>累计迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E24" s="72" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2612,7 +2612,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="D49" s="74" t="inlineStr">
         <is>
-          <t>累计迟发1次</t>
+          <t>累计迟发2次</t>
         </is>
       </c>
       <c r="E49" s="72" t="n"/>
@@ -4400,7 +4400,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D54" s="71" t="n"/>
+      <c r="D54" s="71" t="inlineStr">
+        <is>
+          <t>累计迟发1次</t>
+        </is>
+      </c>
       <c r="E54" s="72" t="n"/>
       <c r="F54" s="79" t="inlineStr">
         <is>
@@ -4509,6 +4513,207 @@
       </c>
       <c r="G58" s="70" t="n"/>
     </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
   </sheetData>
   <autoFilter ref="A2:F58"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2995,7 +2995,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="68" t="n"/>
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E8" s="69" t="n"/>
       <c r="F8" s="63" t="inlineStr">
         <is>
@@ -3083,7 +3087,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D10" s="70" t="n"/>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E10" s="69" t="n"/>
       <c r="F10" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D7" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发3次</t>
+          <t>累计未发2次，迟发3次</t>
         </is>
       </c>
       <c r="E7" s="69" t="n"/>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D42" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E42" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2615,7 +2615,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O259"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D15" s="70" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发1次</t>
+          <t>累计未发2次，迟发2次</t>
         </is>
       </c>
       <c r="E15" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2615,7 +2615,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2612,7 +2612,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O299"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="D46" s="71" t="inlineStr">
         <is>
-          <t>累计迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E46" s="69" t="n"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D47" s="71" t="inlineStr">
         <is>
-          <t>累计迟发2次</t>
+          <t>累计未发1次，迟发2次</t>
         </is>
       </c>
       <c r="E47" s="69" t="n"/>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D48" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E48" s="69" t="n"/>
@@ -4768,6 +4768,46 @@
     <row customHeight="1" ht="16" r="257" s="53"/>
     <row customHeight="1" ht="16" r="258" s="53"/>
     <row customHeight="1" ht="16" r="259" s="53"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
   </sheetData>
   <autoFilter ref="A2:F58"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2612,7 +2612,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O299"/>
+  <dimension ref="A1:O319"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D33" s="73" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发1次</t>
+          <t>累计未发2次，迟发2次</t>
         </is>
       </c>
       <c r="E33" s="69" t="n"/>
@@ -4097,7 +4097,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D43" s="71" t="n"/>
+      <c r="D43" s="71" t="inlineStr">
+        <is>
+          <t>累计迟发1次</t>
+        </is>
+      </c>
       <c r="E43" s="69" t="n"/>
       <c r="F43" s="63" t="inlineStr">
         <is>
@@ -4808,6 +4812,26 @@
     <row r="297"/>
     <row r="298"/>
     <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
   </sheetData>
   <autoFilter ref="A2:F58"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2612,7 +2612,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O319"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
     <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D33" s="73" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发2次</t>
+          <t>累计未发2次，迟发3次</t>
         </is>
       </c>
       <c r="E33" s="69" t="n"/>
@@ -4772,66 +4772,6 @@
     <row customHeight="1" ht="16" r="257" s="53"/>
     <row customHeight="1" ht="16" r="258" s="53"/>
     <row customHeight="1" ht="16" r="259" s="53"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
   </sheetData>
   <autoFilter ref="A2:F58"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46142</v>
+        <v>46144</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发4次</t>
+          <t>累计未发5次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D27" s="68" t="inlineStr">
         <is>
-          <t>累计未发5次，迟发1次</t>
+          <t>累计未发6次，迟发1次</t>
         </is>
       </c>
       <c r="E27" s="69" t="n"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D32" s="71" t="inlineStr">
         <is>
-          <t>累计未发3次，迟发2次</t>
+          <t>累计未发4次，迟发2次</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D42" s="71" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E42" s="69" t="n"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D50" s="70" t="inlineStr">
         <is>
-          <t>累计迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E50" s="69" t="n"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D51" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E51" s="69" t="n"/>
@@ -4441,7 +4441,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D55" s="68" t="n"/>
+      <c r="D55" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E55" s="69" t="n"/>
       <c r="F55" s="63" t="inlineStr">
         <is>
@@ -4491,7 +4495,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D57" s="68" t="n"/>
+      <c r="D57" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E57" s="69" t="n"/>
       <c r="F57" s="63" t="inlineStr">
         <is>
@@ -4541,7 +4549,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D59" s="68" t="n"/>
+      <c r="D59" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E59" s="69" t="n"/>
       <c r="F59" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D48" s="71" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E48" s="69" t="n"/>
@@ -4470,7 +4470,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D56" s="68" t="n"/>
+      <c r="D56" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E56" s="69" t="n"/>
       <c r="F56" s="63" t="inlineStr">
         <is>
@@ -4497,7 +4501,7 @@
       </c>
       <c r="D57" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E57" s="69" t="n"/>
@@ -4524,7 +4528,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D58" s="68" t="n"/>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E58" s="69" t="n"/>
       <c r="F58" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D32" s="71" t="inlineStr">
         <is>
-          <t>累计未发4次，迟发2次</t>
+          <t>累计未发4次，迟发3次</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D36" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发2次</t>
+          <t>累计未发1次，迟发3次</t>
         </is>
       </c>
       <c r="E36" s="69" t="n"/>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="D45" s="71" t="inlineStr">
         <is>
-          <t>累计迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E45" s="69" t="n"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="D55" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E55" s="69" t="n"/>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D57" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发2次，迟发1次</t>
         </is>
       </c>
       <c r="E57" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="D15" s="70" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发2次</t>
+          <t>累计未发3次，迟发2次</t>
         </is>
       </c>
       <c r="E15" s="69" t="n"/>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D27" s="68" t="inlineStr">
         <is>
-          <t>累计未发6次，迟发1次</t>
+          <t>累计未发7次，迟发1次</t>
         </is>
       </c>
       <c r="E27" s="69" t="n"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D32" s="71" t="inlineStr">
         <is>
-          <t>累计未发4次，迟发3次</t>
+          <t>累计未发5次，迟发3次</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D58" s="68" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>迟发2次</t>
         </is>
       </c>
       <c r="E58" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D21" s="70" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发2次</t>
+          <t>累计未发3次，迟发2次</t>
         </is>
       </c>
       <c r="E21" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46148</v>
+        <v>46152</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D13" s="70" t="inlineStr">
         <is>
-          <t>累计未发4次</t>
+          <t>累计未发4次，迟发1次</t>
         </is>
       </c>
       <c r="E13" s="70" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D48" s="71" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E48" s="69" t="n"/>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D58" s="68" t="inlineStr">
         <is>
-          <t>迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E58" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D24" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发1次</t>
+          <t>累计未发2次，迟发1次</t>
         </is>
       </c>
       <c r="E24" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D27" s="68" t="inlineStr">
         <is>
-          <t>累计未发7次，迟发1次</t>
+          <t>累计未发8次，迟发1次</t>
         </is>
       </c>
       <c r="E27" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3172,7 +3172,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D12" s="73" t="n"/>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E12" s="69" t="n"/>
       <c r="F12" s="63" t="inlineStr">
         <is>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E18" s="69" t="n"/>
@@ -4070,7 +4074,7 @@
       </c>
       <c r="D42" s="71" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E42" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E18" s="69" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D55" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E55" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D23" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E23" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46161</v>
+        <v>46164</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D55" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发3次，迟发1次</t>
         </is>
       </c>
       <c r="E55" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D31" s="71" t="inlineStr">
         <is>
-          <t>累计未发3次，迟发3次</t>
+          <t>累计未发4次，迟发3次</t>
         </is>
       </c>
       <c r="E31" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D32" s="71" t="inlineStr">
         <is>
-          <t>累计未发5次，迟发3次</t>
+          <t>累计未发6次，迟发3次</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D26" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E26" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E18" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D30" s="71" t="inlineStr">
         <is>
-          <t>累计迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E30" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3587,7 +3587,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D25" s="71" t="n"/>
+      <c r="D25" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E25" s="69" t="n"/>
       <c r="F25" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发5次</t>
+          <t>累计未发6次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D5" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E5" s="69" t="n"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>累计未发4次</t>
+          <t>累计未发5次</t>
         </is>
       </c>
       <c r="E18" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D13" s="70" t="inlineStr">
         <is>
-          <t>累计未发4次，迟发1次</t>
+          <t>累计未发4次，迟发2次</t>
         </is>
       </c>
       <c r="E13" s="70" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linxiaozhong/Downloads/日报及月报/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7DFF96-BC15-A94D-ABE3-EC0FBCB8AE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D4FEA7-8D5E-DB4C-88BD-E450562545CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="210">
   <si>
     <t>区域</t>
   </si>
@@ -421,15 +421,9 @@
     <t>粤东区</t>
   </si>
   <si>
-    <t>粤东</t>
-  </si>
-  <si>
     <t>粤</t>
   </si>
   <si>
-    <t>粤西</t>
-  </si>
-  <si>
     <t>华东分公司</t>
   </si>
   <si>
@@ -659,6 +653,30 @@
   </si>
   <si>
     <t>累计未发1次；(换主任前)累计未发2次，累计迟发5次</t>
+  </si>
+  <si>
+    <t>华东分公司</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>苏州吴江中心</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>粤西区</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛山顺德中心</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>粤东区</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1075,7 +1093,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1311,6 +1329,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2657,7 +2682,7 @@
   <sheetPr codeName="2026年日报">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O259"/>
+  <dimension ref="A1:O261"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.1640625" style="53" customWidth="1"/>
@@ -2698,14 +2723,14 @@
         <v>5</v>
       </c>
       <c r="H2" s="24">
-        <f>SUM(H3:H104)</f>
+        <f>SUM(H3:H106)</f>
         <v>58</v>
       </c>
       <c r="J2" s="64" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="62">
-        <f>SUM(K3:K104)</f>
+        <f>SUM(K3:K106)</f>
         <v>58</v>
       </c>
     </row>
@@ -2728,29 +2753,29 @@
         <v>7</v>
       </c>
       <c r="H3" s="23">
-        <f t="shared" ref="H3:H15" si="0">COUNTIF($A:$A,$G3)</f>
+        <f>COUNTIF($A:$A,$G3)</f>
         <v>7</v>
       </c>
       <c r="J3" s="61" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="62">
-        <f t="shared" ref="K3:K12" si="1">COUNTIFS($A:$A,$G3,$C:$C,"&lt;&gt;新中心")</f>
+        <f>COUNTIFS($A:$A,$G3,$C:$C,"&lt;&gt;新中心")</f>
         <v>7</v>
       </c>
       <c r="L3" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="35">
+        <f>COUNTIF(F:F,L3)</f>
+        <v>11</v>
+      </c>
+      <c r="N3" t="s">
         <v>126</v>
-      </c>
-      <c r="M3" s="35">
-        <f>K3+K4</f>
-        <v>11</v>
-      </c>
-      <c r="N3" t="s">
-        <v>127</v>
       </c>
       <c r="O3">
         <f>M3+M4</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="16.5" customHeight="1">
@@ -2772,29 +2797,29 @@
         <v>16</v>
       </c>
       <c r="H4" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G4)</f>
         <v>4</v>
       </c>
       <c r="J4" s="61" t="s">
         <v>16</v>
       </c>
       <c r="K4" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G4,$C:$C,"&lt;&gt;新中心")</f>
         <v>4</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="M4" s="35">
-        <f>K5+K6+K13</f>
-        <v>12</v>
+        <f>COUNTIF(F:F,L4)</f>
+        <v>13</v>
       </c>
       <c r="N4" t="s">
         <v>17</v>
       </c>
       <c r="O4">
         <f>M5+M6</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1">
@@ -2816,22 +2841,22 @@
         <v>20</v>
       </c>
       <c r="H5" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G5)</f>
         <v>5</v>
       </c>
       <c r="J5" s="61" t="s">
         <v>20</v>
       </c>
       <c r="K5" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G5,$C:$C,"&lt;&gt;新中心")</f>
         <v>5</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M5" s="35">
-        <f>K7+K8+K9</f>
-        <v>11</v>
+        <f>COUNTIF(F:F,L5)</f>
+        <v>12</v>
       </c>
       <c r="N5" t="s">
         <v>21</v>
@@ -2860,21 +2885,21 @@
         <v>25</v>
       </c>
       <c r="H6" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G6)</f>
         <v>3</v>
       </c>
       <c r="J6" s="61" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G6,$C:$C,"&lt;&gt;新中心")</f>
         <v>3</v>
       </c>
       <c r="L6" s="34" t="s">
         <v>40</v>
       </c>
       <c r="M6" s="35">
-        <f>K10</f>
+        <f>COUNTIF(F:F,L6)</f>
         <v>7</v>
       </c>
     </row>
@@ -2897,21 +2922,21 @@
         <v>29</v>
       </c>
       <c r="H7" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G7)</f>
         <v>5</v>
       </c>
       <c r="J7" s="61" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G7,$C:$C,"&lt;&gt;新中心")</f>
         <v>5</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M7" s="35">
-        <f>K11+K12</f>
+        <f>COUNTIF(F:F,L7)</f>
         <v>17</v>
       </c>
     </row>
@@ -2934,14 +2959,14 @@
         <v>34</v>
       </c>
       <c r="H8" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G8)</f>
         <v>3</v>
       </c>
       <c r="J8" s="61" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G8,$C:$C,"&lt;&gt;新中心")</f>
         <v>3</v>
       </c>
     </row>
@@ -2964,14 +2989,14 @@
         <v>37</v>
       </c>
       <c r="H9" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G9)</f>
         <v>3</v>
       </c>
       <c r="J9" s="61" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G9,$C:$C,"&lt;&gt;新中心")</f>
         <v>3</v>
       </c>
     </row>
@@ -2994,14 +3019,14 @@
         <v>40</v>
       </c>
       <c r="H10" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G10)</f>
         <v>7</v>
       </c>
       <c r="J10" s="61" t="s">
         <v>40</v>
       </c>
       <c r="K10" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G10,$C:$C,"&lt;&gt;新中心")</f>
         <v>7</v>
       </c>
     </row>
@@ -3018,20 +3043,20 @@
       <c r="D11" s="71"/>
       <c r="E11" s="69"/>
       <c r="F11" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G11" s="48" t="s">
         <v>43</v>
       </c>
       <c r="H11" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G11)</f>
         <v>11</v>
       </c>
       <c r="J11" s="61" t="s">
         <v>43</v>
       </c>
       <c r="K11" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G11,$C:$C,"&lt;&gt;新中心")</f>
         <v>11</v>
       </c>
     </row>
@@ -3048,20 +3073,20 @@
       <c r="D12" s="73"/>
       <c r="E12" s="69"/>
       <c r="F12" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G12" s="48" t="s">
         <v>45</v>
       </c>
       <c r="H12" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G12)</f>
         <v>6</v>
       </c>
       <c r="J12" s="61" t="s">
         <v>45</v>
       </c>
       <c r="K12" s="62">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($A:$A,$G12,$C:$C,"&lt;&gt;新中心")</f>
         <v>6</v>
       </c>
     </row>
@@ -3078,20 +3103,20 @@
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
       <c r="F13" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G13" s="48" t="s">
         <v>49</v>
       </c>
       <c r="H13" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K13" s="62">
-        <f>COUNTIFS($A:$A,$G15,$C:$C,"&lt;&gt;新中心")</f>
+        <f>COUNTIFS($A:$A,$G16,$C:$C,"&lt;&gt;新中心")</f>
         <v>4</v>
       </c>
     </row>
@@ -3108,62 +3133,64 @@
       <c r="D14" s="70"/>
       <c r="E14" s="69"/>
       <c r="F14" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" s="48" t="s">
         <v>51</v>
       </c>
       <c r="H14" s="23">
-        <f t="shared" si="0"/>
+        <f>COUNTIF($A:$A,$G14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.5" customHeight="1">
+    <row r="15" spans="1:15" s="82" customFormat="1" ht="16.5" customHeight="1">
       <c r="A15" s="61" t="s">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="D15" s="70"/>
       <c r="E15" s="69"/>
       <c r="F15" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="G15" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="23">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G15" s="83"/>
+      <c r="H15" s="23"/>
+      <c r="J15" s="81"/>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="A16" s="61" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="69"/>
       <c r="F16" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="67"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.5" customHeight="1">
+        <v>131</v>
+      </c>
+      <c r="G16" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="23">
+        <f>COUNTIF($A:$A,$G16)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16.5" customHeight="1">
       <c r="A17" s="61" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="61" t="s">
         <v>9</v>
@@ -3171,16 +3198,16 @@
       <c r="D17" s="68"/>
       <c r="E17" s="69"/>
       <c r="F17" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G17" s="67"/>
     </row>
-    <row r="18" spans="1:7" ht="16.5" customHeight="1">
+    <row r="18" spans="1:10" ht="16.5" customHeight="1">
       <c r="A18" s="61" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" s="61" t="s">
         <v>9</v>
@@ -3188,16 +3215,16 @@
       <c r="D18" s="68"/>
       <c r="E18" s="69"/>
       <c r="F18" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G18" s="67"/>
     </row>
-    <row r="19" spans="1:7" ht="16.5" customHeight="1">
+    <row r="19" spans="1:10" ht="16.5" customHeight="1">
       <c r="A19" s="61" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C19" s="61" t="s">
         <v>9</v>
@@ -3205,186 +3232,188 @@
       <c r="D19" s="68"/>
       <c r="E19" s="69"/>
       <c r="F19" s="63" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G19" s="67"/>
     </row>
-    <row r="20" spans="1:7" ht="16.5" customHeight="1">
+    <row r="20" spans="1:10" ht="16.5" customHeight="1">
       <c r="A20" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="73"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="69"/>
       <c r="F20" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G20" s="67"/>
     </row>
-    <row r="21" spans="1:7" ht="16.5" customHeight="1">
+    <row r="21" spans="1:10" ht="16.5" customHeight="1">
       <c r="A21" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="70"/>
+      <c r="D21" s="73"/>
       <c r="E21" s="69"/>
       <c r="F21" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G21" s="67"/>
     </row>
-    <row r="22" spans="1:7" ht="16.5" customHeight="1">
+    <row r="22" spans="1:10" ht="16.5" customHeight="1">
       <c r="A22" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C22" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="74"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="69"/>
       <c r="F22" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G22" s="67"/>
     </row>
-    <row r="23" spans="1:7" ht="16.5" customHeight="1">
+    <row r="23" spans="1:10" ht="16.5" customHeight="1">
       <c r="A23" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="68"/>
+        <v>63</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="74"/>
       <c r="E23" s="69"/>
       <c r="F23" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G23" s="67"/>
     </row>
-    <row r="24" spans="1:7" ht="16.5" customHeight="1">
+    <row r="24" spans="1:10" ht="16.5" customHeight="1">
       <c r="A24" s="61" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B24" s="61" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="71"/>
+      <c r="D24" s="68"/>
       <c r="E24" s="69"/>
       <c r="F24" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G24" s="67"/>
     </row>
-    <row r="25" spans="1:7" ht="16.5" customHeight="1">
+    <row r="25" spans="1:10" s="82" customFormat="1" ht="16.5" customHeight="1">
       <c r="A25" s="61" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="C25" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="71"/>
+        <v>206</v>
+      </c>
+      <c r="D25" s="68"/>
       <c r="E25" s="69"/>
       <c r="F25" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G25" s="67"/>
-    </row>
-    <row r="26" spans="1:7" ht="16.5" customHeight="1">
+      <c r="H25" s="81"/>
+      <c r="J25" s="81"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="61" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C26" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="70"/>
+      <c r="D26" s="71"/>
       <c r="E26" s="69"/>
       <c r="F26" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G26" s="67"/>
     </row>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1">
+    <row r="27" spans="1:10" ht="16.5" customHeight="1">
       <c r="A27" s="61" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C27" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="68"/>
+      <c r="D27" s="71"/>
       <c r="E27" s="69"/>
       <c r="F27" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G27" s="67"/>
     </row>
-    <row r="28" spans="1:7" ht="16.5" customHeight="1">
+    <row r="28" spans="1:10" ht="16.5" customHeight="1">
       <c r="A28" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>74</v>
+        <v>34</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>70</v>
       </c>
       <c r="C28" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="71"/>
+      <c r="D28" s="70"/>
       <c r="E28" s="69"/>
       <c r="F28" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G28" s="67"/>
     </row>
-    <row r="29" spans="1:7" ht="16.5" customHeight="1">
+    <row r="29" spans="1:10" ht="16.5" customHeight="1">
       <c r="A29" s="61" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="61" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C29" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="71"/>
+      <c r="D29" s="68"/>
       <c r="E29" s="69"/>
       <c r="F29" s="63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G29" s="67"/>
     </row>
-    <row r="30" spans="1:7" ht="16.5" customHeight="1">
+    <row r="30" spans="1:10" ht="16.5" customHeight="1">
       <c r="A30" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="61" t="s">
-        <v>78</v>
+        <v>37</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>74</v>
       </c>
       <c r="C30" s="75" t="s">
         <v>9</v>
@@ -3392,16 +3421,16 @@
       <c r="D30" s="71"/>
       <c r="E30" s="69"/>
       <c r="F30" s="63" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="G30" s="67"/>
     </row>
-    <row r="31" spans="1:7" ht="16.5" customHeight="1">
+    <row r="31" spans="1:10" ht="16.5" customHeight="1">
       <c r="A31" s="61" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" s="75" t="s">
         <v>9</v>
@@ -3409,16 +3438,16 @@
       <c r="D31" s="71"/>
       <c r="E31" s="69"/>
       <c r="F31" s="63" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="G31" s="67"/>
     </row>
-    <row r="32" spans="1:7" ht="16.5" customHeight="1">
+    <row r="32" spans="1:10" ht="16.5" customHeight="1">
       <c r="A32" s="61" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32" s="75" t="s">
         <v>9</v>
@@ -3435,12 +3464,12 @@
         <v>40</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="C33" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="73"/>
+      <c r="D33" s="71"/>
       <c r="E33" s="69"/>
       <c r="F33" s="63" t="s">
         <v>40</v>
@@ -3452,7 +3481,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C34" s="75" t="s">
         <v>9</v>
@@ -3466,35 +3495,35 @@
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1">
       <c r="A35" s="61" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="C35" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="70"/>
+      <c r="D35" s="73"/>
       <c r="E35" s="69"/>
       <c r="F35" s="63" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G35" s="67"/>
     </row>
     <row r="36" spans="1:7" ht="16.5" customHeight="1">
       <c r="A36" s="61" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" s="61" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C36" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="70"/>
+      <c r="D36" s="71"/>
       <c r="E36" s="69"/>
       <c r="F36" s="63" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G36" s="67"/>
     </row>
@@ -3503,15 +3532,15 @@
         <v>43</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C37" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="68"/>
+      <c r="D37" s="70"/>
       <c r="E37" s="69"/>
       <c r="F37" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G37" s="67"/>
     </row>
@@ -3520,15 +3549,15 @@
         <v>43</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C38" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="71"/>
+      <c r="D38" s="70"/>
       <c r="E38" s="69"/>
       <c r="F38" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G38" s="67"/>
     </row>
@@ -3537,7 +3566,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="61" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C39" s="75" t="s">
         <v>9</v>
@@ -3545,7 +3574,7 @@
       <c r="D39" s="68"/>
       <c r="E39" s="69"/>
       <c r="F39" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G39" s="67"/>
     </row>
@@ -3554,15 +3583,15 @@
         <v>43</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="68"/>
+      <c r="D40" s="71"/>
       <c r="E40" s="69"/>
       <c r="F40" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G40" s="67"/>
     </row>
@@ -3571,15 +3600,15 @@
         <v>43</v>
       </c>
       <c r="B41" s="61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C41" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="71"/>
+      <c r="D41" s="68"/>
       <c r="E41" s="69"/>
       <c r="F41" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G41" s="67"/>
     </row>
@@ -3588,15 +3617,15 @@
         <v>43</v>
       </c>
       <c r="B42" s="61" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C42" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="71"/>
+      <c r="D42" s="68"/>
       <c r="E42" s="69"/>
       <c r="F42" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G42" s="67"/>
     </row>
@@ -3605,7 +3634,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43" s="75" t="s">
         <v>9</v>
@@ -3613,7 +3642,7 @@
       <c r="D43" s="71"/>
       <c r="E43" s="69"/>
       <c r="F43" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G43" s="67"/>
     </row>
@@ -3622,15 +3651,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="61" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C44" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="68"/>
-      <c r="E44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G44" s="67"/>
     </row>
@@ -3639,7 +3668,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="61" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="C45" s="75" t="s">
         <v>9</v>
@@ -3647,33 +3676,33 @@
       <c r="D45" s="71"/>
       <c r="E45" s="69"/>
       <c r="F45" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G45" s="67"/>
     </row>
     <row r="46" spans="1:7" ht="16.5" customHeight="1">
       <c r="A46" s="61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C46" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="71"/>
-      <c r="E46" s="69"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="71"/>
       <c r="F46" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G46" s="67"/>
     </row>
     <row r="47" spans="1:7" ht="16.5" customHeight="1">
       <c r="A47" s="61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C47" s="75" t="s">
         <v>9</v>
@@ -3681,7 +3710,7 @@
       <c r="D47" s="71"/>
       <c r="E47" s="69"/>
       <c r="F47" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G47" s="67"/>
     </row>
@@ -3690,7 +3719,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="61" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C48" s="75" t="s">
         <v>9</v>
@@ -3698,7 +3727,7 @@
       <c r="D48" s="71"/>
       <c r="E48" s="69"/>
       <c r="F48" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G48" s="67"/>
     </row>
@@ -3707,7 +3736,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="61" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="C49" s="75" t="s">
         <v>9</v>
@@ -3715,67 +3744,67 @@
       <c r="D49" s="71"/>
       <c r="E49" s="69"/>
       <c r="F49" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G49" s="67"/>
     </row>
-    <row r="50" spans="1:7" ht="16" customHeight="1">
-      <c r="A50" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="72" t="s">
-        <v>143</v>
-      </c>
-      <c r="C50" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="70"/>
+    <row r="50" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A50" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="71"/>
       <c r="E50" s="69"/>
       <c r="F50" s="63" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G50" s="67"/>
     </row>
     <row r="51" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A51" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="C51" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="70"/>
+      <c r="A51" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="71"/>
       <c r="E51" s="69"/>
       <c r="F51" s="63" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G51" s="67"/>
     </row>
-    <row r="52" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A52" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="59" t="s">
+    <row r="52" spans="1:7" ht="16" customHeight="1">
+      <c r="A52" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="76" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="70"/>
       <c r="E52" s="69"/>
       <c r="F52" s="63" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="G52" s="67"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" customHeight="1">
       <c r="A53" s="58" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C53" s="59" t="s">
         <v>9</v>
@@ -3783,50 +3812,50 @@
       <c r="D53" s="70"/>
       <c r="E53" s="69"/>
       <c r="F53" s="63" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G53" s="67"/>
     </row>
     <row r="54" spans="1:7" ht="16.5" customHeight="1">
       <c r="A54" s="58" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C54" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="68"/>
+      <c r="D54" s="70"/>
       <c r="E54" s="69"/>
       <c r="F54" s="63" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G54" s="67"/>
     </row>
     <row r="55" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A55" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B55" s="60" t="s">
-        <v>148</v>
+      <c r="A55" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>144</v>
       </c>
       <c r="C55" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="68"/>
+      <c r="D55" s="70"/>
       <c r="E55" s="69"/>
       <c r="F55" s="63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G55" s="67"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A56" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="60" t="s">
-        <v>149</v>
+      <c r="A56" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="58" t="s">
+        <v>145</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>9</v>
@@ -3834,16 +3863,16 @@
       <c r="D56" s="68"/>
       <c r="E56" s="69"/>
       <c r="F56" s="63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G56" s="67"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B57" s="60" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C57" s="59" t="s">
         <v>9</v>
@@ -3851,16 +3880,16 @@
       <c r="D57" s="68"/>
       <c r="E57" s="69"/>
       <c r="F57" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G57" s="67"/>
     </row>
     <row r="58" spans="1:7" ht="16.5" customHeight="1">
       <c r="A58" s="60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C58" s="59" t="s">
         <v>9</v>
@@ -3868,44 +3897,76 @@
       <c r="D58" s="68"/>
       <c r="E58" s="69"/>
       <c r="F58" s="63" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G58" s="67"/>
     </row>
-    <row r="59" spans="1:7" ht="16" customHeight="1">
+    <row r="59" spans="1:7" ht="16.5" customHeight="1">
       <c r="A59" s="60" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" s="59" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="68"/>
       <c r="E59" s="69"/>
       <c r="F59" s="63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16" customHeight="1">
+        <v>131</v>
+      </c>
+      <c r="G59" s="67"/>
+    </row>
+    <row r="60" spans="1:7" ht="16.5" customHeight="1">
       <c r="A60" s="60" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="59" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="68"/>
       <c r="E60" s="69"/>
       <c r="F60" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="G60" s="67"/>
+    </row>
+    <row r="61" spans="1:7" ht="16" customHeight="1">
+      <c r="A61" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="68"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" customHeight="1">
+      <c r="A62" s="60" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="16" customHeight="1"/>
-    <row r="62" spans="1:7" ht="16" customHeight="1"/>
+      <c r="B62" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="68"/>
+      <c r="E62" s="69"/>
+      <c r="F62" s="63" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="63" spans="1:7" ht="16" customHeight="1"/>
     <row r="64" spans="1:7" ht="16" customHeight="1"/>
     <row r="65" ht="16" customHeight="1"/>
@@ -4103,8 +4164,10 @@
     <row r="257" ht="16" customHeight="1"/>
     <row r="258" ht="16" customHeight="1"/>
     <row r="259" ht="16" customHeight="1"/>
+    <row r="260" ht="16" customHeight="1"/>
+    <row r="261" ht="16" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:F58" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:F60" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4130,7 +4193,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="22.5" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -4157,43 +4220,43 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>5</v>
@@ -4418,7 +4481,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -4602,7 +4665,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -5112,7 +5175,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -6279,7 +6342,7 @@
   <sheetData>
     <row r="1" spans="1:22" ht="22.5" customHeight="1">
       <c r="A1" s="78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -6306,43 +6369,43 @@
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="J2" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="M2" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>166</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>168</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>5</v>
@@ -6383,7 +6446,7 @@
         <v>5</v>
       </c>
       <c r="U3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V3">
         <f>T3+T4</f>
@@ -6530,7 +6593,7 @@
         <v>5</v>
       </c>
       <c r="U7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V7">
         <f>T7+T8+T9</f>
@@ -6573,7 +6636,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -6670,7 +6733,7 @@
         <v>8</v>
       </c>
       <c r="U11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="V11">
         <f>T11+T12</f>
@@ -6782,7 +6845,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -7240,7 +7303,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -8451,7 +8514,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G6" s="31" t="s">
         <v>25</v>
@@ -8486,7 +8549,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>29</v>
@@ -8647,7 +8710,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E13" s="33"/>
       <c r="G13" s="31" t="s">
@@ -8866,7 +8929,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16.5" customHeight="1">
@@ -8894,7 +8957,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5" customHeight="1">
@@ -8908,7 +8971,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16.5" customHeight="1">
@@ -8925,7 +8988,7 @@
         <v>66</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.5" customHeight="1">
@@ -8933,7 +8996,7 @@
         <v>40</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C33" s="42" t="s">
         <v>9</v>
@@ -8953,7 +9016,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5" customHeight="1">
@@ -9054,7 +9117,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" s="42" t="s">
         <v>9</v>
@@ -9092,13 +9155,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="46" t="s">
         <v>140</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5" customHeight="1">
@@ -9126,7 +9189,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5" customHeight="1">
@@ -9148,7 +9211,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C49" s="42" t="s">
         <v>9</v>
@@ -9205,7 +9268,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C53" s="50" t="s">
         <v>9</v>
@@ -9219,7 +9282,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C54" s="57" t="s">
         <v>9</v>
@@ -9233,7 +9296,7 @@
         <v>40</v>
       </c>
       <c r="B55" s="56" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="57" t="s">
         <v>9</v>
@@ -9247,7 +9310,7 @@
         <v>45</v>
       </c>
       <c r="B56" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C56" s="57" t="s">
         <v>9</v>
@@ -9261,7 +9324,7 @@
         <v>45</v>
       </c>
       <c r="B57" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C57" s="57" t="s">
         <v>9</v>
@@ -9299,13 +9362,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>172</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>174</v>
       </c>
       <c r="G1" s="23" t="s">
         <v>3</v>
@@ -9323,10 +9386,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>9</v>
@@ -9341,7 +9404,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I2" s="23">
         <v>7</v>
@@ -9352,7 +9415,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>18</v>
@@ -9364,7 +9427,7 @@
         <v>77</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I3" s="23">
         <v>6</v>
@@ -9375,7 +9438,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>27</v>
@@ -9384,13 +9447,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>53</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I4" s="23">
         <v>8</v>
@@ -9401,25 +9464,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I5" s="23">
         <v>8</v>
@@ -9430,19 +9493,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C6" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>182</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>184</v>
       </c>
       <c r="I6" s="23">
         <v>4</v>
@@ -9453,17 +9516,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I7" s="23">
         <v>3</v>
@@ -9474,19 +9537,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
@@ -9494,16 +9557,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
@@ -9511,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>56</v>
@@ -9528,7 +9591,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>50</v>
@@ -9540,7 +9603,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
@@ -9548,7 +9611,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>54</v>
@@ -9557,7 +9620,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
@@ -9565,7 +9628,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>44</v>
@@ -9574,7 +9637,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>10</v>
@@ -9585,7 +9648,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>55</v>
@@ -9599,7 +9662,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>41</v>
@@ -9608,7 +9671,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G15" s="23" t="s">
         <v>88</v>
@@ -9619,7 +9682,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>58</v>
@@ -9628,7 +9691,7 @@
         <v>9</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
@@ -9636,7 +9699,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>67</v>
@@ -9648,7 +9711,7 @@
         <v>66</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G17" s="23" t="s">
         <v>53</v>
@@ -9659,7 +9722,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>74</v>
@@ -9668,10 +9731,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G18" s="23" t="s">
         <v>59</v>
@@ -9682,7 +9745,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>63</v>
@@ -9699,7 +9762,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>71</v>
@@ -9719,7 +9782,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>60</v>
@@ -9728,7 +9791,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>28</v>
@@ -9739,7 +9802,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>65</v>
@@ -9751,7 +9814,7 @@
         <v>115</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1">
@@ -9759,7 +9822,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>68</v>
@@ -9779,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>114</v>
@@ -9799,7 +9862,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>117</v>
@@ -9819,7 +9882,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>90</v>
@@ -9836,7 +9899,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>102</v>
@@ -9848,7 +9911,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
@@ -9856,7 +9919,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>87</v>
@@ -9868,7 +9931,7 @@
         <v>59</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
@@ -9876,7 +9939,7 @@
         <v>6</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>101</v>
@@ -9885,7 +9948,7 @@
         <v>9</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G29" s="23" t="s">
         <v>10</v>
@@ -9896,7 +9959,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>93</v>
@@ -9919,7 +9982,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>91</v>
@@ -9928,7 +9991,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F31" s="23" t="s">
         <v>66</v>
@@ -9939,7 +10002,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C32" s="24" t="s">
         <v>107</v>
@@ -9948,7 +10011,7 @@
         <v>9</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G32" s="23" t="s">
         <v>59</v>
@@ -9959,7 +10022,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>110</v>
@@ -9968,7 +10031,7 @@
         <v>9</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G33" s="23" t="s">
         <v>59</v>
@@ -9979,7 +10042,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>111</v>
@@ -9999,7 +10062,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>112</v>
@@ -10019,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>78</v>
@@ -10031,7 +10094,7 @@
         <v>77</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
@@ -10039,7 +10102,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>83</v>
@@ -10048,10 +10111,10 @@
         <v>9</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G37" s="23" t="s">
         <v>59</v>
@@ -10062,7 +10125,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>81</v>
@@ -10071,7 +10134,7 @@
         <v>9</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G38" s="23" t="s">
         <v>10</v>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linxiaozhong/Downloads/日报及月报/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D4FEA7-8D5E-DB4C-88BD-E450562545CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6386E29F-7E27-A64E-B1F5-E097A8ABE5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="211">
   <si>
     <t>区域</t>
   </si>
@@ -676,6 +676,10 @@
   </si>
   <si>
     <t>粤东区</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海金桥中心</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1093,7 +1097,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1324,18 +1328,17 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2682,7 +2685,7 @@
   <sheetPr codeName="2026年日报">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O261"/>
+  <dimension ref="A1:O262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.1640625" style="53" customWidth="1"/>
@@ -2723,14 +2726,14 @@
         <v>5</v>
       </c>
       <c r="H2" s="24">
-        <f>SUM(H3:H106)</f>
+        <f>SUM(H3:H107)</f>
         <v>58</v>
       </c>
       <c r="J2" s="64" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="62">
-        <f>SUM(K3:K106)</f>
+        <f>SUM(K3:K107)</f>
         <v>58</v>
       </c>
     </row>
@@ -2819,7 +2822,7 @@
       </c>
       <c r="O4">
         <f>M5+M6</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1">
@@ -2856,7 +2859,7 @@
       </c>
       <c r="M5" s="35">
         <f>COUNTIF(F:F,L5)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N5" t="s">
         <v>21</v>
@@ -3143,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="82" customFormat="1" ht="16.5" customHeight="1">
+    <row r="15" spans="1:15" s="78" customFormat="1" ht="16.5" customHeight="1">
       <c r="A15" s="61" t="s">
         <v>207</v>
       </c>
@@ -3158,9 +3161,9 @@
       <c r="F15" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="G15" s="83"/>
+      <c r="G15" s="79"/>
       <c r="H15" s="23"/>
-      <c r="J15" s="81"/>
+      <c r="J15" s="67"/>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1">
       <c r="A16" s="61" t="s">
@@ -3321,7 +3324,7 @@
       </c>
       <c r="G24" s="67"/>
     </row>
-    <row r="25" spans="1:10" s="82" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="1:10" s="78" customFormat="1" ht="16.5" customHeight="1">
       <c r="A25" s="61" t="s">
         <v>204</v>
       </c>
@@ -3337,32 +3340,34 @@
         <v>127</v>
       </c>
       <c r="G25" s="67"/>
-      <c r="H25" s="81"/>
-      <c r="J25" s="81"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1">
+      <c r="H25" s="67"/>
+      <c r="J25" s="67"/>
+    </row>
+    <row r="26" spans="1:10" s="78" customFormat="1" ht="16.5" customHeight="1">
       <c r="A26" s="61" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>67</v>
+        <v>210</v>
       </c>
       <c r="C26" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="71"/>
+        <v>206</v>
+      </c>
+      <c r="D26" s="68"/>
       <c r="E26" s="69"/>
       <c r="F26" s="63" t="s">
         <v>127</v>
       </c>
       <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="J26" s="67"/>
     </row>
     <row r="27" spans="1:10" ht="16.5" customHeight="1">
       <c r="A27" s="61" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="75" t="s">
         <v>9</v>
@@ -3379,12 +3384,12 @@
         <v>34</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="70"/>
+      <c r="D28" s="71"/>
       <c r="E28" s="69"/>
       <c r="F28" s="63" t="s">
         <v>127</v>
@@ -3393,15 +3398,15 @@
     </row>
     <row r="29" spans="1:10" ht="16.5" customHeight="1">
       <c r="A29" s="61" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B29" s="61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="70"/>
       <c r="E29" s="69"/>
       <c r="F29" s="63" t="s">
         <v>127</v>
@@ -3412,13 +3417,13 @@
       <c r="A30" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="63" t="s">
-        <v>74</v>
+      <c r="B30" s="61" t="s">
+        <v>71</v>
       </c>
       <c r="C30" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="71"/>
+      <c r="D30" s="68"/>
       <c r="E30" s="69"/>
       <c r="F30" s="63" t="s">
         <v>127</v>
@@ -3429,8 +3434,8 @@
       <c r="A31" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="61" t="s">
-        <v>76</v>
+      <c r="B31" s="63" t="s">
+        <v>74</v>
       </c>
       <c r="C31" s="75" t="s">
         <v>9</v>
@@ -3444,10 +3449,10 @@
     </row>
     <row r="32" spans="1:10" ht="16.5" customHeight="1">
       <c r="A32" s="61" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B32" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C32" s="75" t="s">
         <v>9</v>
@@ -3455,7 +3460,7 @@
       <c r="D32" s="71"/>
       <c r="E32" s="69"/>
       <c r="F32" s="63" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="G32" s="67"/>
     </row>
@@ -3464,7 +3469,7 @@
         <v>40</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" s="75" t="s">
         <v>9</v>
@@ -3481,7 +3486,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="75" t="s">
         <v>9</v>
@@ -3498,12 +3503,12 @@
         <v>40</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="C35" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="73"/>
+      <c r="D35" s="71"/>
       <c r="E35" s="69"/>
       <c r="F35" s="63" t="s">
         <v>40</v>
@@ -3515,12 +3520,12 @@
         <v>40</v>
       </c>
       <c r="B36" s="61" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="C36" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="71"/>
+      <c r="D36" s="73"/>
       <c r="E36" s="69"/>
       <c r="F36" s="63" t="s">
         <v>40</v>
@@ -3529,18 +3534,18 @@
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1">
       <c r="A37" s="61" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B37" s="61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C37" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="70"/>
+      <c r="D37" s="71"/>
       <c r="E37" s="69"/>
       <c r="F37" s="63" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="G37" s="67"/>
     </row>
@@ -3549,7 +3554,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" s="75" t="s">
         <v>9</v>
@@ -3566,12 +3571,12 @@
         <v>43</v>
       </c>
       <c r="B39" s="61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="68"/>
+      <c r="D39" s="70"/>
       <c r="E39" s="69"/>
       <c r="F39" s="63" t="s">
         <v>129</v>
@@ -3583,12 +3588,12 @@
         <v>43</v>
       </c>
       <c r="B40" s="61" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C40" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="71"/>
+      <c r="D40" s="68"/>
       <c r="E40" s="69"/>
       <c r="F40" s="63" t="s">
         <v>129</v>
@@ -3600,12 +3605,12 @@
         <v>43</v>
       </c>
       <c r="B41" s="61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C41" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="68"/>
+      <c r="D41" s="71"/>
       <c r="E41" s="69"/>
       <c r="F41" s="63" t="s">
         <v>129</v>
@@ -3617,7 +3622,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" s="75" t="s">
         <v>9</v>
@@ -3634,12 +3639,12 @@
         <v>43</v>
       </c>
       <c r="B43" s="61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="71"/>
+      <c r="D43" s="68"/>
       <c r="E43" s="69"/>
       <c r="F43" s="63" t="s">
         <v>129</v>
@@ -3651,7 +3656,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="61" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C44" s="75" t="s">
         <v>9</v>
@@ -3668,7 +3673,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="61" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C45" s="75" t="s">
         <v>9</v>
@@ -3685,13 +3690,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C46" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="69"/>
       <c r="F46" s="63" t="s">
         <v>129</v>
       </c>
@@ -3702,13 +3707,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="C47" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="71"/>
-      <c r="E47" s="69"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="71"/>
       <c r="F47" s="63" t="s">
         <v>129</v>
       </c>
@@ -3716,10 +3721,10 @@
     </row>
     <row r="48" spans="1:7" ht="16.5" customHeight="1">
       <c r="A48" s="61" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="61" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="C48" s="75" t="s">
         <v>9</v>
@@ -3736,7 +3741,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C49" s="75" t="s">
         <v>9</v>
@@ -3753,7 +3758,7 @@
         <v>45</v>
       </c>
       <c r="B50" s="61" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C50" s="75" t="s">
         <v>9</v>
@@ -3770,7 +3775,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="61" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C51" s="75" t="s">
         <v>9</v>
@@ -3782,31 +3787,31 @@
       </c>
       <c r="G51" s="67"/>
     </row>
-    <row r="52" spans="1:7" ht="16" customHeight="1">
-      <c r="A52" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="72" t="s">
-        <v>141</v>
-      </c>
-      <c r="C52" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="70"/>
+    <row r="52" spans="1:7" ht="16.5" customHeight="1">
+      <c r="A52" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="71"/>
       <c r="E52" s="69"/>
       <c r="F52" s="63" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G52" s="67"/>
     </row>
-    <row r="53" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A53" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="C53" s="59" t="s">
+    <row r="53" spans="1:7" ht="16" customHeight="1">
+      <c r="A53" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="76" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="70"/>
@@ -3818,10 +3823,10 @@
     </row>
     <row r="54" spans="1:7" ht="16.5" customHeight="1">
       <c r="A54" s="58" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C54" s="59" t="s">
         <v>9</v>
@@ -3829,16 +3834,16 @@
       <c r="D54" s="70"/>
       <c r="E54" s="69"/>
       <c r="F54" s="63" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="G54" s="67"/>
     </row>
     <row r="55" spans="1:7" ht="16.5" customHeight="1">
       <c r="A55" s="58" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C55" s="59" t="s">
         <v>9</v>
@@ -3846,7 +3851,7 @@
       <c r="D55" s="70"/>
       <c r="E55" s="69"/>
       <c r="F55" s="63" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="G55" s="67"/>
     </row>
@@ -3855,12 +3860,12 @@
         <v>45</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C56" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="68"/>
+      <c r="D56" s="70"/>
       <c r="E56" s="69"/>
       <c r="F56" s="63" t="s">
         <v>129</v>
@@ -3868,11 +3873,11 @@
       <c r="G56" s="67"/>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A57" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="B57" s="60" t="s">
-        <v>146</v>
+      <c r="A57" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="58" t="s">
+        <v>145</v>
       </c>
       <c r="C57" s="59" t="s">
         <v>9</v>
@@ -3880,7 +3885,7 @@
       <c r="D57" s="68"/>
       <c r="E57" s="69"/>
       <c r="F57" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G57" s="67"/>
     </row>
@@ -3889,7 +3894,7 @@
         <v>132</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="59" t="s">
         <v>9</v>
@@ -3906,7 +3911,7 @@
         <v>132</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" s="59" t="s">
         <v>9</v>
@@ -3923,7 +3928,7 @@
         <v>132</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C60" s="59" t="s">
         <v>9</v>
@@ -3935,28 +3940,29 @@
       </c>
       <c r="G60" s="67"/>
     </row>
-    <row r="61" spans="1:7" ht="16" customHeight="1">
+    <row r="61" spans="1:7" ht="16.5" customHeight="1">
       <c r="A61" s="60" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="B61" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="59" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="68"/>
       <c r="E61" s="69"/>
       <c r="F61" s="63" t="s">
-        <v>125</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="G61" s="67"/>
     </row>
     <row r="62" spans="1:7" ht="16" customHeight="1">
       <c r="A62" s="60" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B62" s="60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C62" s="77" t="s">
         <v>9</v>
@@ -3964,10 +3970,25 @@
       <c r="D62" s="68"/>
       <c r="E62" s="69"/>
       <c r="F62" s="63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" customHeight="1">
+      <c r="A63" s="60" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" customHeight="1"/>
+      <c r="B63" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C63" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="68"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="63" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="64" spans="1:7" ht="16" customHeight="1"/>
     <row r="65" ht="16" customHeight="1"/>
     <row r="66" ht="16" customHeight="1"/>
@@ -4166,8 +4187,9 @@
     <row r="259" ht="16" customHeight="1"/>
     <row r="260" ht="16" customHeight="1"/>
     <row r="261" ht="16" customHeight="1"/>
+    <row r="262" ht="16" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:F60" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:F61" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4192,23 +4214,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="22.5" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="82"/>
       <c r="S1" s="1"/>
       <c r="T1" s="2"/>
     </row>
@@ -6341,23 +6363,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="22.5" customHeight="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="82"/>
       <c r="S1" s="1"/>
       <c r="T1" s="2"/>
     </row>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46177</v>
+        <v>46186</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3701,7 +3701,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D31" s="71" t="n"/>
+      <c r="D31" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E31" s="69" t="n"/>
       <c r="F31" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46186</v>
+        <v>46188</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3830,7 +3830,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D36" s="73" t="n"/>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E36" s="69" t="n"/>
       <c r="F36" s="63" t="inlineStr">
         <is>
@@ -4380,7 +4384,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D58" s="68" t="n"/>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E58" s="69" t="n"/>
       <c r="F58" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4259,7 +4259,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D53" s="70" t="n"/>
+      <c r="D53" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E53" s="69" t="n"/>
       <c r="F53" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46190</v>
+        <v>46192</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2824,7 +2824,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="68" t="n"/>
+      <c r="D5" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E5" s="69" t="n"/>
       <c r="F5" s="63" t="inlineStr">
         <is>
@@ -2988,7 +2992,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>迟发2次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>迟发2次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3578,7 +3578,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D26" s="68" t="n"/>
+      <c r="D26" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E26" s="69" t="n"/>
       <c r="F26" s="63" t="inlineStr">
         <is>
@@ -3605,7 +3609,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D27" s="71" t="n"/>
+      <c r="D27" s="71" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E27" s="69" t="n"/>
       <c r="F27" s="63" t="inlineStr">
         <is>
@@ -3836,7 +3844,7 @@
       </c>
       <c r="D36" s="73" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E36" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2888,7 +2888,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D6" s="68" t="n"/>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E6" s="69" t="n"/>
       <c r="F6" s="63" t="inlineStr">
         <is>
@@ -4121,7 +4125,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D47" s="68" t="n"/>
+      <c r="D47" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E47" s="71" t="n"/>
       <c r="F47" s="63" t="inlineStr">
         <is>
@@ -4528,7 +4536,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D63" s="68" t="n"/>
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E63" s="69" t="n"/>
       <c r="F63" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46194</v>
+        <v>46198</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D19" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E19" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46198</v>
+        <v>46200</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3975,7 +3975,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D41" s="71" t="n"/>
+      <c r="D41" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E41" s="69" t="n"/>
       <c r="F41" s="63" t="inlineStr">
         <is>
@@ -4075,7 +4079,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D45" s="71" t="n"/>
+      <c r="D45" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E45" s="69" t="n"/>
       <c r="F45" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3900,7 +3900,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D38" s="70" t="n"/>
+      <c r="D38" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E38" s="69" t="n"/>
       <c r="F38" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46201</v>
+        <v>46203</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D19" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E19" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4191,7 +4191,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D49" s="71" t="n"/>
+      <c r="D49" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E49" s="69" t="n"/>
       <c r="F49" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4033,7 +4033,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D43" s="68" t="n"/>
+      <c r="D43" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E43" s="69" t="n"/>
       <c r="F43" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D36" s="73" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E36" s="69" t="n"/>
@@ -4353,7 +4353,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D55" s="70" t="n"/>
+      <c r="D55" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E55" s="69" t="n"/>
       <c r="F55" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>
@@ -3796,7 +3796,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D34" s="71" t="n"/>
+      <c r="D34" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E34" s="69" t="n"/>
       <c r="F34" s="63" t="inlineStr">
         <is>
@@ -3902,7 +3906,7 @@
       </c>
       <c r="D38" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E38" s="69" t="n"/>
@@ -4407,7 +4411,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D57" s="68" t="n"/>
+      <c r="D57" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E57" s="69" t="n"/>
       <c r="F57" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3692,7 +3692,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D30" s="68" t="n"/>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E30" s="69" t="n"/>
       <c r="F30" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D8" s="68" t="inlineStr">
         <is>
-          <t>迟发3次</t>
+          <t>迟发4次</t>
         </is>
       </c>
       <c r="E8" s="69" t="n"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>迟发3次</t>
+          <t>迟发4次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -3258,7 +3258,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D14" s="70" t="n"/>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E14" s="69" t="n"/>
       <c r="F14" s="63" t="inlineStr">
         <is>
@@ -3291,7 +3295,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D15" s="70" t="n"/>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E15" s="69" t="n"/>
       <c r="F15" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linxiaozhong/Downloads/日报及月报/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953A1A89-969C-4049-959A-DC274F5E87D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661BBD57-AB3A-0948-BAE6-9DDB5AA97745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="210">
   <si>
     <t>区域</t>
   </si>
@@ -668,6 +668,10 @@
   </si>
   <si>
     <t>迟发2次</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计未发2次，迟发1次</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -3575,8 +3579,8 @@
       <c r="C38" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="70" t="s">
-        <v>77</v>
+      <c r="D38" s="68" t="s">
+        <v>209</v>
       </c>
       <c r="E38" s="69"/>
       <c r="F38" s="63" t="s">

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2618,7 +2618,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H2" s="24">
-        <f>SUM(H3:H107)</f>
+        <f>SUM(H3:H108)</f>
         <v/>
       </c>
       <c r="J2" s="64" t="inlineStr">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="K2" s="62">
-        <f>SUM(K3:K107)</f>
+        <f>SUM(K3:K108)</f>
         <v/>
       </c>
     </row>
@@ -4443,12 +4443,12 @@
     <row r="58" ht="16.5" customHeight="1" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
-          <t>粤西五区</t>
+          <t>华北分公司</t>
         </is>
       </c>
       <c r="B58" s="60" t="inlineStr">
         <is>
-          <t>中山中心</t>
+          <t>太原杏花岭中心</t>
         </is>
       </c>
       <c r="C58" s="59" t="inlineStr">
@@ -4456,15 +4456,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D58" s="68" t="inlineStr">
-        <is>
-          <t>累计未发1次，迟发1次</t>
-        </is>
-      </c>
+      <c r="D58" s="68" t="n"/>
       <c r="E58" s="69" t="n"/>
       <c r="F58" s="63" t="inlineStr">
         <is>
-          <t>粤西区</t>
+          <t>华北分公司</t>
         </is>
       </c>
       <c r="G58" s="67" t="n"/>
@@ -4477,7 +4473,7 @@
       </c>
       <c r="B59" s="60" t="inlineStr">
         <is>
-          <t>茂名中心</t>
+          <t>中山中心</t>
         </is>
       </c>
       <c r="C59" s="59" t="inlineStr">
@@ -4485,7 +4481,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D59" s="68" t="n"/>
+      <c r="D59" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次，迟发1次</t>
+        </is>
+      </c>
       <c r="E59" s="69" t="n"/>
       <c r="F59" s="63" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B60" s="60" t="inlineStr">
         <is>
-          <t>湛江中心</t>
+          <t>茂名中心</t>
         </is>
       </c>
       <c r="C60" s="59" t="inlineStr">
@@ -4510,11 +4510,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D60" s="68" t="inlineStr">
-        <is>
-          <t>累计未发1次</t>
-        </is>
-      </c>
+      <c r="D60" s="68" t="n"/>
       <c r="E60" s="69" t="n"/>
       <c r="F60" s="63" t="inlineStr">
         <is>
@@ -4531,7 +4527,7 @@
       </c>
       <c r="B61" s="60" t="inlineStr">
         <is>
-          <t>江门中心</t>
+          <t>湛江中心</t>
         </is>
       </c>
       <c r="C61" s="59" t="inlineStr">
@@ -4539,7 +4535,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D61" s="68" t="n"/>
+      <c r="D61" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E61" s="69" t="n"/>
       <c r="F61" s="63" t="inlineStr">
         <is>
@@ -4551,12 +4551,12 @@
     <row r="62" ht="16" customHeight="1" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
-          <t>华南一区</t>
+          <t>粤西五区</t>
         </is>
       </c>
       <c r="B62" s="60" t="inlineStr">
         <is>
-          <t>深圳梅林中心</t>
+          <t>江门中心</t>
         </is>
       </c>
       <c r="C62" s="77" t="inlineStr">
@@ -4568,19 +4568,19 @@
       <c r="E62" s="69" t="n"/>
       <c r="F62" s="63" t="inlineStr">
         <is>
-          <t>粤东区</t>
+          <t>粤西区</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
-          <t>华东四区</t>
+          <t>华南一区</t>
         </is>
       </c>
       <c r="B63" s="60" t="inlineStr">
         <is>
-          <t>合肥包河中心</t>
+          <t>深圳梅林中心</t>
         </is>
       </c>
       <c r="C63" s="77" t="inlineStr">
@@ -4588,19 +4588,41 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>累计未发1次</t>
-        </is>
-      </c>
+      <c r="D63" s="68" t="n"/>
       <c r="E63" s="69" t="n"/>
       <c r="F63" s="63" t="inlineStr">
         <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1" s="53">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>华东四区</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="16" customHeight="1" s="53"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>合肥包河中心</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>华东四区</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="16" customHeight="1" s="53"/>
     <row r="66" ht="16" customHeight="1" s="53"/>
     <row r="67" ht="16" customHeight="1" s="53"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16400" windowWidth="27040" xWindow="0" yWindow="500"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,257 +449,257 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1">
+    <xf applyAlignment="1" borderId="7" fillId="7" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="83">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="5" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="10" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="11" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="12" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="16" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="14" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="常规" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1073,16 +1073,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1472,7 +1472,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1642,7 +1642,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D40" s="46" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D48" s="51" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -2619,26 +2619,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46215</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+        <v>46221</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>区域</t>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2748,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2808,7 +2808,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2872,7 +2872,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2978,7 +2978,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3066,7 +3066,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3200,7 +3200,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3279,7 +3279,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="15" s="78">
       <c r="A15" s="61" t="inlineStr">
         <is>
           <t>粤西区</t>
@@ -3310,7 +3310,7 @@
       <c r="H15" s="23" t="n"/>
       <c r="J15" s="67" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3343,7 +3343,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G17" s="67" t="n"/>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G18" s="67" t="n"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G19" s="67" t="n"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G20" s="67" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G21" s="67" t="n"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="G22" s="67" t="n"/>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G23" s="67" t="n"/>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="G24" s="67" t="n"/>
     </row>
-    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="25" s="78">
       <c r="A25" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3574,7 +3574,7 @@
       <c r="H25" s="67" t="n"/>
       <c r="J25" s="67" t="n"/>
     </row>
-    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="26" s="78">
       <c r="A26" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3605,7 +3605,7 @@
       <c r="H26" s="67" t="n"/>
       <c r="J26" s="67" t="n"/>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G27" s="67" t="n"/>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G28" s="67" t="n"/>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G29" s="67" t="n"/>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D30" s="68" t="inlineStr">
         <is>
-          <t>迟发2次</t>
+          <t>迟发3次</t>
         </is>
       </c>
       <c r="E30" s="69" t="n"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G30" s="67" t="n"/>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G31" s="67" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G32" s="67" t="n"/>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="G33" s="67" t="n"/>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D34" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E34" s="69" t="n"/>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G34" s="67" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G35" s="67" t="n"/>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="G36" s="67" t="n"/>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="G37" s="67" t="n"/>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G38" s="67" t="n"/>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G39" s="67" t="n"/>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G40" s="67" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="G41" s="67" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G42" s="67" t="n"/>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G43" s="67" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G44" s="67" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G45" s="67" t="n"/>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G46" s="67" t="n"/>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G47" s="67" t="n"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="G48" s="67" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="G49" s="67" t="n"/>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G50" s="67" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G51" s="67" t="n"/>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="G52" s="67" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="72" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G53" s="67" t="n"/>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="58" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="G54" s="67" t="n"/>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="58" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="G55" s="67" t="n"/>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G56" s="67" t="n"/>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G57" s="67" t="n"/>
     </row>
-    <row r="58" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="58" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
           <t>华北分公司</t>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="G58" s="67" t="n"/>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="59" s="53">
       <c r="A59" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="G59" s="67" t="n"/>
     </row>
-    <row r="60" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="60" s="53">
       <c r="A60" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G60" s="67" t="n"/>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="61" s="53">
       <c r="A61" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="G61" s="67" t="n"/>
     </row>
-    <row r="62" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="62" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="63" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4596,234 +4596,234 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1" s="53">
-      <c r="A64" t="inlineStr">
+    <row customHeight="1" ht="16" r="64" s="53">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>合肥包河中心</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>累计未发1次</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1" s="53"/>
-    <row r="66" ht="16" customHeight="1" s="53"/>
-    <row r="67" ht="16" customHeight="1" s="53"/>
-    <row r="68" ht="16" customHeight="1" s="53"/>
-    <row r="69" ht="16" customHeight="1" s="53"/>
-    <row r="70" ht="16" customHeight="1" s="53"/>
-    <row r="71" ht="16" customHeight="1" s="53"/>
-    <row r="72" ht="16" customHeight="1" s="53"/>
-    <row r="73" ht="16" customHeight="1" s="53"/>
-    <row r="74" ht="16" customHeight="1" s="53"/>
-    <row r="75" ht="16" customHeight="1" s="53"/>
-    <row r="76" ht="16" customHeight="1" s="53"/>
-    <row r="77" ht="16" customHeight="1" s="53"/>
-    <row r="78" ht="16" customHeight="1" s="53"/>
-    <row r="79" ht="16" customHeight="1" s="53"/>
-    <row r="80" ht="16" customHeight="1" s="53"/>
-    <row r="81" ht="16" customHeight="1" s="53"/>
-    <row r="82" ht="16" customHeight="1" s="53"/>
-    <row r="83" ht="16" customHeight="1" s="53"/>
-    <row r="84" ht="16" customHeight="1" s="53"/>
-    <row r="85" ht="16" customHeight="1" s="53"/>
-    <row r="86" ht="16" customHeight="1" s="53"/>
-    <row r="87" ht="16" customHeight="1" s="53"/>
-    <row r="88" ht="16" customHeight="1" s="53"/>
-    <row r="89" ht="16" customHeight="1" s="53"/>
-    <row r="90" ht="16" customHeight="1" s="53"/>
-    <row r="91" ht="16" customHeight="1" s="53"/>
-    <row r="92" ht="16" customHeight="1" s="53"/>
-    <row r="93" ht="16" customHeight="1" s="53"/>
-    <row r="94" ht="16" customHeight="1" s="53"/>
-    <row r="95" ht="16" customHeight="1" s="53"/>
-    <row r="96" ht="16" customHeight="1" s="53"/>
-    <row r="97" ht="16" customHeight="1" s="53"/>
-    <row r="98" ht="16" customHeight="1" s="53"/>
-    <row r="99" ht="16" customHeight="1" s="53"/>
-    <row r="100" ht="16" customHeight="1" s="53"/>
-    <row r="101" ht="16" customHeight="1" s="53"/>
-    <row r="102" ht="16" customHeight="1" s="53"/>
-    <row r="103" ht="16" customHeight="1" s="53"/>
-    <row r="104" ht="16" customHeight="1" s="53"/>
-    <row r="105" ht="16" customHeight="1" s="53"/>
-    <row r="106" ht="16" customHeight="1" s="53"/>
-    <row r="107" ht="16" customHeight="1" s="53"/>
-    <row r="108" ht="16" customHeight="1" s="53"/>
-    <row r="109" ht="16" customHeight="1" s="53"/>
-    <row r="110" ht="16" customHeight="1" s="53"/>
-    <row r="111" ht="16" customHeight="1" s="53"/>
-    <row r="112" ht="16" customHeight="1" s="53"/>
-    <row r="113" ht="16" customHeight="1" s="53"/>
-    <row r="114" ht="16" customHeight="1" s="53"/>
-    <row r="115" ht="16" customHeight="1" s="53"/>
-    <row r="116" ht="16" customHeight="1" s="53"/>
-    <row r="117" ht="16" customHeight="1" s="53"/>
-    <row r="118" ht="16" customHeight="1" s="53"/>
-    <row r="119" ht="16" customHeight="1" s="53"/>
-    <row r="120" ht="16" customHeight="1" s="53"/>
-    <row r="121" ht="16" customHeight="1" s="53"/>
-    <row r="122" ht="16" customHeight="1" s="53"/>
-    <row r="123" ht="16" customHeight="1" s="53"/>
-    <row r="124" ht="16" customHeight="1" s="53"/>
-    <row r="125" ht="16" customHeight="1" s="53"/>
-    <row r="126" ht="16" customHeight="1" s="53"/>
-    <row r="127" ht="16" customHeight="1" s="53"/>
-    <row r="128" ht="16" customHeight="1" s="53"/>
-    <row r="129" ht="16" customHeight="1" s="53"/>
-    <row r="130" ht="16" customHeight="1" s="53"/>
-    <row r="131" ht="16" customHeight="1" s="53"/>
-    <row r="132" ht="16" customHeight="1" s="53"/>
-    <row r="133" ht="16" customHeight="1" s="53"/>
-    <row r="134" ht="16" customHeight="1" s="53"/>
-    <row r="135" ht="16" customHeight="1" s="53"/>
-    <row r="136" ht="16" customHeight="1" s="53"/>
-    <row r="137" ht="16" customHeight="1" s="53"/>
-    <row r="138" ht="16" customHeight="1" s="53"/>
-    <row r="139" ht="16" customHeight="1" s="53"/>
-    <row r="140" ht="16" customHeight="1" s="53"/>
-    <row r="141" ht="16" customHeight="1" s="53"/>
-    <row r="142" ht="16" customHeight="1" s="53"/>
-    <row r="143" ht="16" customHeight="1" s="53"/>
-    <row r="144" ht="16" customHeight="1" s="53"/>
-    <row r="145" ht="16" customHeight="1" s="53"/>
-    <row r="146" ht="16" customHeight="1" s="53"/>
-    <row r="147" ht="16" customHeight="1" s="53"/>
-    <row r="148" ht="16" customHeight="1" s="53"/>
-    <row r="149" ht="16" customHeight="1" s="53"/>
-    <row r="150" ht="16" customHeight="1" s="53"/>
-    <row r="151" ht="16" customHeight="1" s="53"/>
-    <row r="152" ht="16" customHeight="1" s="53"/>
-    <row r="153" ht="16" customHeight="1" s="53"/>
-    <row r="154" ht="16" customHeight="1" s="53"/>
-    <row r="155" ht="16" customHeight="1" s="53"/>
-    <row r="156" ht="16" customHeight="1" s="53"/>
-    <row r="157" ht="16" customHeight="1" s="53"/>
-    <row r="158" ht="16" customHeight="1" s="53"/>
-    <row r="159" ht="16" customHeight="1" s="53"/>
-    <row r="160" ht="16" customHeight="1" s="53"/>
-    <row r="161" ht="16" customHeight="1" s="53"/>
-    <row r="162" ht="16" customHeight="1" s="53"/>
-    <row r="163" ht="16" customHeight="1" s="53"/>
-    <row r="164" ht="16" customHeight="1" s="53"/>
-    <row r="165" ht="16" customHeight="1" s="53"/>
-    <row r="166" ht="16" customHeight="1" s="53"/>
-    <row r="167" ht="16" customHeight="1" s="53"/>
-    <row r="168" ht="16" customHeight="1" s="53"/>
-    <row r="169" ht="16" customHeight="1" s="53"/>
-    <row r="170" ht="16" customHeight="1" s="53"/>
-    <row r="171" ht="16" customHeight="1" s="53"/>
-    <row r="172" ht="16" customHeight="1" s="53"/>
-    <row r="173" ht="16" customHeight="1" s="53"/>
-    <row r="174" ht="16" customHeight="1" s="53"/>
-    <row r="175" ht="16" customHeight="1" s="53"/>
-    <row r="176" ht="16" customHeight="1" s="53"/>
-    <row r="177" ht="16" customHeight="1" s="53"/>
-    <row r="178" ht="16" customHeight="1" s="53"/>
-    <row r="179" ht="16" customHeight="1" s="53"/>
-    <row r="180" ht="16" customHeight="1" s="53"/>
-    <row r="181" ht="16" customHeight="1" s="53"/>
-    <row r="182" ht="16" customHeight="1" s="53"/>
-    <row r="183" ht="16" customHeight="1" s="53"/>
-    <row r="184" ht="16" customHeight="1" s="53"/>
-    <row r="185" ht="16" customHeight="1" s="53"/>
-    <row r="186" ht="16" customHeight="1" s="53"/>
-    <row r="187" ht="16" customHeight="1" s="53"/>
-    <row r="188" ht="16" customHeight="1" s="53"/>
-    <row r="189" ht="16" customHeight="1" s="53"/>
-    <row r="190" ht="16" customHeight="1" s="53"/>
-    <row r="191" ht="16" customHeight="1" s="53"/>
-    <row r="192" ht="16" customHeight="1" s="53"/>
-    <row r="193" ht="16" customHeight="1" s="53"/>
-    <row r="194" ht="16" customHeight="1" s="53"/>
-    <row r="195" ht="16" customHeight="1" s="53"/>
-    <row r="196" ht="16" customHeight="1" s="53"/>
-    <row r="197" ht="16" customHeight="1" s="53"/>
-    <row r="198" ht="16" customHeight="1" s="53"/>
-    <row r="199" ht="16" customHeight="1" s="53"/>
-    <row r="200" ht="16" customHeight="1" s="53"/>
-    <row r="201" ht="16" customHeight="1" s="53"/>
-    <row r="202" ht="16" customHeight="1" s="53"/>
-    <row r="203" ht="16" customHeight="1" s="53"/>
-    <row r="204" ht="16" customHeight="1" s="53"/>
-    <row r="205" ht="16" customHeight="1" s="53"/>
-    <row r="206" ht="16" customHeight="1" s="53"/>
-    <row r="207" ht="16" customHeight="1" s="53"/>
-    <row r="208" ht="16" customHeight="1" s="53"/>
-    <row r="209" ht="16" customHeight="1" s="53"/>
-    <row r="210" ht="16" customHeight="1" s="53"/>
-    <row r="211" ht="16" customHeight="1" s="53"/>
-    <row r="212" ht="16" customHeight="1" s="53"/>
-    <row r="213" ht="16" customHeight="1" s="53"/>
-    <row r="214" ht="16" customHeight="1" s="53"/>
-    <row r="215" ht="16" customHeight="1" s="53"/>
-    <row r="216" ht="16" customHeight="1" s="53"/>
-    <row r="217" ht="16" customHeight="1" s="53"/>
-    <row r="218" ht="16" customHeight="1" s="53"/>
-    <row r="219" ht="16" customHeight="1" s="53"/>
-    <row r="220" ht="16" customHeight="1" s="53"/>
-    <row r="221" ht="16" customHeight="1" s="53"/>
-    <row r="222" ht="16" customHeight="1" s="53"/>
-    <row r="223" ht="16" customHeight="1" s="53"/>
-    <row r="224" ht="16" customHeight="1" s="53"/>
-    <row r="225" ht="16" customHeight="1" s="53"/>
-    <row r="226" ht="16" customHeight="1" s="53"/>
-    <row r="227" ht="16" customHeight="1" s="53"/>
-    <row r="228" ht="16" customHeight="1" s="53"/>
-    <row r="229" ht="16" customHeight="1" s="53"/>
-    <row r="230" ht="16" customHeight="1" s="53"/>
-    <row r="231" ht="16" customHeight="1" s="53"/>
-    <row r="232" ht="16" customHeight="1" s="53"/>
-    <row r="233" ht="16" customHeight="1" s="53"/>
-    <row r="234" ht="16" customHeight="1" s="53"/>
-    <row r="235" ht="16" customHeight="1" s="53"/>
-    <row r="236" ht="16" customHeight="1" s="53"/>
-    <row r="237" ht="16" customHeight="1" s="53"/>
-    <row r="238" ht="16" customHeight="1" s="53"/>
-    <row r="239" ht="16" customHeight="1" s="53"/>
-    <row r="240" ht="16" customHeight="1" s="53"/>
-    <row r="241" ht="16" customHeight="1" s="53"/>
-    <row r="242" ht="16" customHeight="1" s="53"/>
-    <row r="243" ht="16" customHeight="1" s="53"/>
-    <row r="244" ht="16" customHeight="1" s="53"/>
-    <row r="245" ht="16" customHeight="1" s="53"/>
-    <row r="246" ht="16" customHeight="1" s="53"/>
-    <row r="247" ht="16" customHeight="1" s="53"/>
-    <row r="248" ht="16" customHeight="1" s="53"/>
-    <row r="249" ht="16" customHeight="1" s="53"/>
-    <row r="250" ht="16" customHeight="1" s="53"/>
-    <row r="251" ht="16" customHeight="1" s="53"/>
-    <row r="252" ht="16" customHeight="1" s="53"/>
-    <row r="253" ht="16" customHeight="1" s="53"/>
-    <row r="254" ht="16" customHeight="1" s="53"/>
-    <row r="255" ht="16" customHeight="1" s="53"/>
-    <row r="256" ht="16" customHeight="1" s="53"/>
-    <row r="257" ht="16" customHeight="1" s="53"/>
-    <row r="258" ht="16" customHeight="1" s="53"/>
-    <row r="259" ht="16" customHeight="1" s="53"/>
-    <row r="260" ht="16" customHeight="1" s="53"/>
-    <row r="261" ht="16" customHeight="1" s="53"/>
-    <row r="262" ht="16" customHeight="1" s="53"/>
+    <row customHeight="1" ht="16" r="65" s="53"/>
+    <row customHeight="1" ht="16" r="66" s="53"/>
+    <row customHeight="1" ht="16" r="67" s="53"/>
+    <row customHeight="1" ht="16" r="68" s="53"/>
+    <row customHeight="1" ht="16" r="69" s="53"/>
+    <row customHeight="1" ht="16" r="70" s="53"/>
+    <row customHeight="1" ht="16" r="71" s="53"/>
+    <row customHeight="1" ht="16" r="72" s="53"/>
+    <row customHeight="1" ht="16" r="73" s="53"/>
+    <row customHeight="1" ht="16" r="74" s="53"/>
+    <row customHeight="1" ht="16" r="75" s="53"/>
+    <row customHeight="1" ht="16" r="76" s="53"/>
+    <row customHeight="1" ht="16" r="77" s="53"/>
+    <row customHeight="1" ht="16" r="78" s="53"/>
+    <row customHeight="1" ht="16" r="79" s="53"/>
+    <row customHeight="1" ht="16" r="80" s="53"/>
+    <row customHeight="1" ht="16" r="81" s="53"/>
+    <row customHeight="1" ht="16" r="82" s="53"/>
+    <row customHeight="1" ht="16" r="83" s="53"/>
+    <row customHeight="1" ht="16" r="84" s="53"/>
+    <row customHeight="1" ht="16" r="85" s="53"/>
+    <row customHeight="1" ht="16" r="86" s="53"/>
+    <row customHeight="1" ht="16" r="87" s="53"/>
+    <row customHeight="1" ht="16" r="88" s="53"/>
+    <row customHeight="1" ht="16" r="89" s="53"/>
+    <row customHeight="1" ht="16" r="90" s="53"/>
+    <row customHeight="1" ht="16" r="91" s="53"/>
+    <row customHeight="1" ht="16" r="92" s="53"/>
+    <row customHeight="1" ht="16" r="93" s="53"/>
+    <row customHeight="1" ht="16" r="94" s="53"/>
+    <row customHeight="1" ht="16" r="95" s="53"/>
+    <row customHeight="1" ht="16" r="96" s="53"/>
+    <row customHeight="1" ht="16" r="97" s="53"/>
+    <row customHeight="1" ht="16" r="98" s="53"/>
+    <row customHeight="1" ht="16" r="99" s="53"/>
+    <row customHeight="1" ht="16" r="100" s="53"/>
+    <row customHeight="1" ht="16" r="101" s="53"/>
+    <row customHeight="1" ht="16" r="102" s="53"/>
+    <row customHeight="1" ht="16" r="103" s="53"/>
+    <row customHeight="1" ht="16" r="104" s="53"/>
+    <row customHeight="1" ht="16" r="105" s="53"/>
+    <row customHeight="1" ht="16" r="106" s="53"/>
+    <row customHeight="1" ht="16" r="107" s="53"/>
+    <row customHeight="1" ht="16" r="108" s="53"/>
+    <row customHeight="1" ht="16" r="109" s="53"/>
+    <row customHeight="1" ht="16" r="110" s="53"/>
+    <row customHeight="1" ht="16" r="111" s="53"/>
+    <row customHeight="1" ht="16" r="112" s="53"/>
+    <row customHeight="1" ht="16" r="113" s="53"/>
+    <row customHeight="1" ht="16" r="114" s="53"/>
+    <row customHeight="1" ht="16" r="115" s="53"/>
+    <row customHeight="1" ht="16" r="116" s="53"/>
+    <row customHeight="1" ht="16" r="117" s="53"/>
+    <row customHeight="1" ht="16" r="118" s="53"/>
+    <row customHeight="1" ht="16" r="119" s="53"/>
+    <row customHeight="1" ht="16" r="120" s="53"/>
+    <row customHeight="1" ht="16" r="121" s="53"/>
+    <row customHeight="1" ht="16" r="122" s="53"/>
+    <row customHeight="1" ht="16" r="123" s="53"/>
+    <row customHeight="1" ht="16" r="124" s="53"/>
+    <row customHeight="1" ht="16" r="125" s="53"/>
+    <row customHeight="1" ht="16" r="126" s="53"/>
+    <row customHeight="1" ht="16" r="127" s="53"/>
+    <row customHeight="1" ht="16" r="128" s="53"/>
+    <row customHeight="1" ht="16" r="129" s="53"/>
+    <row customHeight="1" ht="16" r="130" s="53"/>
+    <row customHeight="1" ht="16" r="131" s="53"/>
+    <row customHeight="1" ht="16" r="132" s="53"/>
+    <row customHeight="1" ht="16" r="133" s="53"/>
+    <row customHeight="1" ht="16" r="134" s="53"/>
+    <row customHeight="1" ht="16" r="135" s="53"/>
+    <row customHeight="1" ht="16" r="136" s="53"/>
+    <row customHeight="1" ht="16" r="137" s="53"/>
+    <row customHeight="1" ht="16" r="138" s="53"/>
+    <row customHeight="1" ht="16" r="139" s="53"/>
+    <row customHeight="1" ht="16" r="140" s="53"/>
+    <row customHeight="1" ht="16" r="141" s="53"/>
+    <row customHeight="1" ht="16" r="142" s="53"/>
+    <row customHeight="1" ht="16" r="143" s="53"/>
+    <row customHeight="1" ht="16" r="144" s="53"/>
+    <row customHeight="1" ht="16" r="145" s="53"/>
+    <row customHeight="1" ht="16" r="146" s="53"/>
+    <row customHeight="1" ht="16" r="147" s="53"/>
+    <row customHeight="1" ht="16" r="148" s="53"/>
+    <row customHeight="1" ht="16" r="149" s="53"/>
+    <row customHeight="1" ht="16" r="150" s="53"/>
+    <row customHeight="1" ht="16" r="151" s="53"/>
+    <row customHeight="1" ht="16" r="152" s="53"/>
+    <row customHeight="1" ht="16" r="153" s="53"/>
+    <row customHeight="1" ht="16" r="154" s="53"/>
+    <row customHeight="1" ht="16" r="155" s="53"/>
+    <row customHeight="1" ht="16" r="156" s="53"/>
+    <row customHeight="1" ht="16" r="157" s="53"/>
+    <row customHeight="1" ht="16" r="158" s="53"/>
+    <row customHeight="1" ht="16" r="159" s="53"/>
+    <row customHeight="1" ht="16" r="160" s="53"/>
+    <row customHeight="1" ht="16" r="161" s="53"/>
+    <row customHeight="1" ht="16" r="162" s="53"/>
+    <row customHeight="1" ht="16" r="163" s="53"/>
+    <row customHeight="1" ht="16" r="164" s="53"/>
+    <row customHeight="1" ht="16" r="165" s="53"/>
+    <row customHeight="1" ht="16" r="166" s="53"/>
+    <row customHeight="1" ht="16" r="167" s="53"/>
+    <row customHeight="1" ht="16" r="168" s="53"/>
+    <row customHeight="1" ht="16" r="169" s="53"/>
+    <row customHeight="1" ht="16" r="170" s="53"/>
+    <row customHeight="1" ht="16" r="171" s="53"/>
+    <row customHeight="1" ht="16" r="172" s="53"/>
+    <row customHeight="1" ht="16" r="173" s="53"/>
+    <row customHeight="1" ht="16" r="174" s="53"/>
+    <row customHeight="1" ht="16" r="175" s="53"/>
+    <row customHeight="1" ht="16" r="176" s="53"/>
+    <row customHeight="1" ht="16" r="177" s="53"/>
+    <row customHeight="1" ht="16" r="178" s="53"/>
+    <row customHeight="1" ht="16" r="179" s="53"/>
+    <row customHeight="1" ht="16" r="180" s="53"/>
+    <row customHeight="1" ht="16" r="181" s="53"/>
+    <row customHeight="1" ht="16" r="182" s="53"/>
+    <row customHeight="1" ht="16" r="183" s="53"/>
+    <row customHeight="1" ht="16" r="184" s="53"/>
+    <row customHeight="1" ht="16" r="185" s="53"/>
+    <row customHeight="1" ht="16" r="186" s="53"/>
+    <row customHeight="1" ht="16" r="187" s="53"/>
+    <row customHeight="1" ht="16" r="188" s="53"/>
+    <row customHeight="1" ht="16" r="189" s="53"/>
+    <row customHeight="1" ht="16" r="190" s="53"/>
+    <row customHeight="1" ht="16" r="191" s="53"/>
+    <row customHeight="1" ht="16" r="192" s="53"/>
+    <row customHeight="1" ht="16" r="193" s="53"/>
+    <row customHeight="1" ht="16" r="194" s="53"/>
+    <row customHeight="1" ht="16" r="195" s="53"/>
+    <row customHeight="1" ht="16" r="196" s="53"/>
+    <row customHeight="1" ht="16" r="197" s="53"/>
+    <row customHeight="1" ht="16" r="198" s="53"/>
+    <row customHeight="1" ht="16" r="199" s="53"/>
+    <row customHeight="1" ht="16" r="200" s="53"/>
+    <row customHeight="1" ht="16" r="201" s="53"/>
+    <row customHeight="1" ht="16" r="202" s="53"/>
+    <row customHeight="1" ht="16" r="203" s="53"/>
+    <row customHeight="1" ht="16" r="204" s="53"/>
+    <row customHeight="1" ht="16" r="205" s="53"/>
+    <row customHeight="1" ht="16" r="206" s="53"/>
+    <row customHeight="1" ht="16" r="207" s="53"/>
+    <row customHeight="1" ht="16" r="208" s="53"/>
+    <row customHeight="1" ht="16" r="209" s="53"/>
+    <row customHeight="1" ht="16" r="210" s="53"/>
+    <row customHeight="1" ht="16" r="211" s="53"/>
+    <row customHeight="1" ht="16" r="212" s="53"/>
+    <row customHeight="1" ht="16" r="213" s="53"/>
+    <row customHeight="1" ht="16" r="214" s="53"/>
+    <row customHeight="1" ht="16" r="215" s="53"/>
+    <row customHeight="1" ht="16" r="216" s="53"/>
+    <row customHeight="1" ht="16" r="217" s="53"/>
+    <row customHeight="1" ht="16" r="218" s="53"/>
+    <row customHeight="1" ht="16" r="219" s="53"/>
+    <row customHeight="1" ht="16" r="220" s="53"/>
+    <row customHeight="1" ht="16" r="221" s="53"/>
+    <row customHeight="1" ht="16" r="222" s="53"/>
+    <row customHeight="1" ht="16" r="223" s="53"/>
+    <row customHeight="1" ht="16" r="224" s="53"/>
+    <row customHeight="1" ht="16" r="225" s="53"/>
+    <row customHeight="1" ht="16" r="226" s="53"/>
+    <row customHeight="1" ht="16" r="227" s="53"/>
+    <row customHeight="1" ht="16" r="228" s="53"/>
+    <row customHeight="1" ht="16" r="229" s="53"/>
+    <row customHeight="1" ht="16" r="230" s="53"/>
+    <row customHeight="1" ht="16" r="231" s="53"/>
+    <row customHeight="1" ht="16" r="232" s="53"/>
+    <row customHeight="1" ht="16" r="233" s="53"/>
+    <row customHeight="1" ht="16" r="234" s="53"/>
+    <row customHeight="1" ht="16" r="235" s="53"/>
+    <row customHeight="1" ht="16" r="236" s="53"/>
+    <row customHeight="1" ht="16" r="237" s="53"/>
+    <row customHeight="1" ht="16" r="238" s="53"/>
+    <row customHeight="1" ht="16" r="239" s="53"/>
+    <row customHeight="1" ht="16" r="240" s="53"/>
+    <row customHeight="1" ht="16" r="241" s="53"/>
+    <row customHeight="1" ht="16" r="242" s="53"/>
+    <row customHeight="1" ht="16" r="243" s="53"/>
+    <row customHeight="1" ht="16" r="244" s="53"/>
+    <row customHeight="1" ht="16" r="245" s="53"/>
+    <row customHeight="1" ht="16" r="246" s="53"/>
+    <row customHeight="1" ht="16" r="247" s="53"/>
+    <row customHeight="1" ht="16" r="248" s="53"/>
+    <row customHeight="1" ht="16" r="249" s="53"/>
+    <row customHeight="1" ht="16" r="250" s="53"/>
+    <row customHeight="1" ht="16" r="251" s="53"/>
+    <row customHeight="1" ht="16" r="252" s="53"/>
+    <row customHeight="1" ht="16" r="253" s="53"/>
+    <row customHeight="1" ht="16" r="254" s="53"/>
+    <row customHeight="1" ht="16" r="255" s="53"/>
+    <row customHeight="1" ht="16" r="256" s="53"/>
+    <row customHeight="1" ht="16" r="257" s="53"/>
+    <row customHeight="1" ht="16" r="258" s="53"/>
+    <row customHeight="1" ht="16" r="259" s="53"/>
+    <row customHeight="1" ht="16" r="260" s="53"/>
+    <row customHeight="1" ht="16" r="261" s="53"/>
+    <row customHeight="1" ht="16" r="262" s="53"/>
   </sheetData>
   <autoFilter ref="A2:F61"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -4836,17 +4836,17 @@
   <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -4869,7 +4869,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>区域</t>
@@ -4955,7 +4955,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4998,7 +4998,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5125,7 +5125,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5164,7 +5164,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5230,7 +5230,7 @@
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5269,7 +5269,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5306,7 +5306,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5343,7 +5343,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5382,7 +5382,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5419,7 +5419,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5446,7 +5446,7 @@
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5474,7 +5474,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5502,7 +5502,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5560,7 +5560,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5590,7 +5590,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5654,7 +5654,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5684,7 +5684,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5722,7 +5722,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5752,7 +5752,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5784,7 +5784,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5818,7 +5818,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5878,7 +5878,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5914,7 +5914,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5941,7 +5941,7 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5973,7 +5973,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6005,7 +6005,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6030,7 +6030,7 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6060,7 +6060,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6090,7 +6090,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6124,7 +6124,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6154,7 +6154,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6182,7 +6182,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6210,7 +6210,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6238,7 +6238,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6266,7 +6266,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6294,7 +6294,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6350,7 +6350,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6378,7 +6378,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6416,7 +6416,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6446,7 +6446,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6482,7 +6482,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6516,7 +6516,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6552,7 +6552,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6584,7 +6584,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -7232,7 +7232,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -7245,17 +7245,17 @@
   <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -7278,7 +7278,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>区域</t>
@@ -7364,7 +7364,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7410,7 +7410,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7447,7 +7447,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7493,7 +7493,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7539,7 +7539,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7587,7 +7587,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7624,7 +7624,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7709,7 +7709,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7755,7 +7755,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7792,7 +7792,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7829,7 +7829,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7875,7 +7875,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7903,7 +7903,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7931,7 +7931,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7959,7 +7959,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7987,7 +7987,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8015,7 +8015,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8043,7 +8043,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8071,7 +8071,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8099,7 +8099,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8127,7 +8127,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8155,7 +8155,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8183,7 +8183,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8211,7 +8211,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8239,7 +8239,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8269,7 +8269,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8297,7 +8297,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8325,7 +8325,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8353,7 +8353,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8381,7 +8381,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8409,7 +8409,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8437,7 +8437,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8467,7 +8467,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8495,7 +8495,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8523,7 +8523,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8551,7 +8551,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8579,7 +8579,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8609,7 +8609,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8641,7 +8641,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8669,7 +8669,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8697,7 +8697,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8725,7 +8725,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8753,7 +8753,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8781,7 +8781,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8813,7 +8813,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8845,7 +8845,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -9521,7 +9521,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -9532,16 +9532,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -9551,7 +9551,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -9596,7 +9596,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9642,7 +9642,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9687,7 +9687,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9736,7 +9736,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9785,7 +9785,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9827,7 +9827,7 @@
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="35" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9902,7 +9902,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9938,7 +9938,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -9974,7 +9974,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10010,7 +10010,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10051,7 +10051,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10082,7 +10082,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10160,7 +10160,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D20" s="39" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D25" s="36" t="n"/>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10323,7 +10323,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10389,7 +10389,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10460,7 +10460,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D41" s="46" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="D43" s="46" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="E44" s="46" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10729,7 +10729,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E50" s="49" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="37" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="55" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="55" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10990,7 +10990,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -11001,18 +11001,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6.83203125" customWidth="1" style="23" min="1" max="1"/>
-    <col width="8.83203125" customWidth="1" style="23" min="2" max="2"/>
-    <col width="19.6640625" customWidth="1" style="23" min="3" max="3"/>
-    <col width="13" customWidth="1" style="23" min="4" max="4"/>
-    <col hidden="1" width="30.5" customWidth="1" style="23" min="5" max="6"/>
-    <col width="30.5" customWidth="1" style="23" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" style="23" min="8" max="26"/>
+    <col customWidth="1" max="1" min="1" style="23" width="6.83203125"/>
+    <col customWidth="1" max="2" min="2" style="23" width="8.83203125"/>
+    <col customWidth="1" max="3" min="3" style="23" width="19.6640625"/>
+    <col customWidth="1" max="4" min="4" style="23" width="13"/>
+    <col customWidth="1" hidden="1" max="6" min="5" style="23" width="30.5"/>
+    <col customWidth="1" max="7" min="7" style="23" width="30.5"/>
+    <col customWidth="1" max="26" min="8" style="23" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="1" s="53">
       <c r="A1" s="21" t="n"/>
       <c r="B1" s="22" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="2" s="53">
       <c r="A2" s="24" t="n">
         <v>1</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="3" s="53">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="4" s="53">
       <c r="A4" s="24" t="n">
         <v>3</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="5" s="53">
       <c r="A5" s="24" t="n">
         <v>4</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="6" s="53">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="7" s="53">
       <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
@@ -11273,7 +11273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="8" s="53">
       <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="9" s="53">
       <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="10" s="53">
       <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="11" s="53">
       <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="12" s="53">
       <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
@@ -11408,7 +11408,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="13" s="53">
       <c r="A13" s="24" t="n">
         <v>4</v>
       </c>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="14" s="53">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
@@ -11458,7 +11458,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="15" s="53">
       <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="16" s="53">
       <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="17" s="53">
       <c r="A17" s="24" t="n">
         <v>2</v>
       </c>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="18" s="53">
       <c r="A18" s="24" t="n">
         <v>3</v>
       </c>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="19" s="53">
       <c r="A19" s="24" t="n">
         <v>4</v>
       </c>
@@ -11608,7 +11608,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="20" s="53">
       <c r="A20" s="24" t="n">
         <v>5</v>
       </c>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="21" s="53">
       <c r="A21" s="24" t="n">
         <v>6</v>
       </c>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="22" s="53">
       <c r="A22" s="24" t="n">
         <v>7</v>
       </c>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="23" s="53">
       <c r="A23" s="24" t="n">
         <v>8</v>
       </c>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="24" s="53">
       <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
@@ -11758,7 +11758,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="25" s="53">
       <c r="A25" s="24" t="n">
         <v>2</v>
       </c>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="26" s="53">
       <c r="A26" s="24" t="n">
         <v>3</v>
       </c>
@@ -11813,7 +11813,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="27" s="53">
       <c r="A27" s="24" t="n">
         <v>4</v>
       </c>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="28" s="53">
       <c r="A28" s="24" t="n">
         <v>5</v>
       </c>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="29" s="53">
       <c r="A29" s="24" t="n">
         <v>6</v>
       </c>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="30" s="53">
       <c r="A30" s="24" t="n">
         <v>7</v>
       </c>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="31" s="53">
       <c r="A31" s="24" t="n">
         <v>8</v>
       </c>
@@ -11968,7 +11968,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="32" s="53">
       <c r="A32" s="24" t="n">
         <v>1</v>
       </c>
@@ -11998,7 +11998,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="33" s="53">
       <c r="A33" s="24" t="n">
         <v>2</v>
       </c>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="34" s="53">
       <c r="A34" s="24" t="n">
         <v>3</v>
       </c>
@@ -12058,7 +12058,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="35" s="53">
       <c r="A35" s="24" t="n">
         <v>4</v>
       </c>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="36" s="53">
       <c r="A36" s="24" t="n">
         <v>1</v>
       </c>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="37" s="53">
       <c r="A37" s="24" t="n">
         <v>2</v>
       </c>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="38" s="53">
       <c r="A38" s="24" t="n">
         <v>3</v>
       </c>
@@ -12184,6 +12184,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D5" s="68" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E5" s="69" t="n"/>
@@ -3945,7 +3945,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D39" s="70" t="n"/>
+      <c r="D39" s="70" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E39" s="69" t="n"/>
       <c r="F39" s="63" t="inlineStr">
         <is>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="D43" s="68" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>迟发2次</t>
         </is>
       </c>
       <c r="E43" s="69" t="n"/>
@@ -4429,7 +4433,7 @@
       </c>
       <c r="D57" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E57" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16400" windowWidth="27040" xWindow="0" yWindow="500"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'2026年日报'!$A$2:$F$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,257 +449,257 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf applyAlignment="1" borderId="7" fillId="7" fontId="0" numFmtId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="83">
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="5" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="9" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="10" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="11" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="12" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="16" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="17" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="17" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="14" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="9" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="19" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="19" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="常规" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1073,16 +1073,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1472,7 +1472,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1642,7 +1642,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D40" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D48" s="51" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="53" s="53">
+    <row r="53" ht="16.5" customHeight="1" s="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2619,16 +2619,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O64"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -2638,7 +2638,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>区域</t>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2748,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2808,7 +2808,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2872,7 +2872,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2978,7 +2978,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3066,7 +3066,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3200,7 +3200,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3279,7 +3279,7 @@
         <v/>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="15" s="78">
+    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A15" s="61" t="inlineStr">
         <is>
           <t>粤西区</t>
@@ -3310,7 +3310,7 @@
       <c r="H15" s="23" t="n"/>
       <c r="J15" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3343,7 +3343,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G17" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G18" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G19" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G20" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G21" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="G22" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G23" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="G24" s="67" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="25" s="78">
+    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A25" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3574,7 +3574,7 @@
       <c r="H25" s="67" t="n"/>
       <c r="J25" s="67" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="26" s="78">
+    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A26" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3605,7 +3605,7 @@
       <c r="H26" s="67" t="n"/>
       <c r="J26" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G27" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G28" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G29" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G30" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G31" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G32" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="G33" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G34" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G35" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="G36" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="G37" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G38" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G39" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G40" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G41" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="G42" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="G43" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G44" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G45" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G46" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G47" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G48" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G49" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G50" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="G51" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G52" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16" r="53" s="53">
+    <row r="53" ht="16" customHeight="1" s="53">
       <c r="A53" s="72" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G53" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="58" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="G54" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="55" s="53">
+    <row r="55" ht="16.5" customHeight="1" s="53">
       <c r="A55" s="58" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G55" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="56" s="53">
+    <row r="56" ht="16.5" customHeight="1" s="53">
       <c r="A56" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G56" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="57" s="53">
+    <row r="57" ht="16.5" customHeight="1" s="53">
       <c r="A57" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D57" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E57" s="69" t="n"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G57" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="58" s="53">
+    <row r="58" ht="16.5" customHeight="1" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
           <t>华北分公司</t>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="G58" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="59" s="53">
+    <row r="59" ht="16.5" customHeight="1" s="53">
       <c r="A59" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G59" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="60" s="53">
+    <row r="60" ht="16.5" customHeight="1" s="53">
       <c r="A60" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="G60" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="61" s="53">
+    <row r="61" ht="16.5" customHeight="1" s="53">
       <c r="A61" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="G61" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16" r="62" s="53">
+    <row r="62" ht="16" customHeight="1" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="63" s="53">
+    <row r="63" ht="16" customHeight="1" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="64" s="53">
+    <row r="64" ht="16" customHeight="1" s="53">
       <c r="A64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4627,207 +4627,207 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="65" s="53"/>
-    <row customHeight="1" ht="16" r="66" s="53"/>
-    <row customHeight="1" ht="16" r="67" s="53"/>
-    <row customHeight="1" ht="16" r="68" s="53"/>
-    <row customHeight="1" ht="16" r="69" s="53"/>
-    <row customHeight="1" ht="16" r="70" s="53"/>
-    <row customHeight="1" ht="16" r="71" s="53"/>
-    <row customHeight="1" ht="16" r="72" s="53"/>
-    <row customHeight="1" ht="16" r="73" s="53"/>
-    <row customHeight="1" ht="16" r="74" s="53"/>
-    <row customHeight="1" ht="16" r="75" s="53"/>
-    <row customHeight="1" ht="16" r="76" s="53"/>
-    <row customHeight="1" ht="16" r="77" s="53"/>
-    <row customHeight="1" ht="16" r="78" s="53"/>
-    <row customHeight="1" ht="16" r="79" s="53"/>
-    <row customHeight="1" ht="16" r="80" s="53"/>
-    <row customHeight="1" ht="16" r="81" s="53"/>
-    <row customHeight="1" ht="16" r="82" s="53"/>
-    <row customHeight="1" ht="16" r="83" s="53"/>
-    <row customHeight="1" ht="16" r="84" s="53"/>
-    <row customHeight="1" ht="16" r="85" s="53"/>
-    <row customHeight="1" ht="16" r="86" s="53"/>
-    <row customHeight="1" ht="16" r="87" s="53"/>
-    <row customHeight="1" ht="16" r="88" s="53"/>
-    <row customHeight="1" ht="16" r="89" s="53"/>
-    <row customHeight="1" ht="16" r="90" s="53"/>
-    <row customHeight="1" ht="16" r="91" s="53"/>
-    <row customHeight="1" ht="16" r="92" s="53"/>
-    <row customHeight="1" ht="16" r="93" s="53"/>
-    <row customHeight="1" ht="16" r="94" s="53"/>
-    <row customHeight="1" ht="16" r="95" s="53"/>
-    <row customHeight="1" ht="16" r="96" s="53"/>
-    <row customHeight="1" ht="16" r="97" s="53"/>
-    <row customHeight="1" ht="16" r="98" s="53"/>
-    <row customHeight="1" ht="16" r="99" s="53"/>
-    <row customHeight="1" ht="16" r="100" s="53"/>
-    <row customHeight="1" ht="16" r="101" s="53"/>
-    <row customHeight="1" ht="16" r="102" s="53"/>
-    <row customHeight="1" ht="16" r="103" s="53"/>
-    <row customHeight="1" ht="16" r="104" s="53"/>
-    <row customHeight="1" ht="16" r="105" s="53"/>
-    <row customHeight="1" ht="16" r="106" s="53"/>
-    <row customHeight="1" ht="16" r="107" s="53"/>
-    <row customHeight="1" ht="16" r="108" s="53"/>
-    <row customHeight="1" ht="16" r="109" s="53"/>
-    <row customHeight="1" ht="16" r="110" s="53"/>
-    <row customHeight="1" ht="16" r="111" s="53"/>
-    <row customHeight="1" ht="16" r="112" s="53"/>
-    <row customHeight="1" ht="16" r="113" s="53"/>
-    <row customHeight="1" ht="16" r="114" s="53"/>
-    <row customHeight="1" ht="16" r="115" s="53"/>
-    <row customHeight="1" ht="16" r="116" s="53"/>
-    <row customHeight="1" ht="16" r="117" s="53"/>
-    <row customHeight="1" ht="16" r="118" s="53"/>
-    <row customHeight="1" ht="16" r="119" s="53"/>
-    <row customHeight="1" ht="16" r="120" s="53"/>
-    <row customHeight="1" ht="16" r="121" s="53"/>
-    <row customHeight="1" ht="16" r="122" s="53"/>
-    <row customHeight="1" ht="16" r="123" s="53"/>
-    <row customHeight="1" ht="16" r="124" s="53"/>
-    <row customHeight="1" ht="16" r="125" s="53"/>
-    <row customHeight="1" ht="16" r="126" s="53"/>
-    <row customHeight="1" ht="16" r="127" s="53"/>
-    <row customHeight="1" ht="16" r="128" s="53"/>
-    <row customHeight="1" ht="16" r="129" s="53"/>
-    <row customHeight="1" ht="16" r="130" s="53"/>
-    <row customHeight="1" ht="16" r="131" s="53"/>
-    <row customHeight="1" ht="16" r="132" s="53"/>
-    <row customHeight="1" ht="16" r="133" s="53"/>
-    <row customHeight="1" ht="16" r="134" s="53"/>
-    <row customHeight="1" ht="16" r="135" s="53"/>
-    <row customHeight="1" ht="16" r="136" s="53"/>
-    <row customHeight="1" ht="16" r="137" s="53"/>
-    <row customHeight="1" ht="16" r="138" s="53"/>
-    <row customHeight="1" ht="16" r="139" s="53"/>
-    <row customHeight="1" ht="16" r="140" s="53"/>
-    <row customHeight="1" ht="16" r="141" s="53"/>
-    <row customHeight="1" ht="16" r="142" s="53"/>
-    <row customHeight="1" ht="16" r="143" s="53"/>
-    <row customHeight="1" ht="16" r="144" s="53"/>
-    <row customHeight="1" ht="16" r="145" s="53"/>
-    <row customHeight="1" ht="16" r="146" s="53"/>
-    <row customHeight="1" ht="16" r="147" s="53"/>
-    <row customHeight="1" ht="16" r="148" s="53"/>
-    <row customHeight="1" ht="16" r="149" s="53"/>
-    <row customHeight="1" ht="16" r="150" s="53"/>
-    <row customHeight="1" ht="16" r="151" s="53"/>
-    <row customHeight="1" ht="16" r="152" s="53"/>
-    <row customHeight="1" ht="16" r="153" s="53"/>
-    <row customHeight="1" ht="16" r="154" s="53"/>
-    <row customHeight="1" ht="16" r="155" s="53"/>
-    <row customHeight="1" ht="16" r="156" s="53"/>
-    <row customHeight="1" ht="16" r="157" s="53"/>
-    <row customHeight="1" ht="16" r="158" s="53"/>
-    <row customHeight="1" ht="16" r="159" s="53"/>
-    <row customHeight="1" ht="16" r="160" s="53"/>
-    <row customHeight="1" ht="16" r="161" s="53"/>
-    <row customHeight="1" ht="16" r="162" s="53"/>
-    <row customHeight="1" ht="16" r="163" s="53"/>
-    <row customHeight="1" ht="16" r="164" s="53"/>
-    <row customHeight="1" ht="16" r="165" s="53"/>
-    <row customHeight="1" ht="16" r="166" s="53"/>
-    <row customHeight="1" ht="16" r="167" s="53"/>
-    <row customHeight="1" ht="16" r="168" s="53"/>
-    <row customHeight="1" ht="16" r="169" s="53"/>
-    <row customHeight="1" ht="16" r="170" s="53"/>
-    <row customHeight="1" ht="16" r="171" s="53"/>
-    <row customHeight="1" ht="16" r="172" s="53"/>
-    <row customHeight="1" ht="16" r="173" s="53"/>
-    <row customHeight="1" ht="16" r="174" s="53"/>
-    <row customHeight="1" ht="16" r="175" s="53"/>
-    <row customHeight="1" ht="16" r="176" s="53"/>
-    <row customHeight="1" ht="16" r="177" s="53"/>
-    <row customHeight="1" ht="16" r="178" s="53"/>
-    <row customHeight="1" ht="16" r="179" s="53"/>
-    <row customHeight="1" ht="16" r="180" s="53"/>
-    <row customHeight="1" ht="16" r="181" s="53"/>
-    <row customHeight="1" ht="16" r="182" s="53"/>
-    <row customHeight="1" ht="16" r="183" s="53"/>
-    <row customHeight="1" ht="16" r="184" s="53"/>
-    <row customHeight="1" ht="16" r="185" s="53"/>
-    <row customHeight="1" ht="16" r="186" s="53"/>
-    <row customHeight="1" ht="16" r="187" s="53"/>
-    <row customHeight="1" ht="16" r="188" s="53"/>
-    <row customHeight="1" ht="16" r="189" s="53"/>
-    <row customHeight="1" ht="16" r="190" s="53"/>
-    <row customHeight="1" ht="16" r="191" s="53"/>
-    <row customHeight="1" ht="16" r="192" s="53"/>
-    <row customHeight="1" ht="16" r="193" s="53"/>
-    <row customHeight="1" ht="16" r="194" s="53"/>
-    <row customHeight="1" ht="16" r="195" s="53"/>
-    <row customHeight="1" ht="16" r="196" s="53"/>
-    <row customHeight="1" ht="16" r="197" s="53"/>
-    <row customHeight="1" ht="16" r="198" s="53"/>
-    <row customHeight="1" ht="16" r="199" s="53"/>
-    <row customHeight="1" ht="16" r="200" s="53"/>
-    <row customHeight="1" ht="16" r="201" s="53"/>
-    <row customHeight="1" ht="16" r="202" s="53"/>
-    <row customHeight="1" ht="16" r="203" s="53"/>
-    <row customHeight="1" ht="16" r="204" s="53"/>
-    <row customHeight="1" ht="16" r="205" s="53"/>
-    <row customHeight="1" ht="16" r="206" s="53"/>
-    <row customHeight="1" ht="16" r="207" s="53"/>
-    <row customHeight="1" ht="16" r="208" s="53"/>
-    <row customHeight="1" ht="16" r="209" s="53"/>
-    <row customHeight="1" ht="16" r="210" s="53"/>
-    <row customHeight="1" ht="16" r="211" s="53"/>
-    <row customHeight="1" ht="16" r="212" s="53"/>
-    <row customHeight="1" ht="16" r="213" s="53"/>
-    <row customHeight="1" ht="16" r="214" s="53"/>
-    <row customHeight="1" ht="16" r="215" s="53"/>
-    <row customHeight="1" ht="16" r="216" s="53"/>
-    <row customHeight="1" ht="16" r="217" s="53"/>
-    <row customHeight="1" ht="16" r="218" s="53"/>
-    <row customHeight="1" ht="16" r="219" s="53"/>
-    <row customHeight="1" ht="16" r="220" s="53"/>
-    <row customHeight="1" ht="16" r="221" s="53"/>
-    <row customHeight="1" ht="16" r="222" s="53"/>
-    <row customHeight="1" ht="16" r="223" s="53"/>
-    <row customHeight="1" ht="16" r="224" s="53"/>
-    <row customHeight="1" ht="16" r="225" s="53"/>
-    <row customHeight="1" ht="16" r="226" s="53"/>
-    <row customHeight="1" ht="16" r="227" s="53"/>
-    <row customHeight="1" ht="16" r="228" s="53"/>
-    <row customHeight="1" ht="16" r="229" s="53"/>
-    <row customHeight="1" ht="16" r="230" s="53"/>
-    <row customHeight="1" ht="16" r="231" s="53"/>
-    <row customHeight="1" ht="16" r="232" s="53"/>
-    <row customHeight="1" ht="16" r="233" s="53"/>
-    <row customHeight="1" ht="16" r="234" s="53"/>
-    <row customHeight="1" ht="16" r="235" s="53"/>
-    <row customHeight="1" ht="16" r="236" s="53"/>
-    <row customHeight="1" ht="16" r="237" s="53"/>
-    <row customHeight="1" ht="16" r="238" s="53"/>
-    <row customHeight="1" ht="16" r="239" s="53"/>
-    <row customHeight="1" ht="16" r="240" s="53"/>
-    <row customHeight="1" ht="16" r="241" s="53"/>
-    <row customHeight="1" ht="16" r="242" s="53"/>
-    <row customHeight="1" ht="16" r="243" s="53"/>
-    <row customHeight="1" ht="16" r="244" s="53"/>
-    <row customHeight="1" ht="16" r="245" s="53"/>
-    <row customHeight="1" ht="16" r="246" s="53"/>
-    <row customHeight="1" ht="16" r="247" s="53"/>
-    <row customHeight="1" ht="16" r="248" s="53"/>
-    <row customHeight="1" ht="16" r="249" s="53"/>
-    <row customHeight="1" ht="16" r="250" s="53"/>
-    <row customHeight="1" ht="16" r="251" s="53"/>
-    <row customHeight="1" ht="16" r="252" s="53"/>
-    <row customHeight="1" ht="16" r="253" s="53"/>
-    <row customHeight="1" ht="16" r="254" s="53"/>
-    <row customHeight="1" ht="16" r="255" s="53"/>
-    <row customHeight="1" ht="16" r="256" s="53"/>
-    <row customHeight="1" ht="16" r="257" s="53"/>
-    <row customHeight="1" ht="16" r="258" s="53"/>
-    <row customHeight="1" ht="16" r="259" s="53"/>
-    <row customHeight="1" ht="16" r="260" s="53"/>
-    <row customHeight="1" ht="16" r="261" s="53"/>
-    <row customHeight="1" ht="16" r="262" s="53"/>
+    <row r="65" ht="16" customHeight="1" s="53"/>
+    <row r="66" ht="16" customHeight="1" s="53"/>
+    <row r="67" ht="16" customHeight="1" s="53"/>
+    <row r="68" ht="16" customHeight="1" s="53"/>
+    <row r="69" ht="16" customHeight="1" s="53"/>
+    <row r="70" ht="16" customHeight="1" s="53"/>
+    <row r="71" ht="16" customHeight="1" s="53"/>
+    <row r="72" ht="16" customHeight="1" s="53"/>
+    <row r="73" ht="16" customHeight="1" s="53"/>
+    <row r="74" ht="16" customHeight="1" s="53"/>
+    <row r="75" ht="16" customHeight="1" s="53"/>
+    <row r="76" ht="16" customHeight="1" s="53"/>
+    <row r="77" ht="16" customHeight="1" s="53"/>
+    <row r="78" ht="16" customHeight="1" s="53"/>
+    <row r="79" ht="16" customHeight="1" s="53"/>
+    <row r="80" ht="16" customHeight="1" s="53"/>
+    <row r="81" ht="16" customHeight="1" s="53"/>
+    <row r="82" ht="16" customHeight="1" s="53"/>
+    <row r="83" ht="16" customHeight="1" s="53"/>
+    <row r="84" ht="16" customHeight="1" s="53"/>
+    <row r="85" ht="16" customHeight="1" s="53"/>
+    <row r="86" ht="16" customHeight="1" s="53"/>
+    <row r="87" ht="16" customHeight="1" s="53"/>
+    <row r="88" ht="16" customHeight="1" s="53"/>
+    <row r="89" ht="16" customHeight="1" s="53"/>
+    <row r="90" ht="16" customHeight="1" s="53"/>
+    <row r="91" ht="16" customHeight="1" s="53"/>
+    <row r="92" ht="16" customHeight="1" s="53"/>
+    <row r="93" ht="16" customHeight="1" s="53"/>
+    <row r="94" ht="16" customHeight="1" s="53"/>
+    <row r="95" ht="16" customHeight="1" s="53"/>
+    <row r="96" ht="16" customHeight="1" s="53"/>
+    <row r="97" ht="16" customHeight="1" s="53"/>
+    <row r="98" ht="16" customHeight="1" s="53"/>
+    <row r="99" ht="16" customHeight="1" s="53"/>
+    <row r="100" ht="16" customHeight="1" s="53"/>
+    <row r="101" ht="16" customHeight="1" s="53"/>
+    <row r="102" ht="16" customHeight="1" s="53"/>
+    <row r="103" ht="16" customHeight="1" s="53"/>
+    <row r="104" ht="16" customHeight="1" s="53"/>
+    <row r="105" ht="16" customHeight="1" s="53"/>
+    <row r="106" ht="16" customHeight="1" s="53"/>
+    <row r="107" ht="16" customHeight="1" s="53"/>
+    <row r="108" ht="16" customHeight="1" s="53"/>
+    <row r="109" ht="16" customHeight="1" s="53"/>
+    <row r="110" ht="16" customHeight="1" s="53"/>
+    <row r="111" ht="16" customHeight="1" s="53"/>
+    <row r="112" ht="16" customHeight="1" s="53"/>
+    <row r="113" ht="16" customHeight="1" s="53"/>
+    <row r="114" ht="16" customHeight="1" s="53"/>
+    <row r="115" ht="16" customHeight="1" s="53"/>
+    <row r="116" ht="16" customHeight="1" s="53"/>
+    <row r="117" ht="16" customHeight="1" s="53"/>
+    <row r="118" ht="16" customHeight="1" s="53"/>
+    <row r="119" ht="16" customHeight="1" s="53"/>
+    <row r="120" ht="16" customHeight="1" s="53"/>
+    <row r="121" ht="16" customHeight="1" s="53"/>
+    <row r="122" ht="16" customHeight="1" s="53"/>
+    <row r="123" ht="16" customHeight="1" s="53"/>
+    <row r="124" ht="16" customHeight="1" s="53"/>
+    <row r="125" ht="16" customHeight="1" s="53"/>
+    <row r="126" ht="16" customHeight="1" s="53"/>
+    <row r="127" ht="16" customHeight="1" s="53"/>
+    <row r="128" ht="16" customHeight="1" s="53"/>
+    <row r="129" ht="16" customHeight="1" s="53"/>
+    <row r="130" ht="16" customHeight="1" s="53"/>
+    <row r="131" ht="16" customHeight="1" s="53"/>
+    <row r="132" ht="16" customHeight="1" s="53"/>
+    <row r="133" ht="16" customHeight="1" s="53"/>
+    <row r="134" ht="16" customHeight="1" s="53"/>
+    <row r="135" ht="16" customHeight="1" s="53"/>
+    <row r="136" ht="16" customHeight="1" s="53"/>
+    <row r="137" ht="16" customHeight="1" s="53"/>
+    <row r="138" ht="16" customHeight="1" s="53"/>
+    <row r="139" ht="16" customHeight="1" s="53"/>
+    <row r="140" ht="16" customHeight="1" s="53"/>
+    <row r="141" ht="16" customHeight="1" s="53"/>
+    <row r="142" ht="16" customHeight="1" s="53"/>
+    <row r="143" ht="16" customHeight="1" s="53"/>
+    <row r="144" ht="16" customHeight="1" s="53"/>
+    <row r="145" ht="16" customHeight="1" s="53"/>
+    <row r="146" ht="16" customHeight="1" s="53"/>
+    <row r="147" ht="16" customHeight="1" s="53"/>
+    <row r="148" ht="16" customHeight="1" s="53"/>
+    <row r="149" ht="16" customHeight="1" s="53"/>
+    <row r="150" ht="16" customHeight="1" s="53"/>
+    <row r="151" ht="16" customHeight="1" s="53"/>
+    <row r="152" ht="16" customHeight="1" s="53"/>
+    <row r="153" ht="16" customHeight="1" s="53"/>
+    <row r="154" ht="16" customHeight="1" s="53"/>
+    <row r="155" ht="16" customHeight="1" s="53"/>
+    <row r="156" ht="16" customHeight="1" s="53"/>
+    <row r="157" ht="16" customHeight="1" s="53"/>
+    <row r="158" ht="16" customHeight="1" s="53"/>
+    <row r="159" ht="16" customHeight="1" s="53"/>
+    <row r="160" ht="16" customHeight="1" s="53"/>
+    <row r="161" ht="16" customHeight="1" s="53"/>
+    <row r="162" ht="16" customHeight="1" s="53"/>
+    <row r="163" ht="16" customHeight="1" s="53"/>
+    <row r="164" ht="16" customHeight="1" s="53"/>
+    <row r="165" ht="16" customHeight="1" s="53"/>
+    <row r="166" ht="16" customHeight="1" s="53"/>
+    <row r="167" ht="16" customHeight="1" s="53"/>
+    <row r="168" ht="16" customHeight="1" s="53"/>
+    <row r="169" ht="16" customHeight="1" s="53"/>
+    <row r="170" ht="16" customHeight="1" s="53"/>
+    <row r="171" ht="16" customHeight="1" s="53"/>
+    <row r="172" ht="16" customHeight="1" s="53"/>
+    <row r="173" ht="16" customHeight="1" s="53"/>
+    <row r="174" ht="16" customHeight="1" s="53"/>
+    <row r="175" ht="16" customHeight="1" s="53"/>
+    <row r="176" ht="16" customHeight="1" s="53"/>
+    <row r="177" ht="16" customHeight="1" s="53"/>
+    <row r="178" ht="16" customHeight="1" s="53"/>
+    <row r="179" ht="16" customHeight="1" s="53"/>
+    <row r="180" ht="16" customHeight="1" s="53"/>
+    <row r="181" ht="16" customHeight="1" s="53"/>
+    <row r="182" ht="16" customHeight="1" s="53"/>
+    <row r="183" ht="16" customHeight="1" s="53"/>
+    <row r="184" ht="16" customHeight="1" s="53"/>
+    <row r="185" ht="16" customHeight="1" s="53"/>
+    <row r="186" ht="16" customHeight="1" s="53"/>
+    <row r="187" ht="16" customHeight="1" s="53"/>
+    <row r="188" ht="16" customHeight="1" s="53"/>
+    <row r="189" ht="16" customHeight="1" s="53"/>
+    <row r="190" ht="16" customHeight="1" s="53"/>
+    <row r="191" ht="16" customHeight="1" s="53"/>
+    <row r="192" ht="16" customHeight="1" s="53"/>
+    <row r="193" ht="16" customHeight="1" s="53"/>
+    <row r="194" ht="16" customHeight="1" s="53"/>
+    <row r="195" ht="16" customHeight="1" s="53"/>
+    <row r="196" ht="16" customHeight="1" s="53"/>
+    <row r="197" ht="16" customHeight="1" s="53"/>
+    <row r="198" ht="16" customHeight="1" s="53"/>
+    <row r="199" ht="16" customHeight="1" s="53"/>
+    <row r="200" ht="16" customHeight="1" s="53"/>
+    <row r="201" ht="16" customHeight="1" s="53"/>
+    <row r="202" ht="16" customHeight="1" s="53"/>
+    <row r="203" ht="16" customHeight="1" s="53"/>
+    <row r="204" ht="16" customHeight="1" s="53"/>
+    <row r="205" ht="16" customHeight="1" s="53"/>
+    <row r="206" ht="16" customHeight="1" s="53"/>
+    <row r="207" ht="16" customHeight="1" s="53"/>
+    <row r="208" ht="16" customHeight="1" s="53"/>
+    <row r="209" ht="16" customHeight="1" s="53"/>
+    <row r="210" ht="16" customHeight="1" s="53"/>
+    <row r="211" ht="16" customHeight="1" s="53"/>
+    <row r="212" ht="16" customHeight="1" s="53"/>
+    <row r="213" ht="16" customHeight="1" s="53"/>
+    <row r="214" ht="16" customHeight="1" s="53"/>
+    <row r="215" ht="16" customHeight="1" s="53"/>
+    <row r="216" ht="16" customHeight="1" s="53"/>
+    <row r="217" ht="16" customHeight="1" s="53"/>
+    <row r="218" ht="16" customHeight="1" s="53"/>
+    <row r="219" ht="16" customHeight="1" s="53"/>
+    <row r="220" ht="16" customHeight="1" s="53"/>
+    <row r="221" ht="16" customHeight="1" s="53"/>
+    <row r="222" ht="16" customHeight="1" s="53"/>
+    <row r="223" ht="16" customHeight="1" s="53"/>
+    <row r="224" ht="16" customHeight="1" s="53"/>
+    <row r="225" ht="16" customHeight="1" s="53"/>
+    <row r="226" ht="16" customHeight="1" s="53"/>
+    <row r="227" ht="16" customHeight="1" s="53"/>
+    <row r="228" ht="16" customHeight="1" s="53"/>
+    <row r="229" ht="16" customHeight="1" s="53"/>
+    <row r="230" ht="16" customHeight="1" s="53"/>
+    <row r="231" ht="16" customHeight="1" s="53"/>
+    <row r="232" ht="16" customHeight="1" s="53"/>
+    <row r="233" ht="16" customHeight="1" s="53"/>
+    <row r="234" ht="16" customHeight="1" s="53"/>
+    <row r="235" ht="16" customHeight="1" s="53"/>
+    <row r="236" ht="16" customHeight="1" s="53"/>
+    <row r="237" ht="16" customHeight="1" s="53"/>
+    <row r="238" ht="16" customHeight="1" s="53"/>
+    <row r="239" ht="16" customHeight="1" s="53"/>
+    <row r="240" ht="16" customHeight="1" s="53"/>
+    <row r="241" ht="16" customHeight="1" s="53"/>
+    <row r="242" ht="16" customHeight="1" s="53"/>
+    <row r="243" ht="16" customHeight="1" s="53"/>
+    <row r="244" ht="16" customHeight="1" s="53"/>
+    <row r="245" ht="16" customHeight="1" s="53"/>
+    <row r="246" ht="16" customHeight="1" s="53"/>
+    <row r="247" ht="16" customHeight="1" s="53"/>
+    <row r="248" ht="16" customHeight="1" s="53"/>
+    <row r="249" ht="16" customHeight="1" s="53"/>
+    <row r="250" ht="16" customHeight="1" s="53"/>
+    <row r="251" ht="16" customHeight="1" s="53"/>
+    <row r="252" ht="16" customHeight="1" s="53"/>
+    <row r="253" ht="16" customHeight="1" s="53"/>
+    <row r="254" ht="16" customHeight="1" s="53"/>
+    <row r="255" ht="16" customHeight="1" s="53"/>
+    <row r="256" ht="16" customHeight="1" s="53"/>
+    <row r="257" ht="16" customHeight="1" s="53"/>
+    <row r="258" ht="16" customHeight="1" s="53"/>
+    <row r="259" ht="16" customHeight="1" s="53"/>
+    <row r="260" ht="16" customHeight="1" s="53"/>
+    <row r="261" ht="16" customHeight="1" s="53"/>
+    <row r="262" ht="16" customHeight="1" s="53"/>
   </sheetData>
   <autoFilter ref="A2:F61"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4840,17 +4840,17 @@
   <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
-    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
-    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
-    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
-    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
-    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
-    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
-    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
+    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
+    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
+    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
+    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
+    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
+    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
+    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
+    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="22.5" r="1" s="53">
+    <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -4873,7 +4873,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>区域</t>
@@ -4959,7 +4959,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5002,7 +5002,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5047,7 +5047,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5084,7 +5084,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5129,7 +5129,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5168,7 +5168,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5205,7 +5205,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5234,7 +5234,7 @@
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5273,7 +5273,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5310,7 +5310,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5347,7 +5347,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5386,7 +5386,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5423,7 +5423,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5450,7 +5450,7 @@
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5478,7 +5478,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5506,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5534,7 +5534,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5564,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5594,7 +5594,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5630,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5658,7 +5658,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5688,7 +5688,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5756,7 +5756,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5788,7 +5788,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5822,7 +5822,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5854,7 +5854,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5882,7 +5882,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5918,7 +5918,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5945,7 +5945,7 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5977,7 +5977,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6009,7 +6009,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6034,7 +6034,7 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6064,7 +6064,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6094,7 +6094,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6128,7 +6128,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6158,7 +6158,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6186,7 +6186,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6214,7 +6214,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6242,7 +6242,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6270,7 +6270,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6298,7 +6298,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6326,7 +6326,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6354,7 +6354,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6382,7 +6382,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6420,7 +6420,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6450,7 +6450,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6486,7 +6486,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6520,7 +6520,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6556,7 +6556,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6588,7 +6588,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="53" s="53">
+    <row r="53" ht="16.5" customHeight="1" s="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -7236,7 +7236,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7249,17 +7249,17 @@
   <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
-    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
-    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
-    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
-    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
-    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
-    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
-    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
+    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
+    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
+    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
+    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
+    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
+    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
+    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
+    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="22.5" r="1" s="53">
+    <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -7282,7 +7282,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>区域</t>
@@ -7368,7 +7368,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7451,7 +7451,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7497,7 +7497,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7543,7 +7543,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7591,7 +7591,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7628,7 +7628,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7665,7 +7665,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7713,7 +7713,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7759,7 +7759,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7796,7 +7796,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7833,7 +7833,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7879,7 +7879,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7907,7 +7907,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7935,7 +7935,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7963,7 +7963,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7991,7 +7991,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8019,7 +8019,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8047,7 +8047,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8075,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8103,7 +8103,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8131,7 +8131,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8159,7 +8159,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8187,7 +8187,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8215,7 +8215,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8243,7 +8243,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8273,7 +8273,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8301,7 +8301,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8357,7 +8357,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8385,7 +8385,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8413,7 +8413,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8441,7 +8441,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8471,7 +8471,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8499,7 +8499,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8527,7 +8527,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8555,7 +8555,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8583,7 +8583,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8613,7 +8613,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8645,7 +8645,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8673,7 +8673,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8701,7 +8701,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8729,7 +8729,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8757,7 +8757,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8785,7 +8785,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8817,7 +8817,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8849,7 +8849,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -9525,7 +9525,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9536,16 +9536,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -9555,7 +9555,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -9600,7 +9600,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9646,7 +9646,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9691,7 +9691,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9740,7 +9740,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9789,7 +9789,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9831,7 +9831,7 @@
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="35" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9866,7 +9866,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9906,7 +9906,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9942,7 +9942,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -9978,7 +9978,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10014,7 +10014,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10055,7 +10055,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10086,7 +10086,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10142,7 +10142,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10181,7 +10181,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="D20" s="39" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="D25" s="36" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10349,7 +10349,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10508,7 +10508,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10552,7 +10552,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10574,7 +10574,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D41" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D43" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="E44" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10733,7 +10733,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10755,7 +10755,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E50" s="49" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="53" s="53">
+    <row r="53" ht="16" customHeight="1" s="53">
       <c r="A53" s="37" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="55" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="55" s="53">
+    <row r="55" ht="16.5" customHeight="1" s="53">
       <c r="A55" s="55" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10954,7 +10954,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="56" s="53">
+    <row r="56" ht="16.5" customHeight="1" s="53">
       <c r="A56" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10976,7 +10976,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="57" s="53">
+    <row r="57" ht="16.5" customHeight="1" s="53">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10994,7 +10994,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -11005,18 +11005,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="23" width="6.83203125"/>
-    <col customWidth="1" max="2" min="2" style="23" width="8.83203125"/>
-    <col customWidth="1" max="3" min="3" style="23" width="19.6640625"/>
-    <col customWidth="1" max="4" min="4" style="23" width="13"/>
-    <col customWidth="1" hidden="1" max="6" min="5" style="23" width="30.5"/>
-    <col customWidth="1" max="7" min="7" style="23" width="30.5"/>
-    <col customWidth="1" max="26" min="8" style="23" width="10.83203125"/>
+    <col width="6.83203125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="8.83203125" customWidth="1" style="23" min="2" max="2"/>
+    <col width="19.6640625" customWidth="1" style="23" min="3" max="3"/>
+    <col width="13" customWidth="1" style="23" min="4" max="4"/>
+    <col hidden="1" width="30.5" customWidth="1" style="23" min="5" max="6"/>
+    <col width="30.5" customWidth="1" style="23" min="7" max="7"/>
+    <col width="10.83203125" customWidth="1" style="23" min="8" max="26"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="15" r="1" s="53">
+    <row r="1" ht="15" customHeight="1" s="53">
       <c r="A1" s="21" t="n"/>
       <c r="B1" s="22" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="2" s="53">
+    <row r="2" ht="15.75" customHeight="1" s="53">
       <c r="A2" s="24" t="n">
         <v>1</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="3" s="53">
+    <row r="3" ht="15" customHeight="1" s="53">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="4" s="53">
+    <row r="4" ht="15" customHeight="1" s="53">
       <c r="A4" s="24" t="n">
         <v>3</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="5" s="53">
+    <row r="5" ht="15" customHeight="1" s="53">
       <c r="A5" s="24" t="n">
         <v>4</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="6" s="53">
+    <row r="6" ht="15" customHeight="1" s="53">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="7" s="53">
+    <row r="7" ht="15" customHeight="1" s="53">
       <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="8" s="53">
+    <row r="8" ht="15" customHeight="1" s="53">
       <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="9" s="53">
+    <row r="9" ht="15" customHeight="1" s="53">
       <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="10" s="53">
+    <row r="10" ht="15" customHeight="1" s="53">
       <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="11" s="53">
+    <row r="11" ht="15" customHeight="1" s="53">
       <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="12" s="53">
+    <row r="12" ht="15" customHeight="1" s="53">
       <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="13" s="53">
+    <row r="13" ht="15" customHeight="1" s="53">
       <c r="A13" s="24" t="n">
         <v>4</v>
       </c>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="14" s="53">
+    <row r="14" ht="15" customHeight="1" s="53">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="15" s="53">
+    <row r="15" ht="15" customHeight="1" s="53">
       <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="16" s="53">
+    <row r="16" ht="15" customHeight="1" s="53">
       <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
@@ -11517,7 +11517,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="17" s="53">
+    <row r="17" ht="15.75" customHeight="1" s="53">
       <c r="A17" s="24" t="n">
         <v>2</v>
       </c>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="18" s="53">
+    <row r="18" ht="15" customHeight="1" s="53">
       <c r="A18" s="24" t="n">
         <v>3</v>
       </c>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="19" s="53">
+    <row r="19" ht="15" customHeight="1" s="53">
       <c r="A19" s="24" t="n">
         <v>4</v>
       </c>
@@ -11612,7 +11612,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="20" s="53">
+    <row r="20" ht="15" customHeight="1" s="53">
       <c r="A20" s="24" t="n">
         <v>5</v>
       </c>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="21" s="53">
+    <row r="21" ht="15" customHeight="1" s="53">
       <c r="A21" s="24" t="n">
         <v>6</v>
       </c>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="22" s="53">
+    <row r="22" ht="15" customHeight="1" s="53">
       <c r="A22" s="24" t="n">
         <v>7</v>
       </c>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="23" s="53">
+    <row r="23" ht="15" customHeight="1" s="53">
       <c r="A23" s="24" t="n">
         <v>8</v>
       </c>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="24" s="53">
+    <row r="24" ht="15" customHeight="1" s="53">
       <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
@@ -11762,7 +11762,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="25" s="53">
+    <row r="25" ht="15" customHeight="1" s="53">
       <c r="A25" s="24" t="n">
         <v>2</v>
       </c>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="26" s="53">
+    <row r="26" ht="15" customHeight="1" s="53">
       <c r="A26" s="24" t="n">
         <v>3</v>
       </c>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="27" s="53">
+    <row r="27" ht="15.75" customHeight="1" s="53">
       <c r="A27" s="24" t="n">
         <v>4</v>
       </c>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="28" s="53">
+    <row r="28" ht="15" customHeight="1" s="53">
       <c r="A28" s="24" t="n">
         <v>5</v>
       </c>
@@ -11877,7 +11877,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="29" s="53">
+    <row r="29" ht="15" customHeight="1" s="53">
       <c r="A29" s="24" t="n">
         <v>6</v>
       </c>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="30" s="53">
+    <row r="30" ht="15.75" customHeight="1" s="53">
       <c r="A30" s="24" t="n">
         <v>7</v>
       </c>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="31" s="53">
+    <row r="31" ht="15.75" customHeight="1" s="53">
       <c r="A31" s="24" t="n">
         <v>8</v>
       </c>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="32" s="53">
+    <row r="32" ht="15" customHeight="1" s="53">
       <c r="A32" s="24" t="n">
         <v>1</v>
       </c>
@@ -12002,7 +12002,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="33" s="53">
+    <row r="33" ht="15" customHeight="1" s="53">
       <c r="A33" s="24" t="n">
         <v>2</v>
       </c>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="34" s="53">
+    <row r="34" ht="15" customHeight="1" s="53">
       <c r="A34" s="24" t="n">
         <v>3</v>
       </c>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="35" s="53">
+    <row r="35" ht="15" customHeight="1" s="53">
       <c r="A35" s="24" t="n">
         <v>4</v>
       </c>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="36" s="53">
+    <row r="36" ht="15" customHeight="1" s="53">
       <c r="A36" s="24" t="n">
         <v>1</v>
       </c>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="37" s="53">
+    <row r="37" ht="15" customHeight="1" s="53">
       <c r="A37" s="24" t="n">
         <v>2</v>
       </c>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="38" s="53">
+    <row r="38" ht="15" customHeight="1" s="53">
       <c r="A38" s="24" t="n">
         <v>3</v>
       </c>
@@ -12188,6 +12188,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16400" windowWidth="27040" xWindow="0" yWindow="500"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,257 +449,257 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1">
+    <xf applyAlignment="1" borderId="7" fillId="7" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="83">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="5" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="10" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="11" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="12" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="16" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="14" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="常规" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1073,16 +1073,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1472,7 +1472,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1642,7 +1642,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D40" s="46" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D48" s="51" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -2619,26 +2619,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46222</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+        <v>46229</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>区域</t>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2748,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2808,7 +2808,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2872,7 +2872,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2978,7 +2978,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3024,7 +3024,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3066,7 +3066,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3200,7 +3200,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3279,7 +3279,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="15" s="78">
       <c r="A15" s="61" t="inlineStr">
         <is>
           <t>粤西区</t>
@@ -3310,7 +3310,7 @@
       <c r="H15" s="23" t="n"/>
       <c r="J15" s="67" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3343,7 +3343,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G17" s="67" t="n"/>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="G18" s="67" t="n"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G19" s="67" t="n"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G20" s="67" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G21" s="67" t="n"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="G22" s="67" t="n"/>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G23" s="67" t="n"/>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="G24" s="67" t="n"/>
     </row>
-    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="25" s="78">
       <c r="A25" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3574,7 +3574,7 @@
       <c r="H25" s="67" t="n"/>
       <c r="J25" s="67" t="n"/>
     </row>
-    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="26" s="78">
       <c r="A26" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3605,7 +3605,7 @@
       <c r="H26" s="67" t="n"/>
       <c r="J26" s="67" t="n"/>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G27" s="67" t="n"/>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G28" s="67" t="n"/>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G29" s="67" t="n"/>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="G30" s="67" t="n"/>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G31" s="67" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G32" s="67" t="n"/>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="G33" s="67" t="n"/>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G34" s="67" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G35" s="67" t="n"/>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="G36" s="67" t="n"/>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="G37" s="67" t="n"/>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G38" s="67" t="n"/>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G39" s="67" t="n"/>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G40" s="67" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G41" s="67" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="G42" s="67" t="n"/>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="G43" s="67" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G44" s="67" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G45" s="67" t="n"/>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G46" s="67" t="n"/>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="G47" s="67" t="n"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G48" s="67" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G49" s="67" t="n"/>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G50" s="67" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="G51" s="67" t="n"/>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G52" s="67" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="72" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D53" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E53" s="69" t="n"/>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G53" s="67" t="n"/>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="58" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4352,7 +4352,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D54" s="70" t="n"/>
+      <c r="D54" s="70" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E54" s="69" t="n"/>
       <c r="F54" s="63" t="inlineStr">
         <is>
@@ -4361,7 +4365,7 @@
       </c>
       <c r="G54" s="67" t="n"/>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="58" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4390,7 +4394,7 @@
       </c>
       <c r="G55" s="67" t="n"/>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="G56" s="67" t="n"/>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4444,7 +4448,7 @@
       </c>
       <c r="G57" s="67" t="n"/>
     </row>
-    <row r="58" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="58" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
           <t>华北分公司</t>
@@ -4460,7 +4464,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D58" s="68" t="n"/>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E58" s="69" t="n"/>
       <c r="F58" s="63" t="inlineStr">
         <is>
@@ -4469,7 +4477,7 @@
       </c>
       <c r="G58" s="67" t="n"/>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="59" s="53">
       <c r="A59" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4498,7 +4506,7 @@
       </c>
       <c r="G59" s="67" t="n"/>
     </row>
-    <row r="60" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="60" s="53">
       <c r="A60" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4523,7 +4531,7 @@
       </c>
       <c r="G60" s="67" t="n"/>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="61" s="53">
       <c r="A61" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4552,7 +4560,7 @@
       </c>
       <c r="G61" s="67" t="n"/>
     </row>
-    <row r="62" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="62" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4576,7 +4584,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="63" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4592,7 +4600,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D63" s="68" t="n"/>
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E63" s="69" t="n"/>
       <c r="F63" s="63" t="inlineStr">
         <is>
@@ -4600,7 +4612,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="64" s="53">
       <c r="A64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4627,207 +4639,207 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1" s="53"/>
-    <row r="66" ht="16" customHeight="1" s="53"/>
-    <row r="67" ht="16" customHeight="1" s="53"/>
-    <row r="68" ht="16" customHeight="1" s="53"/>
-    <row r="69" ht="16" customHeight="1" s="53"/>
-    <row r="70" ht="16" customHeight="1" s="53"/>
-    <row r="71" ht="16" customHeight="1" s="53"/>
-    <row r="72" ht="16" customHeight="1" s="53"/>
-    <row r="73" ht="16" customHeight="1" s="53"/>
-    <row r="74" ht="16" customHeight="1" s="53"/>
-    <row r="75" ht="16" customHeight="1" s="53"/>
-    <row r="76" ht="16" customHeight="1" s="53"/>
-    <row r="77" ht="16" customHeight="1" s="53"/>
-    <row r="78" ht="16" customHeight="1" s="53"/>
-    <row r="79" ht="16" customHeight="1" s="53"/>
-    <row r="80" ht="16" customHeight="1" s="53"/>
-    <row r="81" ht="16" customHeight="1" s="53"/>
-    <row r="82" ht="16" customHeight="1" s="53"/>
-    <row r="83" ht="16" customHeight="1" s="53"/>
-    <row r="84" ht="16" customHeight="1" s="53"/>
-    <row r="85" ht="16" customHeight="1" s="53"/>
-    <row r="86" ht="16" customHeight="1" s="53"/>
-    <row r="87" ht="16" customHeight="1" s="53"/>
-    <row r="88" ht="16" customHeight="1" s="53"/>
-    <row r="89" ht="16" customHeight="1" s="53"/>
-    <row r="90" ht="16" customHeight="1" s="53"/>
-    <row r="91" ht="16" customHeight="1" s="53"/>
-    <row r="92" ht="16" customHeight="1" s="53"/>
-    <row r="93" ht="16" customHeight="1" s="53"/>
-    <row r="94" ht="16" customHeight="1" s="53"/>
-    <row r="95" ht="16" customHeight="1" s="53"/>
-    <row r="96" ht="16" customHeight="1" s="53"/>
-    <row r="97" ht="16" customHeight="1" s="53"/>
-    <row r="98" ht="16" customHeight="1" s="53"/>
-    <row r="99" ht="16" customHeight="1" s="53"/>
-    <row r="100" ht="16" customHeight="1" s="53"/>
-    <row r="101" ht="16" customHeight="1" s="53"/>
-    <row r="102" ht="16" customHeight="1" s="53"/>
-    <row r="103" ht="16" customHeight="1" s="53"/>
-    <row r="104" ht="16" customHeight="1" s="53"/>
-    <row r="105" ht="16" customHeight="1" s="53"/>
-    <row r="106" ht="16" customHeight="1" s="53"/>
-    <row r="107" ht="16" customHeight="1" s="53"/>
-    <row r="108" ht="16" customHeight="1" s="53"/>
-    <row r="109" ht="16" customHeight="1" s="53"/>
-    <row r="110" ht="16" customHeight="1" s="53"/>
-    <row r="111" ht="16" customHeight="1" s="53"/>
-    <row r="112" ht="16" customHeight="1" s="53"/>
-    <row r="113" ht="16" customHeight="1" s="53"/>
-    <row r="114" ht="16" customHeight="1" s="53"/>
-    <row r="115" ht="16" customHeight="1" s="53"/>
-    <row r="116" ht="16" customHeight="1" s="53"/>
-    <row r="117" ht="16" customHeight="1" s="53"/>
-    <row r="118" ht="16" customHeight="1" s="53"/>
-    <row r="119" ht="16" customHeight="1" s="53"/>
-    <row r="120" ht="16" customHeight="1" s="53"/>
-    <row r="121" ht="16" customHeight="1" s="53"/>
-    <row r="122" ht="16" customHeight="1" s="53"/>
-    <row r="123" ht="16" customHeight="1" s="53"/>
-    <row r="124" ht="16" customHeight="1" s="53"/>
-    <row r="125" ht="16" customHeight="1" s="53"/>
-    <row r="126" ht="16" customHeight="1" s="53"/>
-    <row r="127" ht="16" customHeight="1" s="53"/>
-    <row r="128" ht="16" customHeight="1" s="53"/>
-    <row r="129" ht="16" customHeight="1" s="53"/>
-    <row r="130" ht="16" customHeight="1" s="53"/>
-    <row r="131" ht="16" customHeight="1" s="53"/>
-    <row r="132" ht="16" customHeight="1" s="53"/>
-    <row r="133" ht="16" customHeight="1" s="53"/>
-    <row r="134" ht="16" customHeight="1" s="53"/>
-    <row r="135" ht="16" customHeight="1" s="53"/>
-    <row r="136" ht="16" customHeight="1" s="53"/>
-    <row r="137" ht="16" customHeight="1" s="53"/>
-    <row r="138" ht="16" customHeight="1" s="53"/>
-    <row r="139" ht="16" customHeight="1" s="53"/>
-    <row r="140" ht="16" customHeight="1" s="53"/>
-    <row r="141" ht="16" customHeight="1" s="53"/>
-    <row r="142" ht="16" customHeight="1" s="53"/>
-    <row r="143" ht="16" customHeight="1" s="53"/>
-    <row r="144" ht="16" customHeight="1" s="53"/>
-    <row r="145" ht="16" customHeight="1" s="53"/>
-    <row r="146" ht="16" customHeight="1" s="53"/>
-    <row r="147" ht="16" customHeight="1" s="53"/>
-    <row r="148" ht="16" customHeight="1" s="53"/>
-    <row r="149" ht="16" customHeight="1" s="53"/>
-    <row r="150" ht="16" customHeight="1" s="53"/>
-    <row r="151" ht="16" customHeight="1" s="53"/>
-    <row r="152" ht="16" customHeight="1" s="53"/>
-    <row r="153" ht="16" customHeight="1" s="53"/>
-    <row r="154" ht="16" customHeight="1" s="53"/>
-    <row r="155" ht="16" customHeight="1" s="53"/>
-    <row r="156" ht="16" customHeight="1" s="53"/>
-    <row r="157" ht="16" customHeight="1" s="53"/>
-    <row r="158" ht="16" customHeight="1" s="53"/>
-    <row r="159" ht="16" customHeight="1" s="53"/>
-    <row r="160" ht="16" customHeight="1" s="53"/>
-    <row r="161" ht="16" customHeight="1" s="53"/>
-    <row r="162" ht="16" customHeight="1" s="53"/>
-    <row r="163" ht="16" customHeight="1" s="53"/>
-    <row r="164" ht="16" customHeight="1" s="53"/>
-    <row r="165" ht="16" customHeight="1" s="53"/>
-    <row r="166" ht="16" customHeight="1" s="53"/>
-    <row r="167" ht="16" customHeight="1" s="53"/>
-    <row r="168" ht="16" customHeight="1" s="53"/>
-    <row r="169" ht="16" customHeight="1" s="53"/>
-    <row r="170" ht="16" customHeight="1" s="53"/>
-    <row r="171" ht="16" customHeight="1" s="53"/>
-    <row r="172" ht="16" customHeight="1" s="53"/>
-    <row r="173" ht="16" customHeight="1" s="53"/>
-    <row r="174" ht="16" customHeight="1" s="53"/>
-    <row r="175" ht="16" customHeight="1" s="53"/>
-    <row r="176" ht="16" customHeight="1" s="53"/>
-    <row r="177" ht="16" customHeight="1" s="53"/>
-    <row r="178" ht="16" customHeight="1" s="53"/>
-    <row r="179" ht="16" customHeight="1" s="53"/>
-    <row r="180" ht="16" customHeight="1" s="53"/>
-    <row r="181" ht="16" customHeight="1" s="53"/>
-    <row r="182" ht="16" customHeight="1" s="53"/>
-    <row r="183" ht="16" customHeight="1" s="53"/>
-    <row r="184" ht="16" customHeight="1" s="53"/>
-    <row r="185" ht="16" customHeight="1" s="53"/>
-    <row r="186" ht="16" customHeight="1" s="53"/>
-    <row r="187" ht="16" customHeight="1" s="53"/>
-    <row r="188" ht="16" customHeight="1" s="53"/>
-    <row r="189" ht="16" customHeight="1" s="53"/>
-    <row r="190" ht="16" customHeight="1" s="53"/>
-    <row r="191" ht="16" customHeight="1" s="53"/>
-    <row r="192" ht="16" customHeight="1" s="53"/>
-    <row r="193" ht="16" customHeight="1" s="53"/>
-    <row r="194" ht="16" customHeight="1" s="53"/>
-    <row r="195" ht="16" customHeight="1" s="53"/>
-    <row r="196" ht="16" customHeight="1" s="53"/>
-    <row r="197" ht="16" customHeight="1" s="53"/>
-    <row r="198" ht="16" customHeight="1" s="53"/>
-    <row r="199" ht="16" customHeight="1" s="53"/>
-    <row r="200" ht="16" customHeight="1" s="53"/>
-    <row r="201" ht="16" customHeight="1" s="53"/>
-    <row r="202" ht="16" customHeight="1" s="53"/>
-    <row r="203" ht="16" customHeight="1" s="53"/>
-    <row r="204" ht="16" customHeight="1" s="53"/>
-    <row r="205" ht="16" customHeight="1" s="53"/>
-    <row r="206" ht="16" customHeight="1" s="53"/>
-    <row r="207" ht="16" customHeight="1" s="53"/>
-    <row r="208" ht="16" customHeight="1" s="53"/>
-    <row r="209" ht="16" customHeight="1" s="53"/>
-    <row r="210" ht="16" customHeight="1" s="53"/>
-    <row r="211" ht="16" customHeight="1" s="53"/>
-    <row r="212" ht="16" customHeight="1" s="53"/>
-    <row r="213" ht="16" customHeight="1" s="53"/>
-    <row r="214" ht="16" customHeight="1" s="53"/>
-    <row r="215" ht="16" customHeight="1" s="53"/>
-    <row r="216" ht="16" customHeight="1" s="53"/>
-    <row r="217" ht="16" customHeight="1" s="53"/>
-    <row r="218" ht="16" customHeight="1" s="53"/>
-    <row r="219" ht="16" customHeight="1" s="53"/>
-    <row r="220" ht="16" customHeight="1" s="53"/>
-    <row r="221" ht="16" customHeight="1" s="53"/>
-    <row r="222" ht="16" customHeight="1" s="53"/>
-    <row r="223" ht="16" customHeight="1" s="53"/>
-    <row r="224" ht="16" customHeight="1" s="53"/>
-    <row r="225" ht="16" customHeight="1" s="53"/>
-    <row r="226" ht="16" customHeight="1" s="53"/>
-    <row r="227" ht="16" customHeight="1" s="53"/>
-    <row r="228" ht="16" customHeight="1" s="53"/>
-    <row r="229" ht="16" customHeight="1" s="53"/>
-    <row r="230" ht="16" customHeight="1" s="53"/>
-    <row r="231" ht="16" customHeight="1" s="53"/>
-    <row r="232" ht="16" customHeight="1" s="53"/>
-    <row r="233" ht="16" customHeight="1" s="53"/>
-    <row r="234" ht="16" customHeight="1" s="53"/>
-    <row r="235" ht="16" customHeight="1" s="53"/>
-    <row r="236" ht="16" customHeight="1" s="53"/>
-    <row r="237" ht="16" customHeight="1" s="53"/>
-    <row r="238" ht="16" customHeight="1" s="53"/>
-    <row r="239" ht="16" customHeight="1" s="53"/>
-    <row r="240" ht="16" customHeight="1" s="53"/>
-    <row r="241" ht="16" customHeight="1" s="53"/>
-    <row r="242" ht="16" customHeight="1" s="53"/>
-    <row r="243" ht="16" customHeight="1" s="53"/>
-    <row r="244" ht="16" customHeight="1" s="53"/>
-    <row r="245" ht="16" customHeight="1" s="53"/>
-    <row r="246" ht="16" customHeight="1" s="53"/>
-    <row r="247" ht="16" customHeight="1" s="53"/>
-    <row r="248" ht="16" customHeight="1" s="53"/>
-    <row r="249" ht="16" customHeight="1" s="53"/>
-    <row r="250" ht="16" customHeight="1" s="53"/>
-    <row r="251" ht="16" customHeight="1" s="53"/>
-    <row r="252" ht="16" customHeight="1" s="53"/>
-    <row r="253" ht="16" customHeight="1" s="53"/>
-    <row r="254" ht="16" customHeight="1" s="53"/>
-    <row r="255" ht="16" customHeight="1" s="53"/>
-    <row r="256" ht="16" customHeight="1" s="53"/>
-    <row r="257" ht="16" customHeight="1" s="53"/>
-    <row r="258" ht="16" customHeight="1" s="53"/>
-    <row r="259" ht="16" customHeight="1" s="53"/>
-    <row r="260" ht="16" customHeight="1" s="53"/>
-    <row r="261" ht="16" customHeight="1" s="53"/>
-    <row r="262" ht="16" customHeight="1" s="53"/>
+    <row customHeight="1" ht="16" r="65" s="53"/>
+    <row customHeight="1" ht="16" r="66" s="53"/>
+    <row customHeight="1" ht="16" r="67" s="53"/>
+    <row customHeight="1" ht="16" r="68" s="53"/>
+    <row customHeight="1" ht="16" r="69" s="53"/>
+    <row customHeight="1" ht="16" r="70" s="53"/>
+    <row customHeight="1" ht="16" r="71" s="53"/>
+    <row customHeight="1" ht="16" r="72" s="53"/>
+    <row customHeight="1" ht="16" r="73" s="53"/>
+    <row customHeight="1" ht="16" r="74" s="53"/>
+    <row customHeight="1" ht="16" r="75" s="53"/>
+    <row customHeight="1" ht="16" r="76" s="53"/>
+    <row customHeight="1" ht="16" r="77" s="53"/>
+    <row customHeight="1" ht="16" r="78" s="53"/>
+    <row customHeight="1" ht="16" r="79" s="53"/>
+    <row customHeight="1" ht="16" r="80" s="53"/>
+    <row customHeight="1" ht="16" r="81" s="53"/>
+    <row customHeight="1" ht="16" r="82" s="53"/>
+    <row customHeight="1" ht="16" r="83" s="53"/>
+    <row customHeight="1" ht="16" r="84" s="53"/>
+    <row customHeight="1" ht="16" r="85" s="53"/>
+    <row customHeight="1" ht="16" r="86" s="53"/>
+    <row customHeight="1" ht="16" r="87" s="53"/>
+    <row customHeight="1" ht="16" r="88" s="53"/>
+    <row customHeight="1" ht="16" r="89" s="53"/>
+    <row customHeight="1" ht="16" r="90" s="53"/>
+    <row customHeight="1" ht="16" r="91" s="53"/>
+    <row customHeight="1" ht="16" r="92" s="53"/>
+    <row customHeight="1" ht="16" r="93" s="53"/>
+    <row customHeight="1" ht="16" r="94" s="53"/>
+    <row customHeight="1" ht="16" r="95" s="53"/>
+    <row customHeight="1" ht="16" r="96" s="53"/>
+    <row customHeight="1" ht="16" r="97" s="53"/>
+    <row customHeight="1" ht="16" r="98" s="53"/>
+    <row customHeight="1" ht="16" r="99" s="53"/>
+    <row customHeight="1" ht="16" r="100" s="53"/>
+    <row customHeight="1" ht="16" r="101" s="53"/>
+    <row customHeight="1" ht="16" r="102" s="53"/>
+    <row customHeight="1" ht="16" r="103" s="53"/>
+    <row customHeight="1" ht="16" r="104" s="53"/>
+    <row customHeight="1" ht="16" r="105" s="53"/>
+    <row customHeight="1" ht="16" r="106" s="53"/>
+    <row customHeight="1" ht="16" r="107" s="53"/>
+    <row customHeight="1" ht="16" r="108" s="53"/>
+    <row customHeight="1" ht="16" r="109" s="53"/>
+    <row customHeight="1" ht="16" r="110" s="53"/>
+    <row customHeight="1" ht="16" r="111" s="53"/>
+    <row customHeight="1" ht="16" r="112" s="53"/>
+    <row customHeight="1" ht="16" r="113" s="53"/>
+    <row customHeight="1" ht="16" r="114" s="53"/>
+    <row customHeight="1" ht="16" r="115" s="53"/>
+    <row customHeight="1" ht="16" r="116" s="53"/>
+    <row customHeight="1" ht="16" r="117" s="53"/>
+    <row customHeight="1" ht="16" r="118" s="53"/>
+    <row customHeight="1" ht="16" r="119" s="53"/>
+    <row customHeight="1" ht="16" r="120" s="53"/>
+    <row customHeight="1" ht="16" r="121" s="53"/>
+    <row customHeight="1" ht="16" r="122" s="53"/>
+    <row customHeight="1" ht="16" r="123" s="53"/>
+    <row customHeight="1" ht="16" r="124" s="53"/>
+    <row customHeight="1" ht="16" r="125" s="53"/>
+    <row customHeight="1" ht="16" r="126" s="53"/>
+    <row customHeight="1" ht="16" r="127" s="53"/>
+    <row customHeight="1" ht="16" r="128" s="53"/>
+    <row customHeight="1" ht="16" r="129" s="53"/>
+    <row customHeight="1" ht="16" r="130" s="53"/>
+    <row customHeight="1" ht="16" r="131" s="53"/>
+    <row customHeight="1" ht="16" r="132" s="53"/>
+    <row customHeight="1" ht="16" r="133" s="53"/>
+    <row customHeight="1" ht="16" r="134" s="53"/>
+    <row customHeight="1" ht="16" r="135" s="53"/>
+    <row customHeight="1" ht="16" r="136" s="53"/>
+    <row customHeight="1" ht="16" r="137" s="53"/>
+    <row customHeight="1" ht="16" r="138" s="53"/>
+    <row customHeight="1" ht="16" r="139" s="53"/>
+    <row customHeight="1" ht="16" r="140" s="53"/>
+    <row customHeight="1" ht="16" r="141" s="53"/>
+    <row customHeight="1" ht="16" r="142" s="53"/>
+    <row customHeight="1" ht="16" r="143" s="53"/>
+    <row customHeight="1" ht="16" r="144" s="53"/>
+    <row customHeight="1" ht="16" r="145" s="53"/>
+    <row customHeight="1" ht="16" r="146" s="53"/>
+    <row customHeight="1" ht="16" r="147" s="53"/>
+    <row customHeight="1" ht="16" r="148" s="53"/>
+    <row customHeight="1" ht="16" r="149" s="53"/>
+    <row customHeight="1" ht="16" r="150" s="53"/>
+    <row customHeight="1" ht="16" r="151" s="53"/>
+    <row customHeight="1" ht="16" r="152" s="53"/>
+    <row customHeight="1" ht="16" r="153" s="53"/>
+    <row customHeight="1" ht="16" r="154" s="53"/>
+    <row customHeight="1" ht="16" r="155" s="53"/>
+    <row customHeight="1" ht="16" r="156" s="53"/>
+    <row customHeight="1" ht="16" r="157" s="53"/>
+    <row customHeight="1" ht="16" r="158" s="53"/>
+    <row customHeight="1" ht="16" r="159" s="53"/>
+    <row customHeight="1" ht="16" r="160" s="53"/>
+    <row customHeight="1" ht="16" r="161" s="53"/>
+    <row customHeight="1" ht="16" r="162" s="53"/>
+    <row customHeight="1" ht="16" r="163" s="53"/>
+    <row customHeight="1" ht="16" r="164" s="53"/>
+    <row customHeight="1" ht="16" r="165" s="53"/>
+    <row customHeight="1" ht="16" r="166" s="53"/>
+    <row customHeight="1" ht="16" r="167" s="53"/>
+    <row customHeight="1" ht="16" r="168" s="53"/>
+    <row customHeight="1" ht="16" r="169" s="53"/>
+    <row customHeight="1" ht="16" r="170" s="53"/>
+    <row customHeight="1" ht="16" r="171" s="53"/>
+    <row customHeight="1" ht="16" r="172" s="53"/>
+    <row customHeight="1" ht="16" r="173" s="53"/>
+    <row customHeight="1" ht="16" r="174" s="53"/>
+    <row customHeight="1" ht="16" r="175" s="53"/>
+    <row customHeight="1" ht="16" r="176" s="53"/>
+    <row customHeight="1" ht="16" r="177" s="53"/>
+    <row customHeight="1" ht="16" r="178" s="53"/>
+    <row customHeight="1" ht="16" r="179" s="53"/>
+    <row customHeight="1" ht="16" r="180" s="53"/>
+    <row customHeight="1" ht="16" r="181" s="53"/>
+    <row customHeight="1" ht="16" r="182" s="53"/>
+    <row customHeight="1" ht="16" r="183" s="53"/>
+    <row customHeight="1" ht="16" r="184" s="53"/>
+    <row customHeight="1" ht="16" r="185" s="53"/>
+    <row customHeight="1" ht="16" r="186" s="53"/>
+    <row customHeight="1" ht="16" r="187" s="53"/>
+    <row customHeight="1" ht="16" r="188" s="53"/>
+    <row customHeight="1" ht="16" r="189" s="53"/>
+    <row customHeight="1" ht="16" r="190" s="53"/>
+    <row customHeight="1" ht="16" r="191" s="53"/>
+    <row customHeight="1" ht="16" r="192" s="53"/>
+    <row customHeight="1" ht="16" r="193" s="53"/>
+    <row customHeight="1" ht="16" r="194" s="53"/>
+    <row customHeight="1" ht="16" r="195" s="53"/>
+    <row customHeight="1" ht="16" r="196" s="53"/>
+    <row customHeight="1" ht="16" r="197" s="53"/>
+    <row customHeight="1" ht="16" r="198" s="53"/>
+    <row customHeight="1" ht="16" r="199" s="53"/>
+    <row customHeight="1" ht="16" r="200" s="53"/>
+    <row customHeight="1" ht="16" r="201" s="53"/>
+    <row customHeight="1" ht="16" r="202" s="53"/>
+    <row customHeight="1" ht="16" r="203" s="53"/>
+    <row customHeight="1" ht="16" r="204" s="53"/>
+    <row customHeight="1" ht="16" r="205" s="53"/>
+    <row customHeight="1" ht="16" r="206" s="53"/>
+    <row customHeight="1" ht="16" r="207" s="53"/>
+    <row customHeight="1" ht="16" r="208" s="53"/>
+    <row customHeight="1" ht="16" r="209" s="53"/>
+    <row customHeight="1" ht="16" r="210" s="53"/>
+    <row customHeight="1" ht="16" r="211" s="53"/>
+    <row customHeight="1" ht="16" r="212" s="53"/>
+    <row customHeight="1" ht="16" r="213" s="53"/>
+    <row customHeight="1" ht="16" r="214" s="53"/>
+    <row customHeight="1" ht="16" r="215" s="53"/>
+    <row customHeight="1" ht="16" r="216" s="53"/>
+    <row customHeight="1" ht="16" r="217" s="53"/>
+    <row customHeight="1" ht="16" r="218" s="53"/>
+    <row customHeight="1" ht="16" r="219" s="53"/>
+    <row customHeight="1" ht="16" r="220" s="53"/>
+    <row customHeight="1" ht="16" r="221" s="53"/>
+    <row customHeight="1" ht="16" r="222" s="53"/>
+    <row customHeight="1" ht="16" r="223" s="53"/>
+    <row customHeight="1" ht="16" r="224" s="53"/>
+    <row customHeight="1" ht="16" r="225" s="53"/>
+    <row customHeight="1" ht="16" r="226" s="53"/>
+    <row customHeight="1" ht="16" r="227" s="53"/>
+    <row customHeight="1" ht="16" r="228" s="53"/>
+    <row customHeight="1" ht="16" r="229" s="53"/>
+    <row customHeight="1" ht="16" r="230" s="53"/>
+    <row customHeight="1" ht="16" r="231" s="53"/>
+    <row customHeight="1" ht="16" r="232" s="53"/>
+    <row customHeight="1" ht="16" r="233" s="53"/>
+    <row customHeight="1" ht="16" r="234" s="53"/>
+    <row customHeight="1" ht="16" r="235" s="53"/>
+    <row customHeight="1" ht="16" r="236" s="53"/>
+    <row customHeight="1" ht="16" r="237" s="53"/>
+    <row customHeight="1" ht="16" r="238" s="53"/>
+    <row customHeight="1" ht="16" r="239" s="53"/>
+    <row customHeight="1" ht="16" r="240" s="53"/>
+    <row customHeight="1" ht="16" r="241" s="53"/>
+    <row customHeight="1" ht="16" r="242" s="53"/>
+    <row customHeight="1" ht="16" r="243" s="53"/>
+    <row customHeight="1" ht="16" r="244" s="53"/>
+    <row customHeight="1" ht="16" r="245" s="53"/>
+    <row customHeight="1" ht="16" r="246" s="53"/>
+    <row customHeight="1" ht="16" r="247" s="53"/>
+    <row customHeight="1" ht="16" r="248" s="53"/>
+    <row customHeight="1" ht="16" r="249" s="53"/>
+    <row customHeight="1" ht="16" r="250" s="53"/>
+    <row customHeight="1" ht="16" r="251" s="53"/>
+    <row customHeight="1" ht="16" r="252" s="53"/>
+    <row customHeight="1" ht="16" r="253" s="53"/>
+    <row customHeight="1" ht="16" r="254" s="53"/>
+    <row customHeight="1" ht="16" r="255" s="53"/>
+    <row customHeight="1" ht="16" r="256" s="53"/>
+    <row customHeight="1" ht="16" r="257" s="53"/>
+    <row customHeight="1" ht="16" r="258" s="53"/>
+    <row customHeight="1" ht="16" r="259" s="53"/>
+    <row customHeight="1" ht="16" r="260" s="53"/>
+    <row customHeight="1" ht="16" r="261" s="53"/>
+    <row customHeight="1" ht="16" r="262" s="53"/>
   </sheetData>
   <autoFilter ref="A2:F61"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -4840,17 +4852,17 @@
   <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -4873,7 +4885,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>区域</t>
@@ -4959,7 +4971,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5002,7 +5014,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5047,7 +5059,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5084,7 +5096,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5129,7 +5141,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5168,7 +5180,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5205,7 +5217,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5234,7 +5246,7 @@
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5273,7 +5285,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5310,7 +5322,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5347,7 +5359,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5386,7 +5398,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5423,7 +5435,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5450,7 +5462,7 @@
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5478,7 +5490,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5506,7 +5518,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5534,7 +5546,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5564,7 +5576,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5594,7 +5606,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5630,7 +5642,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5658,7 +5670,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5688,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5726,7 +5738,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5756,7 +5768,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5788,7 +5800,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5822,7 +5834,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5854,7 +5866,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5882,7 +5894,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5918,7 +5930,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5945,7 +5957,7 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5977,7 +5989,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6009,7 +6021,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6034,7 +6046,7 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6064,7 +6076,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6094,7 +6106,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6128,7 +6140,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6158,7 +6170,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6186,7 +6198,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6214,7 +6226,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6242,7 +6254,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6270,7 +6282,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6298,7 +6310,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6326,7 +6338,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6354,7 +6366,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6382,7 +6394,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6420,7 +6432,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6450,7 +6462,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6486,7 +6498,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6520,7 +6532,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6556,7 +6568,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6588,7 +6600,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -7236,7 +7248,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -7249,17 +7261,17 @@
   <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -7282,7 +7294,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>区域</t>
@@ -7368,7 +7380,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7414,7 +7426,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7451,7 +7463,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7497,7 +7509,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7543,7 +7555,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7591,7 +7603,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7628,7 +7640,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7665,7 +7677,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7713,7 +7725,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7759,7 +7771,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7796,7 +7808,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7833,7 +7845,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7879,7 +7891,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7907,7 +7919,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7935,7 +7947,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7963,7 +7975,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7991,7 +8003,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8019,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8047,7 +8059,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8075,7 +8087,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8103,7 +8115,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8131,7 +8143,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8159,7 +8171,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8187,7 +8199,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8215,7 +8227,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8243,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8273,7 +8285,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8301,7 +8313,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8329,7 +8341,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8357,7 +8369,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8385,7 +8397,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8413,7 +8425,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8441,7 +8453,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8471,7 +8483,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8499,7 +8511,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8527,7 +8539,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8555,7 +8567,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8583,7 +8595,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8613,7 +8625,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8645,7 +8657,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8673,7 +8685,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8701,7 +8713,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8729,7 +8741,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8757,7 +8769,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8785,7 +8797,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8817,7 +8829,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8849,7 +8861,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -9525,7 +9537,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -9536,16 +9548,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -9555,7 +9567,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -9600,7 +9612,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9646,7 +9658,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9691,7 +9703,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9740,7 +9752,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9789,7 +9801,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9831,7 +9843,7 @@
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="35" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9866,7 +9878,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9906,7 +9918,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9942,7 +9954,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -9978,7 +9990,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10014,7 +10026,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10055,7 +10067,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10086,7 +10098,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10108,7 +10120,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10125,7 +10137,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10142,7 +10154,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10164,7 +10176,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10181,7 +10193,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10199,7 +10211,7 @@
       </c>
       <c r="D20" s="39" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10221,7 +10233,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10243,7 +10255,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10265,7 +10277,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10287,7 +10299,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10305,7 +10317,7 @@
       </c>
       <c r="D25" s="36" t="n"/>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10327,7 +10339,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10349,7 +10361,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10371,7 +10383,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10393,7 +10405,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10415,7 +10427,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10437,7 +10449,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10464,7 +10476,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10486,7 +10498,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10508,7 +10520,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10530,7 +10542,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10552,7 +10564,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10574,7 +10586,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10596,7 +10608,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10613,7 +10625,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10635,7 +10647,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10653,7 +10665,7 @@
       </c>
       <c r="D41" s="46" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10675,7 +10687,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10693,7 +10705,7 @@
       </c>
       <c r="D43" s="46" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10711,7 +10723,7 @@
       </c>
       <c r="E44" s="46" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10733,7 +10745,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10755,7 +10767,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10777,7 +10789,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10799,7 +10811,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10821,7 +10833,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10844,7 +10856,7 @@
       </c>
       <c r="E50" s="49" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10866,7 +10878,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10888,7 +10900,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="37" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -10910,7 +10922,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="55" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -10932,7 +10944,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="55" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10954,7 +10966,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10976,7 +10988,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10994,7 +11006,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -11005,18 +11017,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6.83203125" customWidth="1" style="23" min="1" max="1"/>
-    <col width="8.83203125" customWidth="1" style="23" min="2" max="2"/>
-    <col width="19.6640625" customWidth="1" style="23" min="3" max="3"/>
-    <col width="13" customWidth="1" style="23" min="4" max="4"/>
-    <col hidden="1" width="30.5" customWidth="1" style="23" min="5" max="6"/>
-    <col width="30.5" customWidth="1" style="23" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" style="23" min="8" max="26"/>
+    <col customWidth="1" max="1" min="1" style="23" width="6.83203125"/>
+    <col customWidth="1" max="2" min="2" style="23" width="8.83203125"/>
+    <col customWidth="1" max="3" min="3" style="23" width="19.6640625"/>
+    <col customWidth="1" max="4" min="4" style="23" width="13"/>
+    <col customWidth="1" hidden="1" max="6" min="5" style="23" width="30.5"/>
+    <col customWidth="1" max="7" min="7" style="23" width="30.5"/>
+    <col customWidth="1" max="26" min="8" style="23" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="1" s="53">
       <c r="A1" s="21" t="n"/>
       <c r="B1" s="22" t="inlineStr">
         <is>
@@ -11058,7 +11070,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="2" s="53">
       <c r="A2" s="24" t="n">
         <v>1</v>
       </c>
@@ -11101,7 +11113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="3" s="53">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -11134,7 +11146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="4" s="53">
       <c r="A4" s="24" t="n">
         <v>3</v>
       </c>
@@ -11172,7 +11184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="5" s="53">
       <c r="A5" s="24" t="n">
         <v>4</v>
       </c>
@@ -11215,7 +11227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="6" s="53">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -11248,7 +11260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="7" s="53">
       <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
@@ -11277,7 +11289,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="8" s="53">
       <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
@@ -11307,7 +11319,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="9" s="53">
       <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
@@ -11332,7 +11344,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="10" s="53">
       <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
@@ -11357,7 +11369,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="11" s="53">
       <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
@@ -11387,7 +11399,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="12" s="53">
       <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
@@ -11412,7 +11424,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="13" s="53">
       <c r="A13" s="24" t="n">
         <v>4</v>
       </c>
@@ -11442,7 +11454,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="14" s="53">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
@@ -11462,7 +11474,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="15" s="53">
       <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
@@ -11492,7 +11504,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="16" s="53">
       <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
@@ -11517,7 +11529,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="17" s="53">
       <c r="A17" s="24" t="n">
         <v>2</v>
       </c>
@@ -11552,7 +11564,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="18" s="53">
       <c r="A18" s="24" t="n">
         <v>3</v>
       </c>
@@ -11587,7 +11599,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="19" s="53">
       <c r="A19" s="24" t="n">
         <v>4</v>
       </c>
@@ -11612,7 +11624,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="20" s="53">
       <c r="A20" s="24" t="n">
         <v>5</v>
       </c>
@@ -11642,7 +11654,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="21" s="53">
       <c r="A21" s="24" t="n">
         <v>6</v>
       </c>
@@ -11672,7 +11684,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="22" s="53">
       <c r="A22" s="24" t="n">
         <v>7</v>
       </c>
@@ -11702,7 +11714,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="23" s="53">
       <c r="A23" s="24" t="n">
         <v>8</v>
       </c>
@@ -11732,7 +11744,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="24" s="53">
       <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
@@ -11762,7 +11774,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="25" s="53">
       <c r="A25" s="24" t="n">
         <v>2</v>
       </c>
@@ -11792,7 +11804,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="26" s="53">
       <c r="A26" s="24" t="n">
         <v>3</v>
       </c>
@@ -11817,7 +11829,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="27" s="53">
       <c r="A27" s="24" t="n">
         <v>4</v>
       </c>
@@ -11847,7 +11859,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="28" s="53">
       <c r="A28" s="24" t="n">
         <v>5</v>
       </c>
@@ -11877,7 +11889,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="29" s="53">
       <c r="A29" s="24" t="n">
         <v>6</v>
       </c>
@@ -11907,7 +11919,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="30" s="53">
       <c r="A30" s="24" t="n">
         <v>7</v>
       </c>
@@ -11942,7 +11954,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="31" s="53">
       <c r="A31" s="24" t="n">
         <v>8</v>
       </c>
@@ -11972,7 +11984,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="32" s="53">
       <c r="A32" s="24" t="n">
         <v>1</v>
       </c>
@@ -12002,7 +12014,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="33" s="53">
       <c r="A33" s="24" t="n">
         <v>2</v>
       </c>
@@ -12032,7 +12044,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="34" s="53">
       <c r="A34" s="24" t="n">
         <v>3</v>
       </c>
@@ -12062,7 +12074,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="35" s="53">
       <c r="A35" s="24" t="n">
         <v>4</v>
       </c>
@@ -12092,7 +12104,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="36" s="53">
       <c r="A36" s="24" t="n">
         <v>1</v>
       </c>
@@ -12122,7 +12134,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="37" s="53">
       <c r="A37" s="24" t="n">
         <v>2</v>
       </c>
@@ -12157,7 +12169,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="38" s="53">
       <c r="A38" s="24" t="n">
         <v>3</v>
       </c>
@@ -12188,6 +12200,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46229</v>
+        <v>46232</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D34" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发1次</t>
+          <t>累计未发2次，迟发1次</t>
         </is>
       </c>
       <c r="E34" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D10" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发4次</t>
+          <t>累计未发2次，迟发4次</t>
         </is>
       </c>
       <c r="E10" s="69" t="n"/>
@@ -4194,7 +4194,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D48" s="71" t="n"/>
+      <c r="D48" s="71" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E48" s="69" t="n"/>
       <c r="F48" s="63" t="inlineStr">
         <is>
@@ -4495,7 +4499,7 @@
       </c>
       <c r="D59" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发1次</t>
+          <t>累计未发1次，迟发2次</t>
         </is>
       </c>
       <c r="E59" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46236</v>
+        <v>46239</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D26" s="68" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E26" s="69" t="n"/>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D27" s="71" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E27" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46239</v>
+        <v>46243</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2764,7 +2764,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D4" s="71" t="n"/>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E4" s="69" t="n"/>
       <c r="F4" s="63" t="inlineStr">
         <is>
@@ -4059,7 +4063,7 @@
       </c>
       <c r="D43" s="68" t="inlineStr">
         <is>
-          <t>迟发2次</t>
+          <t>累计未发1次，迟发2次</t>
         </is>
       </c>
       <c r="E43" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D30" s="68" t="inlineStr">
         <is>
-          <t>迟发3次</t>
+          <t>累计未发1次，迟发3次</t>
         </is>
       </c>
       <c r="E30" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D4" s="71" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E4" s="69" t="n"/>
@@ -3679,7 +3679,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D29" s="70" t="n"/>
+      <c r="D29" s="70" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E29" s="69" t="n"/>
       <c r="F29" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16400" windowWidth="27040" xWindow="0" yWindow="500"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'2026年日报'!$A$2:$F$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,257 +449,257 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf applyAlignment="1" borderId="7" fillId="7" fontId="0" numFmtId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="83">
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="5" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="2" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="6" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="9" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="10" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="11" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="12" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="16" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="13" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="17" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="17" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="14" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="18" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="9" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="19" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="20" fillId="7" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="19" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="8" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="常规" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1073,16 +1073,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1472,7 +1472,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1642,7 +1642,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D40" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D48" s="51" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="53" s="53">
+    <row r="53" ht="16.5" customHeight="1" s="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2618,17 +2618,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <dimension ref="A1:O65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -2638,7 +2638,7 @@
         <v>46245</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>区域</t>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2748,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2812,7 +2812,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2876,7 +2876,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2931,7 +2931,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3028,7 +3028,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3070,7 +3070,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3162,7 +3162,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3246,7 +3246,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3283,7 +3283,7 @@
         <v/>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="15" s="78">
+    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A15" s="61" t="inlineStr">
         <is>
           <t>粤西区</t>
@@ -3314,7 +3314,7 @@
       <c r="H15" s="23" t="n"/>
       <c r="J15" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G17" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="G18" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G19" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G20" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G21" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G22" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G23" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G24" s="67" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="25" s="78">
+    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A25" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3578,7 +3578,7 @@
       <c r="H25" s="67" t="n"/>
       <c r="J25" s="67" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="16.5" r="26" s="78">
+    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="78">
       <c r="A26" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3609,7 +3609,7 @@
       <c r="H26" s="67" t="n"/>
       <c r="J26" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="G27" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G28" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="G29" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G30" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G31" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="G32" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G33" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G34" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G35" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G36" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="G37" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G38" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G39" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="G40" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G41" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="G42" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G43" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G44" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G45" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G46" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G47" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="G48" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G49" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G50" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G51" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="G52" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16" r="53" s="53">
+    <row r="53" ht="16" customHeight="1" s="53">
       <c r="A53" s="72" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G53" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="58" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="G54" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="55" s="53">
+    <row r="55" ht="16.5" customHeight="1" s="53">
       <c r="A55" s="58" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G55" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="56" s="53">
+    <row r="56" ht="16.5" customHeight="1" s="53">
       <c r="A56" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G56" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="57" s="53">
+    <row r="57" ht="16.5" customHeight="1" s="53">
       <c r="A57" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="G57" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="58" s="53">
+    <row r="58" ht="16.5" customHeight="1" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
           <t>华北分公司</t>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="G58" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="59" s="53">
+    <row r="59" ht="16.5" customHeight="1" s="53">
       <c r="A59" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="G59" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="60" s="53">
+    <row r="60" ht="16.5" customHeight="1" s="53">
       <c r="A60" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G60" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="61" s="53">
+    <row r="61" ht="16.5" customHeight="1" s="53">
       <c r="A61" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G61" s="67" t="n"/>
     </row>
-    <row customHeight="1" ht="16" r="62" s="53">
+    <row r="62" ht="16" customHeight="1" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="63" s="53">
+    <row r="63" ht="16" customHeight="1" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="64" s="53">
+    <row r="64" ht="16" customHeight="1" s="53">
       <c r="A64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4651,207 +4651,228 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="65" s="53"/>
-    <row customHeight="1" ht="16" r="66" s="53"/>
-    <row customHeight="1" ht="16" r="67" s="53"/>
-    <row customHeight="1" ht="16" r="68" s="53"/>
-    <row customHeight="1" ht="16" r="69" s="53"/>
-    <row customHeight="1" ht="16" r="70" s="53"/>
-    <row customHeight="1" ht="16" r="71" s="53"/>
-    <row customHeight="1" ht="16" r="72" s="53"/>
-    <row customHeight="1" ht="16" r="73" s="53"/>
-    <row customHeight="1" ht="16" r="74" s="53"/>
-    <row customHeight="1" ht="16" r="75" s="53"/>
-    <row customHeight="1" ht="16" r="76" s="53"/>
-    <row customHeight="1" ht="16" r="77" s="53"/>
-    <row customHeight="1" ht="16" r="78" s="53"/>
-    <row customHeight="1" ht="16" r="79" s="53"/>
-    <row customHeight="1" ht="16" r="80" s="53"/>
-    <row customHeight="1" ht="16" r="81" s="53"/>
-    <row customHeight="1" ht="16" r="82" s="53"/>
-    <row customHeight="1" ht="16" r="83" s="53"/>
-    <row customHeight="1" ht="16" r="84" s="53"/>
-    <row customHeight="1" ht="16" r="85" s="53"/>
-    <row customHeight="1" ht="16" r="86" s="53"/>
-    <row customHeight="1" ht="16" r="87" s="53"/>
-    <row customHeight="1" ht="16" r="88" s="53"/>
-    <row customHeight="1" ht="16" r="89" s="53"/>
-    <row customHeight="1" ht="16" r="90" s="53"/>
-    <row customHeight="1" ht="16" r="91" s="53"/>
-    <row customHeight="1" ht="16" r="92" s="53"/>
-    <row customHeight="1" ht="16" r="93" s="53"/>
-    <row customHeight="1" ht="16" r="94" s="53"/>
-    <row customHeight="1" ht="16" r="95" s="53"/>
-    <row customHeight="1" ht="16" r="96" s="53"/>
-    <row customHeight="1" ht="16" r="97" s="53"/>
-    <row customHeight="1" ht="16" r="98" s="53"/>
-    <row customHeight="1" ht="16" r="99" s="53"/>
-    <row customHeight="1" ht="16" r="100" s="53"/>
-    <row customHeight="1" ht="16" r="101" s="53"/>
-    <row customHeight="1" ht="16" r="102" s="53"/>
-    <row customHeight="1" ht="16" r="103" s="53"/>
-    <row customHeight="1" ht="16" r="104" s="53"/>
-    <row customHeight="1" ht="16" r="105" s="53"/>
-    <row customHeight="1" ht="16" r="106" s="53"/>
-    <row customHeight="1" ht="16" r="107" s="53"/>
-    <row customHeight="1" ht="16" r="108" s="53"/>
-    <row customHeight="1" ht="16" r="109" s="53"/>
-    <row customHeight="1" ht="16" r="110" s="53"/>
-    <row customHeight="1" ht="16" r="111" s="53"/>
-    <row customHeight="1" ht="16" r="112" s="53"/>
-    <row customHeight="1" ht="16" r="113" s="53"/>
-    <row customHeight="1" ht="16" r="114" s="53"/>
-    <row customHeight="1" ht="16" r="115" s="53"/>
-    <row customHeight="1" ht="16" r="116" s="53"/>
-    <row customHeight="1" ht="16" r="117" s="53"/>
-    <row customHeight="1" ht="16" r="118" s="53"/>
-    <row customHeight="1" ht="16" r="119" s="53"/>
-    <row customHeight="1" ht="16" r="120" s="53"/>
-    <row customHeight="1" ht="16" r="121" s="53"/>
-    <row customHeight="1" ht="16" r="122" s="53"/>
-    <row customHeight="1" ht="16" r="123" s="53"/>
-    <row customHeight="1" ht="16" r="124" s="53"/>
-    <row customHeight="1" ht="16" r="125" s="53"/>
-    <row customHeight="1" ht="16" r="126" s="53"/>
-    <row customHeight="1" ht="16" r="127" s="53"/>
-    <row customHeight="1" ht="16" r="128" s="53"/>
-    <row customHeight="1" ht="16" r="129" s="53"/>
-    <row customHeight="1" ht="16" r="130" s="53"/>
-    <row customHeight="1" ht="16" r="131" s="53"/>
-    <row customHeight="1" ht="16" r="132" s="53"/>
-    <row customHeight="1" ht="16" r="133" s="53"/>
-    <row customHeight="1" ht="16" r="134" s="53"/>
-    <row customHeight="1" ht="16" r="135" s="53"/>
-    <row customHeight="1" ht="16" r="136" s="53"/>
-    <row customHeight="1" ht="16" r="137" s="53"/>
-    <row customHeight="1" ht="16" r="138" s="53"/>
-    <row customHeight="1" ht="16" r="139" s="53"/>
-    <row customHeight="1" ht="16" r="140" s="53"/>
-    <row customHeight="1" ht="16" r="141" s="53"/>
-    <row customHeight="1" ht="16" r="142" s="53"/>
-    <row customHeight="1" ht="16" r="143" s="53"/>
-    <row customHeight="1" ht="16" r="144" s="53"/>
-    <row customHeight="1" ht="16" r="145" s="53"/>
-    <row customHeight="1" ht="16" r="146" s="53"/>
-    <row customHeight="1" ht="16" r="147" s="53"/>
-    <row customHeight="1" ht="16" r="148" s="53"/>
-    <row customHeight="1" ht="16" r="149" s="53"/>
-    <row customHeight="1" ht="16" r="150" s="53"/>
-    <row customHeight="1" ht="16" r="151" s="53"/>
-    <row customHeight="1" ht="16" r="152" s="53"/>
-    <row customHeight="1" ht="16" r="153" s="53"/>
-    <row customHeight="1" ht="16" r="154" s="53"/>
-    <row customHeight="1" ht="16" r="155" s="53"/>
-    <row customHeight="1" ht="16" r="156" s="53"/>
-    <row customHeight="1" ht="16" r="157" s="53"/>
-    <row customHeight="1" ht="16" r="158" s="53"/>
-    <row customHeight="1" ht="16" r="159" s="53"/>
-    <row customHeight="1" ht="16" r="160" s="53"/>
-    <row customHeight="1" ht="16" r="161" s="53"/>
-    <row customHeight="1" ht="16" r="162" s="53"/>
-    <row customHeight="1" ht="16" r="163" s="53"/>
-    <row customHeight="1" ht="16" r="164" s="53"/>
-    <row customHeight="1" ht="16" r="165" s="53"/>
-    <row customHeight="1" ht="16" r="166" s="53"/>
-    <row customHeight="1" ht="16" r="167" s="53"/>
-    <row customHeight="1" ht="16" r="168" s="53"/>
-    <row customHeight="1" ht="16" r="169" s="53"/>
-    <row customHeight="1" ht="16" r="170" s="53"/>
-    <row customHeight="1" ht="16" r="171" s="53"/>
-    <row customHeight="1" ht="16" r="172" s="53"/>
-    <row customHeight="1" ht="16" r="173" s="53"/>
-    <row customHeight="1" ht="16" r="174" s="53"/>
-    <row customHeight="1" ht="16" r="175" s="53"/>
-    <row customHeight="1" ht="16" r="176" s="53"/>
-    <row customHeight="1" ht="16" r="177" s="53"/>
-    <row customHeight="1" ht="16" r="178" s="53"/>
-    <row customHeight="1" ht="16" r="179" s="53"/>
-    <row customHeight="1" ht="16" r="180" s="53"/>
-    <row customHeight="1" ht="16" r="181" s="53"/>
-    <row customHeight="1" ht="16" r="182" s="53"/>
-    <row customHeight="1" ht="16" r="183" s="53"/>
-    <row customHeight="1" ht="16" r="184" s="53"/>
-    <row customHeight="1" ht="16" r="185" s="53"/>
-    <row customHeight="1" ht="16" r="186" s="53"/>
-    <row customHeight="1" ht="16" r="187" s="53"/>
-    <row customHeight="1" ht="16" r="188" s="53"/>
-    <row customHeight="1" ht="16" r="189" s="53"/>
-    <row customHeight="1" ht="16" r="190" s="53"/>
-    <row customHeight="1" ht="16" r="191" s="53"/>
-    <row customHeight="1" ht="16" r="192" s="53"/>
-    <row customHeight="1" ht="16" r="193" s="53"/>
-    <row customHeight="1" ht="16" r="194" s="53"/>
-    <row customHeight="1" ht="16" r="195" s="53"/>
-    <row customHeight="1" ht="16" r="196" s="53"/>
-    <row customHeight="1" ht="16" r="197" s="53"/>
-    <row customHeight="1" ht="16" r="198" s="53"/>
-    <row customHeight="1" ht="16" r="199" s="53"/>
-    <row customHeight="1" ht="16" r="200" s="53"/>
-    <row customHeight="1" ht="16" r="201" s="53"/>
-    <row customHeight="1" ht="16" r="202" s="53"/>
-    <row customHeight="1" ht="16" r="203" s="53"/>
-    <row customHeight="1" ht="16" r="204" s="53"/>
-    <row customHeight="1" ht="16" r="205" s="53"/>
-    <row customHeight="1" ht="16" r="206" s="53"/>
-    <row customHeight="1" ht="16" r="207" s="53"/>
-    <row customHeight="1" ht="16" r="208" s="53"/>
-    <row customHeight="1" ht="16" r="209" s="53"/>
-    <row customHeight="1" ht="16" r="210" s="53"/>
-    <row customHeight="1" ht="16" r="211" s="53"/>
-    <row customHeight="1" ht="16" r="212" s="53"/>
-    <row customHeight="1" ht="16" r="213" s="53"/>
-    <row customHeight="1" ht="16" r="214" s="53"/>
-    <row customHeight="1" ht="16" r="215" s="53"/>
-    <row customHeight="1" ht="16" r="216" s="53"/>
-    <row customHeight="1" ht="16" r="217" s="53"/>
-    <row customHeight="1" ht="16" r="218" s="53"/>
-    <row customHeight="1" ht="16" r="219" s="53"/>
-    <row customHeight="1" ht="16" r="220" s="53"/>
-    <row customHeight="1" ht="16" r="221" s="53"/>
-    <row customHeight="1" ht="16" r="222" s="53"/>
-    <row customHeight="1" ht="16" r="223" s="53"/>
-    <row customHeight="1" ht="16" r="224" s="53"/>
-    <row customHeight="1" ht="16" r="225" s="53"/>
-    <row customHeight="1" ht="16" r="226" s="53"/>
-    <row customHeight="1" ht="16" r="227" s="53"/>
-    <row customHeight="1" ht="16" r="228" s="53"/>
-    <row customHeight="1" ht="16" r="229" s="53"/>
-    <row customHeight="1" ht="16" r="230" s="53"/>
-    <row customHeight="1" ht="16" r="231" s="53"/>
-    <row customHeight="1" ht="16" r="232" s="53"/>
-    <row customHeight="1" ht="16" r="233" s="53"/>
-    <row customHeight="1" ht="16" r="234" s="53"/>
-    <row customHeight="1" ht="16" r="235" s="53"/>
-    <row customHeight="1" ht="16" r="236" s="53"/>
-    <row customHeight="1" ht="16" r="237" s="53"/>
-    <row customHeight="1" ht="16" r="238" s="53"/>
-    <row customHeight="1" ht="16" r="239" s="53"/>
-    <row customHeight="1" ht="16" r="240" s="53"/>
-    <row customHeight="1" ht="16" r="241" s="53"/>
-    <row customHeight="1" ht="16" r="242" s="53"/>
-    <row customHeight="1" ht="16" r="243" s="53"/>
-    <row customHeight="1" ht="16" r="244" s="53"/>
-    <row customHeight="1" ht="16" r="245" s="53"/>
-    <row customHeight="1" ht="16" r="246" s="53"/>
-    <row customHeight="1" ht="16" r="247" s="53"/>
-    <row customHeight="1" ht="16" r="248" s="53"/>
-    <row customHeight="1" ht="16" r="249" s="53"/>
-    <row customHeight="1" ht="16" r="250" s="53"/>
-    <row customHeight="1" ht="16" r="251" s="53"/>
-    <row customHeight="1" ht="16" r="252" s="53"/>
-    <row customHeight="1" ht="16" r="253" s="53"/>
-    <row customHeight="1" ht="16" r="254" s="53"/>
-    <row customHeight="1" ht="16" r="255" s="53"/>
-    <row customHeight="1" ht="16" r="256" s="53"/>
-    <row customHeight="1" ht="16" r="257" s="53"/>
-    <row customHeight="1" ht="16" r="258" s="53"/>
-    <row customHeight="1" ht="16" r="259" s="53"/>
-    <row customHeight="1" ht="16" r="260" s="53"/>
-    <row customHeight="1" ht="16" r="261" s="53"/>
-    <row customHeight="1" ht="16" r="262" s="53"/>
+    <row r="65" ht="16" customHeight="1" s="53">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>华东分公司</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>南京江宁中心</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>华东分公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1" s="53"/>
+    <row r="67" ht="16" customHeight="1" s="53"/>
+    <row r="68" ht="16" customHeight="1" s="53"/>
+    <row r="69" ht="16" customHeight="1" s="53"/>
+    <row r="70" ht="16" customHeight="1" s="53"/>
+    <row r="71" ht="16" customHeight="1" s="53"/>
+    <row r="72" ht="16" customHeight="1" s="53"/>
+    <row r="73" ht="16" customHeight="1" s="53"/>
+    <row r="74" ht="16" customHeight="1" s="53"/>
+    <row r="75" ht="16" customHeight="1" s="53"/>
+    <row r="76" ht="16" customHeight="1" s="53"/>
+    <row r="77" ht="16" customHeight="1" s="53"/>
+    <row r="78" ht="16" customHeight="1" s="53"/>
+    <row r="79" ht="16" customHeight="1" s="53"/>
+    <row r="80" ht="16" customHeight="1" s="53"/>
+    <row r="81" ht="16" customHeight="1" s="53"/>
+    <row r="82" ht="16" customHeight="1" s="53"/>
+    <row r="83" ht="16" customHeight="1" s="53"/>
+    <row r="84" ht="16" customHeight="1" s="53"/>
+    <row r="85" ht="16" customHeight="1" s="53"/>
+    <row r="86" ht="16" customHeight="1" s="53"/>
+    <row r="87" ht="16" customHeight="1" s="53"/>
+    <row r="88" ht="16" customHeight="1" s="53"/>
+    <row r="89" ht="16" customHeight="1" s="53"/>
+    <row r="90" ht="16" customHeight="1" s="53"/>
+    <row r="91" ht="16" customHeight="1" s="53"/>
+    <row r="92" ht="16" customHeight="1" s="53"/>
+    <row r="93" ht="16" customHeight="1" s="53"/>
+    <row r="94" ht="16" customHeight="1" s="53"/>
+    <row r="95" ht="16" customHeight="1" s="53"/>
+    <row r="96" ht="16" customHeight="1" s="53"/>
+    <row r="97" ht="16" customHeight="1" s="53"/>
+    <row r="98" ht="16" customHeight="1" s="53"/>
+    <row r="99" ht="16" customHeight="1" s="53"/>
+    <row r="100" ht="16" customHeight="1" s="53"/>
+    <row r="101" ht="16" customHeight="1" s="53"/>
+    <row r="102" ht="16" customHeight="1" s="53"/>
+    <row r="103" ht="16" customHeight="1" s="53"/>
+    <row r="104" ht="16" customHeight="1" s="53"/>
+    <row r="105" ht="16" customHeight="1" s="53"/>
+    <row r="106" ht="16" customHeight="1" s="53"/>
+    <row r="107" ht="16" customHeight="1" s="53"/>
+    <row r="108" ht="16" customHeight="1" s="53"/>
+    <row r="109" ht="16" customHeight="1" s="53"/>
+    <row r="110" ht="16" customHeight="1" s="53"/>
+    <row r="111" ht="16" customHeight="1" s="53"/>
+    <row r="112" ht="16" customHeight="1" s="53"/>
+    <row r="113" ht="16" customHeight="1" s="53"/>
+    <row r="114" ht="16" customHeight="1" s="53"/>
+    <row r="115" ht="16" customHeight="1" s="53"/>
+    <row r="116" ht="16" customHeight="1" s="53"/>
+    <row r="117" ht="16" customHeight="1" s="53"/>
+    <row r="118" ht="16" customHeight="1" s="53"/>
+    <row r="119" ht="16" customHeight="1" s="53"/>
+    <row r="120" ht="16" customHeight="1" s="53"/>
+    <row r="121" ht="16" customHeight="1" s="53"/>
+    <row r="122" ht="16" customHeight="1" s="53"/>
+    <row r="123" ht="16" customHeight="1" s="53"/>
+    <row r="124" ht="16" customHeight="1" s="53"/>
+    <row r="125" ht="16" customHeight="1" s="53"/>
+    <row r="126" ht="16" customHeight="1" s="53"/>
+    <row r="127" ht="16" customHeight="1" s="53"/>
+    <row r="128" ht="16" customHeight="1" s="53"/>
+    <row r="129" ht="16" customHeight="1" s="53"/>
+    <row r="130" ht="16" customHeight="1" s="53"/>
+    <row r="131" ht="16" customHeight="1" s="53"/>
+    <row r="132" ht="16" customHeight="1" s="53"/>
+    <row r="133" ht="16" customHeight="1" s="53"/>
+    <row r="134" ht="16" customHeight="1" s="53"/>
+    <row r="135" ht="16" customHeight="1" s="53"/>
+    <row r="136" ht="16" customHeight="1" s="53"/>
+    <row r="137" ht="16" customHeight="1" s="53"/>
+    <row r="138" ht="16" customHeight="1" s="53"/>
+    <row r="139" ht="16" customHeight="1" s="53"/>
+    <row r="140" ht="16" customHeight="1" s="53"/>
+    <row r="141" ht="16" customHeight="1" s="53"/>
+    <row r="142" ht="16" customHeight="1" s="53"/>
+    <row r="143" ht="16" customHeight="1" s="53"/>
+    <row r="144" ht="16" customHeight="1" s="53"/>
+    <row r="145" ht="16" customHeight="1" s="53"/>
+    <row r="146" ht="16" customHeight="1" s="53"/>
+    <row r="147" ht="16" customHeight="1" s="53"/>
+    <row r="148" ht="16" customHeight="1" s="53"/>
+    <row r="149" ht="16" customHeight="1" s="53"/>
+    <row r="150" ht="16" customHeight="1" s="53"/>
+    <row r="151" ht="16" customHeight="1" s="53"/>
+    <row r="152" ht="16" customHeight="1" s="53"/>
+    <row r="153" ht="16" customHeight="1" s="53"/>
+    <row r="154" ht="16" customHeight="1" s="53"/>
+    <row r="155" ht="16" customHeight="1" s="53"/>
+    <row r="156" ht="16" customHeight="1" s="53"/>
+    <row r="157" ht="16" customHeight="1" s="53"/>
+    <row r="158" ht="16" customHeight="1" s="53"/>
+    <row r="159" ht="16" customHeight="1" s="53"/>
+    <row r="160" ht="16" customHeight="1" s="53"/>
+    <row r="161" ht="16" customHeight="1" s="53"/>
+    <row r="162" ht="16" customHeight="1" s="53"/>
+    <row r="163" ht="16" customHeight="1" s="53"/>
+    <row r="164" ht="16" customHeight="1" s="53"/>
+    <row r="165" ht="16" customHeight="1" s="53"/>
+    <row r="166" ht="16" customHeight="1" s="53"/>
+    <row r="167" ht="16" customHeight="1" s="53"/>
+    <row r="168" ht="16" customHeight="1" s="53"/>
+    <row r="169" ht="16" customHeight="1" s="53"/>
+    <row r="170" ht="16" customHeight="1" s="53"/>
+    <row r="171" ht="16" customHeight="1" s="53"/>
+    <row r="172" ht="16" customHeight="1" s="53"/>
+    <row r="173" ht="16" customHeight="1" s="53"/>
+    <row r="174" ht="16" customHeight="1" s="53"/>
+    <row r="175" ht="16" customHeight="1" s="53"/>
+    <row r="176" ht="16" customHeight="1" s="53"/>
+    <row r="177" ht="16" customHeight="1" s="53"/>
+    <row r="178" ht="16" customHeight="1" s="53"/>
+    <row r="179" ht="16" customHeight="1" s="53"/>
+    <row r="180" ht="16" customHeight="1" s="53"/>
+    <row r="181" ht="16" customHeight="1" s="53"/>
+    <row r="182" ht="16" customHeight="1" s="53"/>
+    <row r="183" ht="16" customHeight="1" s="53"/>
+    <row r="184" ht="16" customHeight="1" s="53"/>
+    <row r="185" ht="16" customHeight="1" s="53"/>
+    <row r="186" ht="16" customHeight="1" s="53"/>
+    <row r="187" ht="16" customHeight="1" s="53"/>
+    <row r="188" ht="16" customHeight="1" s="53"/>
+    <row r="189" ht="16" customHeight="1" s="53"/>
+    <row r="190" ht="16" customHeight="1" s="53"/>
+    <row r="191" ht="16" customHeight="1" s="53"/>
+    <row r="192" ht="16" customHeight="1" s="53"/>
+    <row r="193" ht="16" customHeight="1" s="53"/>
+    <row r="194" ht="16" customHeight="1" s="53"/>
+    <row r="195" ht="16" customHeight="1" s="53"/>
+    <row r="196" ht="16" customHeight="1" s="53"/>
+    <row r="197" ht="16" customHeight="1" s="53"/>
+    <row r="198" ht="16" customHeight="1" s="53"/>
+    <row r="199" ht="16" customHeight="1" s="53"/>
+    <row r="200" ht="16" customHeight="1" s="53"/>
+    <row r="201" ht="16" customHeight="1" s="53"/>
+    <row r="202" ht="16" customHeight="1" s="53"/>
+    <row r="203" ht="16" customHeight="1" s="53"/>
+    <row r="204" ht="16" customHeight="1" s="53"/>
+    <row r="205" ht="16" customHeight="1" s="53"/>
+    <row r="206" ht="16" customHeight="1" s="53"/>
+    <row r="207" ht="16" customHeight="1" s="53"/>
+    <row r="208" ht="16" customHeight="1" s="53"/>
+    <row r="209" ht="16" customHeight="1" s="53"/>
+    <row r="210" ht="16" customHeight="1" s="53"/>
+    <row r="211" ht="16" customHeight="1" s="53"/>
+    <row r="212" ht="16" customHeight="1" s="53"/>
+    <row r="213" ht="16" customHeight="1" s="53"/>
+    <row r="214" ht="16" customHeight="1" s="53"/>
+    <row r="215" ht="16" customHeight="1" s="53"/>
+    <row r="216" ht="16" customHeight="1" s="53"/>
+    <row r="217" ht="16" customHeight="1" s="53"/>
+    <row r="218" ht="16" customHeight="1" s="53"/>
+    <row r="219" ht="16" customHeight="1" s="53"/>
+    <row r="220" ht="16" customHeight="1" s="53"/>
+    <row r="221" ht="16" customHeight="1" s="53"/>
+    <row r="222" ht="16" customHeight="1" s="53"/>
+    <row r="223" ht="16" customHeight="1" s="53"/>
+    <row r="224" ht="16" customHeight="1" s="53"/>
+    <row r="225" ht="16" customHeight="1" s="53"/>
+    <row r="226" ht="16" customHeight="1" s="53"/>
+    <row r="227" ht="16" customHeight="1" s="53"/>
+    <row r="228" ht="16" customHeight="1" s="53"/>
+    <row r="229" ht="16" customHeight="1" s="53"/>
+    <row r="230" ht="16" customHeight="1" s="53"/>
+    <row r="231" ht="16" customHeight="1" s="53"/>
+    <row r="232" ht="16" customHeight="1" s="53"/>
+    <row r="233" ht="16" customHeight="1" s="53"/>
+    <row r="234" ht="16" customHeight="1" s="53"/>
+    <row r="235" ht="16" customHeight="1" s="53"/>
+    <row r="236" ht="16" customHeight="1" s="53"/>
+    <row r="237" ht="16" customHeight="1" s="53"/>
+    <row r="238" ht="16" customHeight="1" s="53"/>
+    <row r="239" ht="16" customHeight="1" s="53"/>
+    <row r="240" ht="16" customHeight="1" s="53"/>
+    <row r="241" ht="16" customHeight="1" s="53"/>
+    <row r="242" ht="16" customHeight="1" s="53"/>
+    <row r="243" ht="16" customHeight="1" s="53"/>
+    <row r="244" ht="16" customHeight="1" s="53"/>
+    <row r="245" ht="16" customHeight="1" s="53"/>
+    <row r="246" ht="16" customHeight="1" s="53"/>
+    <row r="247" ht="16" customHeight="1" s="53"/>
+    <row r="248" ht="16" customHeight="1" s="53"/>
+    <row r="249" ht="16" customHeight="1" s="53"/>
+    <row r="250" ht="16" customHeight="1" s="53"/>
+    <row r="251" ht="16" customHeight="1" s="53"/>
+    <row r="252" ht="16" customHeight="1" s="53"/>
+    <row r="253" ht="16" customHeight="1" s="53"/>
+    <row r="254" ht="16" customHeight="1" s="53"/>
+    <row r="255" ht="16" customHeight="1" s="53"/>
+    <row r="256" ht="16" customHeight="1" s="53"/>
+    <row r="257" ht="16" customHeight="1" s="53"/>
+    <row r="258" ht="16" customHeight="1" s="53"/>
+    <row r="259" ht="16" customHeight="1" s="53"/>
+    <row r="260" ht="16" customHeight="1" s="53"/>
+    <row r="261" ht="16" customHeight="1" s="53"/>
+    <row r="262" ht="16" customHeight="1" s="53"/>
   </sheetData>
   <autoFilter ref="A2:F61"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4864,17 +4885,17 @@
   <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
-    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
-    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
-    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
-    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
-    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
-    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
-    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
+    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
+    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
+    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
+    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
+    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
+    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
+    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
+    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="22.5" r="1" s="53">
+    <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -4897,7 +4918,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>区域</t>
@@ -4983,7 +5004,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5026,7 +5047,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5071,7 +5092,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5108,7 +5129,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5153,7 +5174,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5192,7 +5213,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5229,7 +5250,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5258,7 +5279,7 @@
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5297,7 +5318,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5334,7 +5355,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5371,7 +5392,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5410,7 +5431,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5447,7 +5468,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5474,7 +5495,7 @@
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5502,7 +5523,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5530,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5558,7 +5579,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5588,7 +5609,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5618,7 +5639,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5654,7 +5675,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5682,7 +5703,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5712,7 +5733,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5750,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5780,7 +5801,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5812,7 +5833,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5846,7 +5867,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5878,7 +5899,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5906,7 +5927,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5942,7 +5963,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5969,7 +5990,7 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6001,7 +6022,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6033,7 +6054,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6058,7 +6079,7 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6088,7 +6109,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6118,7 +6139,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6152,7 +6173,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6182,7 +6203,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6210,7 +6231,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6238,7 +6259,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6266,7 +6287,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6294,7 +6315,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6322,7 +6343,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6350,7 +6371,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6378,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6406,7 +6427,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6444,7 +6465,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6474,7 +6495,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6510,7 +6531,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6544,7 +6565,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6580,7 +6601,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6612,7 +6633,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="53" s="53">
+    <row r="53" ht="16.5" customHeight="1" s="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -7260,7 +7281,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7273,17 +7294,17 @@
   <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
-    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
-    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
-    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
-    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
-    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
-    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
-    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
+    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
+    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
+    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
+    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
+    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
+    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
+    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
+    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="22.5" r="1" s="53">
+    <row r="1" ht="22.5" customHeight="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -7306,7 +7327,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>区域</t>
@@ -7392,7 +7413,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7438,7 +7459,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7475,7 +7496,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7521,7 +7542,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7567,7 +7588,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7615,7 +7636,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7652,7 +7673,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7689,7 +7710,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7737,7 +7758,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7783,7 +7804,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7820,7 +7841,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7857,7 +7878,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7903,7 +7924,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7931,7 +7952,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7959,7 +7980,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7987,7 +8008,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -8015,7 +8036,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8043,7 +8064,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8071,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8099,7 +8120,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8127,7 +8148,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8155,7 +8176,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8183,7 +8204,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8211,7 +8232,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8239,7 +8260,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8267,7 +8288,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8297,7 +8318,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8325,7 +8346,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8353,7 +8374,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8381,7 +8402,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8409,7 +8430,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8437,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8465,7 +8486,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8495,7 +8516,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8523,7 +8544,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8551,7 +8572,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8579,7 +8600,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8607,7 +8628,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8637,7 +8658,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8669,7 +8690,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8697,7 +8718,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8725,7 +8746,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8753,7 +8774,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8781,7 +8802,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8809,7 +8830,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8841,7 +8862,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8873,7 +8894,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -9549,7 +9570,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9560,16 +9581,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
-    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
-    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
-    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
-    <col customWidth="1" max="10" min="10" style="53" width="20"/>
+    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
+    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
+    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
+    <col width="20" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="16.5" r="1" s="53">
+    <row r="1" ht="16.5" customHeight="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -9579,7 +9600,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="2" s="53">
+    <row r="2" ht="16.5" customHeight="1" s="53">
       <c r="A2" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -9624,7 +9645,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" s="53">
+    <row r="3" ht="16.5" customHeight="1" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9670,7 +9691,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="4" s="53">
+    <row r="4" ht="16.5" customHeight="1" s="53">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9715,7 +9736,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="5" s="53">
+    <row r="5" ht="16.5" customHeight="1" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9764,7 +9785,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="6" s="53">
+    <row r="6" ht="16.5" customHeight="1" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9813,7 +9834,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="7" s="53">
+    <row r="7" ht="16.5" customHeight="1" s="53">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9855,7 +9876,7 @@
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="35" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="8" s="53">
+    <row r="8" ht="16.5" customHeight="1" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9890,7 +9911,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="9" s="53">
+    <row r="9" ht="16.5" customHeight="1" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9930,7 +9951,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="10" s="53">
+    <row r="10" ht="16.5" customHeight="1" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9966,7 +9987,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="11" s="53">
+    <row r="11" ht="16.5" customHeight="1" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10002,7 +10023,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="12" s="53">
+    <row r="12" ht="16.5" customHeight="1" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10038,7 +10059,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="13" s="53">
+    <row r="13" ht="16.5" customHeight="1" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10079,7 +10100,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="14" s="53">
+    <row r="14" ht="16.5" customHeight="1" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10110,7 +10131,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="15" s="53">
+    <row r="15" ht="16.5" customHeight="1" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10132,7 +10153,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="16" s="53">
+    <row r="16" ht="16.5" customHeight="1" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10149,7 +10170,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="17" s="53">
+    <row r="17" ht="16.5" customHeight="1" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10166,7 +10187,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="18" s="53">
+    <row r="18" ht="16.5" customHeight="1" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10188,7 +10209,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="19" s="53">
+    <row r="19" ht="16.5" customHeight="1" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10205,7 +10226,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="20" s="53">
+    <row r="20" ht="16.5" customHeight="1" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10223,7 +10244,7 @@
       </c>
       <c r="D20" s="39" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="21" s="53">
+    <row r="21" ht="16.5" customHeight="1" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10245,7 +10266,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="22" s="53">
+    <row r="22" ht="16.5" customHeight="1" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10267,7 +10288,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="23" s="53">
+    <row r="23" ht="16.5" customHeight="1" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10289,7 +10310,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="24" s="53">
+    <row r="24" ht="16.5" customHeight="1" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10311,7 +10332,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="25" s="53">
+    <row r="25" ht="16.5" customHeight="1" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10329,7 +10350,7 @@
       </c>
       <c r="D25" s="36" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="26" s="53">
+    <row r="26" ht="16.5" customHeight="1" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10351,7 +10372,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="27" s="53">
+    <row r="27" ht="16.5" customHeight="1" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10373,7 +10394,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="28" s="53">
+    <row r="28" ht="16.5" customHeight="1" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10395,7 +10416,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="29" s="53">
+    <row r="29" ht="16.5" customHeight="1" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10417,7 +10438,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="30" s="53">
+    <row r="30" ht="16.5" customHeight="1" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10439,7 +10460,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="31" s="53">
+    <row r="31" ht="16.5" customHeight="1" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10461,7 +10482,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="32" s="53">
+    <row r="32" ht="16.5" customHeight="1" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10488,7 +10509,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="33" s="53">
+    <row r="33" ht="16.5" customHeight="1" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10510,7 +10531,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="34" s="53">
+    <row r="34" ht="16.5" customHeight="1" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10532,7 +10553,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="35" s="53">
+    <row r="35" ht="16.5" customHeight="1" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10554,7 +10575,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="36" s="53">
+    <row r="36" ht="16.5" customHeight="1" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10576,7 +10597,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="37" s="53">
+    <row r="37" ht="16.5" customHeight="1" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10598,7 +10619,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="38" s="53">
+    <row r="38" ht="16.5" customHeight="1" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10620,7 +10641,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="39" s="53">
+    <row r="39" ht="16.5" customHeight="1" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10637,7 +10658,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="40" s="53">
+    <row r="40" ht="16.5" customHeight="1" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10659,7 +10680,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="41" s="53">
+    <row r="41" ht="16.5" customHeight="1" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10677,7 +10698,7 @@
       </c>
       <c r="D41" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="42" s="53">
+    <row r="42" ht="16.5" customHeight="1" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10699,7 +10720,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="43" s="53">
+    <row r="43" ht="16.5" customHeight="1" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10717,7 +10738,7 @@
       </c>
       <c r="D43" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="44" s="53">
+    <row r="44" ht="16.5" customHeight="1" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10735,7 +10756,7 @@
       </c>
       <c r="E44" s="46" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="45" s="53">
+    <row r="45" ht="16.5" customHeight="1" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10757,7 +10778,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="46" s="53">
+    <row r="46" ht="16.5" customHeight="1" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10779,7 +10800,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="47" s="53">
+    <row r="47" ht="16.5" customHeight="1" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10801,7 +10822,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="48" s="53">
+    <row r="48" ht="16.5" customHeight="1" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10823,7 +10844,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="49" s="53">
+    <row r="49" ht="16.5" customHeight="1" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10845,7 +10866,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="50" s="53">
+    <row r="50" ht="16.5" customHeight="1" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10868,7 +10889,7 @@
       </c>
       <c r="E50" s="49" t="n"/>
     </row>
-    <row customHeight="1" ht="16.5" r="51" s="53">
+    <row r="51" ht="16.5" customHeight="1" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10890,7 +10911,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="52" s="53">
+    <row r="52" ht="16.5" customHeight="1" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10912,7 +10933,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16" r="53" s="53">
+    <row r="53" ht="16" customHeight="1" s="53">
       <c r="A53" s="37" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -10934,7 +10955,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="54" s="53">
+    <row r="54" ht="16.5" customHeight="1" s="53">
       <c r="A54" s="55" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -10956,7 +10977,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="55" s="53">
+    <row r="55" ht="16.5" customHeight="1" s="53">
       <c r="A55" s="55" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10978,7 +10999,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="56" s="53">
+    <row r="56" ht="16.5" customHeight="1" s="53">
       <c r="A56" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -11000,7 +11021,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="57" s="53">
+    <row r="57" ht="16.5" customHeight="1" s="53">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -11018,7 +11039,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -11029,18 +11050,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="23" width="6.83203125"/>
-    <col customWidth="1" max="2" min="2" style="23" width="8.83203125"/>
-    <col customWidth="1" max="3" min="3" style="23" width="19.6640625"/>
-    <col customWidth="1" max="4" min="4" style="23" width="13"/>
-    <col customWidth="1" hidden="1" max="6" min="5" style="23" width="30.5"/>
-    <col customWidth="1" max="7" min="7" style="23" width="30.5"/>
-    <col customWidth="1" max="26" min="8" style="23" width="10.83203125"/>
+    <col width="6.83203125" customWidth="1" style="23" min="1" max="1"/>
+    <col width="8.83203125" customWidth="1" style="23" min="2" max="2"/>
+    <col width="19.6640625" customWidth="1" style="23" min="3" max="3"/>
+    <col width="13" customWidth="1" style="23" min="4" max="4"/>
+    <col hidden="1" width="30.5" customWidth="1" style="23" min="5" max="6"/>
+    <col width="30.5" customWidth="1" style="23" min="7" max="7"/>
+    <col width="10.83203125" customWidth="1" style="23" min="8" max="26"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="15" r="1" s="53">
+    <row r="1" ht="15" customHeight="1" s="53">
       <c r="A1" s="21" t="n"/>
       <c r="B1" s="22" t="inlineStr">
         <is>
@@ -11082,7 +11103,7 @@
         <v/>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="2" s="53">
+    <row r="2" ht="15.75" customHeight="1" s="53">
       <c r="A2" s="24" t="n">
         <v>1</v>
       </c>
@@ -11125,7 +11146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="3" s="53">
+    <row r="3" ht="15" customHeight="1" s="53">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -11158,7 +11179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="4" s="53">
+    <row r="4" ht="15" customHeight="1" s="53">
       <c r="A4" s="24" t="n">
         <v>3</v>
       </c>
@@ -11196,7 +11217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="5" s="53">
+    <row r="5" ht="15" customHeight="1" s="53">
       <c r="A5" s="24" t="n">
         <v>4</v>
       </c>
@@ -11239,7 +11260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="6" s="53">
+    <row r="6" ht="15" customHeight="1" s="53">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -11272,7 +11293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="7" s="53">
+    <row r="7" ht="15" customHeight="1" s="53">
       <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
@@ -11301,7 +11322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="8" s="53">
+    <row r="8" ht="15" customHeight="1" s="53">
       <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
@@ -11331,7 +11352,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="9" s="53">
+    <row r="9" ht="15" customHeight="1" s="53">
       <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
@@ -11356,7 +11377,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="10" s="53">
+    <row r="10" ht="15" customHeight="1" s="53">
       <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
@@ -11381,7 +11402,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="11" s="53">
+    <row r="11" ht="15" customHeight="1" s="53">
       <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
@@ -11411,7 +11432,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="12" s="53">
+    <row r="12" ht="15" customHeight="1" s="53">
       <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
@@ -11436,7 +11457,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="13" s="53">
+    <row r="13" ht="15" customHeight="1" s="53">
       <c r="A13" s="24" t="n">
         <v>4</v>
       </c>
@@ -11466,7 +11487,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="14" s="53">
+    <row r="14" ht="15" customHeight="1" s="53">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
@@ -11486,7 +11507,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="15" s="53">
+    <row r="15" ht="15" customHeight="1" s="53">
       <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
@@ -11516,7 +11537,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="16" s="53">
+    <row r="16" ht="15" customHeight="1" s="53">
       <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
@@ -11541,7 +11562,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="17" s="53">
+    <row r="17" ht="15.75" customHeight="1" s="53">
       <c r="A17" s="24" t="n">
         <v>2</v>
       </c>
@@ -11576,7 +11597,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="18" s="53">
+    <row r="18" ht="15" customHeight="1" s="53">
       <c r="A18" s="24" t="n">
         <v>3</v>
       </c>
@@ -11611,7 +11632,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="19" s="53">
+    <row r="19" ht="15" customHeight="1" s="53">
       <c r="A19" s="24" t="n">
         <v>4</v>
       </c>
@@ -11636,7 +11657,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="20" s="53">
+    <row r="20" ht="15" customHeight="1" s="53">
       <c r="A20" s="24" t="n">
         <v>5</v>
       </c>
@@ -11666,7 +11687,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="21" s="53">
+    <row r="21" ht="15" customHeight="1" s="53">
       <c r="A21" s="24" t="n">
         <v>6</v>
       </c>
@@ -11696,7 +11717,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="22" s="53">
+    <row r="22" ht="15" customHeight="1" s="53">
       <c r="A22" s="24" t="n">
         <v>7</v>
       </c>
@@ -11726,7 +11747,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="23" s="53">
+    <row r="23" ht="15" customHeight="1" s="53">
       <c r="A23" s="24" t="n">
         <v>8</v>
       </c>
@@ -11756,7 +11777,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="24" s="53">
+    <row r="24" ht="15" customHeight="1" s="53">
       <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
@@ -11786,7 +11807,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="25" s="53">
+    <row r="25" ht="15" customHeight="1" s="53">
       <c r="A25" s="24" t="n">
         <v>2</v>
       </c>
@@ -11816,7 +11837,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="26" s="53">
+    <row r="26" ht="15" customHeight="1" s="53">
       <c r="A26" s="24" t="n">
         <v>3</v>
       </c>
@@ -11841,7 +11862,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="27" s="53">
+    <row r="27" ht="15.75" customHeight="1" s="53">
       <c r="A27" s="24" t="n">
         <v>4</v>
       </c>
@@ -11871,7 +11892,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="28" s="53">
+    <row r="28" ht="15" customHeight="1" s="53">
       <c r="A28" s="24" t="n">
         <v>5</v>
       </c>
@@ -11901,7 +11922,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="29" s="53">
+    <row r="29" ht="15" customHeight="1" s="53">
       <c r="A29" s="24" t="n">
         <v>6</v>
       </c>
@@ -11931,7 +11952,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="30" s="53">
+    <row r="30" ht="15.75" customHeight="1" s="53">
       <c r="A30" s="24" t="n">
         <v>7</v>
       </c>
@@ -11966,7 +11987,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15.75" r="31" s="53">
+    <row r="31" ht="15.75" customHeight="1" s="53">
       <c r="A31" s="24" t="n">
         <v>8</v>
       </c>
@@ -11996,7 +12017,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="32" s="53">
+    <row r="32" ht="15" customHeight="1" s="53">
       <c r="A32" s="24" t="n">
         <v>1</v>
       </c>
@@ -12026,7 +12047,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="33" s="53">
+    <row r="33" ht="15" customHeight="1" s="53">
       <c r="A33" s="24" t="n">
         <v>2</v>
       </c>
@@ -12056,7 +12077,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="34" s="53">
+    <row r="34" ht="15" customHeight="1" s="53">
       <c r="A34" s="24" t="n">
         <v>3</v>
       </c>
@@ -12086,7 +12107,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="35" s="53">
+    <row r="35" ht="15" customHeight="1" s="53">
       <c r="A35" s="24" t="n">
         <v>4</v>
       </c>
@@ -12116,7 +12137,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="36" s="53">
+    <row r="36" ht="15" customHeight="1" s="53">
       <c r="A36" s="24" t="n">
         <v>1</v>
       </c>
@@ -12146,7 +12167,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="37" s="53">
+    <row r="37" ht="15" customHeight="1" s="53">
       <c r="A37" s="24" t="n">
         <v>2</v>
       </c>
@@ -12181,7 +12202,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="15" r="38" s="53">
+    <row r="38" ht="15" customHeight="1" s="53">
       <c r="A38" s="24" t="n">
         <v>3</v>
       </c>
@@ -12212,6 +12233,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="27040" windowHeight="16400" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="16400" windowWidth="27040" xWindow="0" yWindow="500"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="2025年日报" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="2026年日报" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2025月报" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="月报(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026年日报 (2026-4-9存档)" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="旧表" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026年日报'!$A$2:$F$61</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'2026年日报'!$A$2:$F$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,257 +449,257 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyAlignment="1">
+    <xf applyAlignment="1" borderId="7" fillId="7" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="83">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="3" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="5" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="2" fillId="2" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="6" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="5" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="10" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="11" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="12" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="16" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="13" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="17" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="15" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="14" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="14" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="18" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="16" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="9" fillId="3" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="7" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="2" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="20" fillId="7" fontId="17" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="7" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="19" fillId="2" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="8" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="9" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="常规" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1073,16 +1073,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -1387,7 +1387,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1472,7 +1472,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1557,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1642,7 +1642,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1682,7 +1682,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D40" s="46" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D48" s="51" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -2619,26 +2619,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+        <v>46250</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="61" t="inlineStr">
         <is>
           <t>区域</t>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2748,7 +2748,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2812,7 +2812,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2876,7 +2876,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2931,7 +2931,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="72" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3028,7 +3028,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3070,7 +3070,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="61" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3162,7 +3162,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3204,7 +3204,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3246,7 +3246,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3283,7 +3283,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="15" s="78">
       <c r="A15" s="61" t="inlineStr">
         <is>
           <t>粤西区</t>
@@ -3314,7 +3314,7 @@
       <c r="H15" s="23" t="n"/>
       <c r="J15" s="67" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="61" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -3347,7 +3347,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="G17" s="67" t="n"/>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="G18" s="67" t="n"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="61" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G19" s="67" t="n"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="G20" s="67" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G21" s="67" t="n"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G22" s="67" t="n"/>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G23" s="67" t="n"/>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G24" s="67" t="n"/>
     </row>
-    <row r="25" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="25" s="78">
       <c r="A25" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3578,7 +3578,7 @@
       <c r="H25" s="67" t="n"/>
       <c r="J25" s="67" t="n"/>
     </row>
-    <row r="26" ht="16.5" customFormat="1" customHeight="1" s="78">
+    <row customFormat="1" customHeight="1" ht="16.5" r="26" s="78">
       <c r="A26" s="61" t="inlineStr">
         <is>
           <t>华东分公司</t>
@@ -3609,7 +3609,7 @@
       <c r="H26" s="67" t="n"/>
       <c r="J26" s="67" t="n"/>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="G27" s="67" t="n"/>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G28" s="67" t="n"/>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="G29" s="67" t="n"/>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="G30" s="67" t="n"/>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G31" s="67" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="61" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="G32" s="67" t="n"/>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G33" s="67" t="n"/>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G34" s="67" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G35" s="67" t="n"/>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G36" s="67" t="n"/>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="61" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="G37" s="67" t="n"/>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G38" s="67" t="n"/>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G39" s="67" t="n"/>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="G40" s="67" t="n"/>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G41" s="67" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="G42" s="67" t="n"/>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G43" s="67" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G44" s="67" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G45" s="67" t="n"/>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G46" s="67" t="n"/>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G47" s="67" t="n"/>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="61" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="G48" s="67" t="n"/>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G49" s="67" t="n"/>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G50" s="67" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4285,7 +4285,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D51" s="71" t="n"/>
+      <c r="D51" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E51" s="69" t="n"/>
       <c r="F51" s="63" t="inlineStr">
         <is>
@@ -4294,7 +4298,7 @@
       </c>
       <c r="G51" s="67" t="n"/>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="61" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4319,7 +4323,7 @@
       </c>
       <c r="G52" s="67" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="72" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -4348,7 +4352,7 @@
       </c>
       <c r="G53" s="67" t="n"/>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="58" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4377,7 +4381,7 @@
       </c>
       <c r="G54" s="67" t="n"/>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="58" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="G55" s="67" t="n"/>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4431,7 +4435,7 @@
       </c>
       <c r="G56" s="67" t="n"/>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="58" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -4460,7 +4464,7 @@
       </c>
       <c r="G57" s="67" t="n"/>
     </row>
-    <row r="58" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="58" s="53">
       <c r="A58" s="60" t="inlineStr">
         <is>
           <t>华北分公司</t>
@@ -4478,7 +4482,7 @@
       </c>
       <c r="D58" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E58" s="69" t="n"/>
@@ -4489,7 +4493,7 @@
       </c>
       <c r="G58" s="67" t="n"/>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="59" s="53">
       <c r="A59" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4518,7 +4522,7 @@
       </c>
       <c r="G59" s="67" t="n"/>
     </row>
-    <row r="60" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="60" s="53">
       <c r="A60" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="G60" s="67" t="n"/>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="61" s="53">
       <c r="A61" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="G61" s="67" t="n"/>
     </row>
-    <row r="62" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="62" s="53">
       <c r="A62" s="60" t="inlineStr">
         <is>
           <t>粤西五区</t>
@@ -4596,7 +4600,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="63" s="53">
       <c r="A63" s="60" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -4624,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="64" s="53">
       <c r="A64" s="0" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -4651,228 +4655,228 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1" s="53">
-      <c r="A65" t="inlineStr">
+    <row customHeight="1" ht="16" r="65" s="53">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>华东分公司</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>南京江宁中心</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>华东分公司</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1" s="53"/>
-    <row r="67" ht="16" customHeight="1" s="53"/>
-    <row r="68" ht="16" customHeight="1" s="53"/>
-    <row r="69" ht="16" customHeight="1" s="53"/>
-    <row r="70" ht="16" customHeight="1" s="53"/>
-    <row r="71" ht="16" customHeight="1" s="53"/>
-    <row r="72" ht="16" customHeight="1" s="53"/>
-    <row r="73" ht="16" customHeight="1" s="53"/>
-    <row r="74" ht="16" customHeight="1" s="53"/>
-    <row r="75" ht="16" customHeight="1" s="53"/>
-    <row r="76" ht="16" customHeight="1" s="53"/>
-    <row r="77" ht="16" customHeight="1" s="53"/>
-    <row r="78" ht="16" customHeight="1" s="53"/>
-    <row r="79" ht="16" customHeight="1" s="53"/>
-    <row r="80" ht="16" customHeight="1" s="53"/>
-    <row r="81" ht="16" customHeight="1" s="53"/>
-    <row r="82" ht="16" customHeight="1" s="53"/>
-    <row r="83" ht="16" customHeight="1" s="53"/>
-    <row r="84" ht="16" customHeight="1" s="53"/>
-    <row r="85" ht="16" customHeight="1" s="53"/>
-    <row r="86" ht="16" customHeight="1" s="53"/>
-    <row r="87" ht="16" customHeight="1" s="53"/>
-    <row r="88" ht="16" customHeight="1" s="53"/>
-    <row r="89" ht="16" customHeight="1" s="53"/>
-    <row r="90" ht="16" customHeight="1" s="53"/>
-    <row r="91" ht="16" customHeight="1" s="53"/>
-    <row r="92" ht="16" customHeight="1" s="53"/>
-    <row r="93" ht="16" customHeight="1" s="53"/>
-    <row r="94" ht="16" customHeight="1" s="53"/>
-    <row r="95" ht="16" customHeight="1" s="53"/>
-    <row r="96" ht="16" customHeight="1" s="53"/>
-    <row r="97" ht="16" customHeight="1" s="53"/>
-    <row r="98" ht="16" customHeight="1" s="53"/>
-    <row r="99" ht="16" customHeight="1" s="53"/>
-    <row r="100" ht="16" customHeight="1" s="53"/>
-    <row r="101" ht="16" customHeight="1" s="53"/>
-    <row r="102" ht="16" customHeight="1" s="53"/>
-    <row r="103" ht="16" customHeight="1" s="53"/>
-    <row r="104" ht="16" customHeight="1" s="53"/>
-    <row r="105" ht="16" customHeight="1" s="53"/>
-    <row r="106" ht="16" customHeight="1" s="53"/>
-    <row r="107" ht="16" customHeight="1" s="53"/>
-    <row r="108" ht="16" customHeight="1" s="53"/>
-    <row r="109" ht="16" customHeight="1" s="53"/>
-    <row r="110" ht="16" customHeight="1" s="53"/>
-    <row r="111" ht="16" customHeight="1" s="53"/>
-    <row r="112" ht="16" customHeight="1" s="53"/>
-    <row r="113" ht="16" customHeight="1" s="53"/>
-    <row r="114" ht="16" customHeight="1" s="53"/>
-    <row r="115" ht="16" customHeight="1" s="53"/>
-    <row r="116" ht="16" customHeight="1" s="53"/>
-    <row r="117" ht="16" customHeight="1" s="53"/>
-    <row r="118" ht="16" customHeight="1" s="53"/>
-    <row r="119" ht="16" customHeight="1" s="53"/>
-    <row r="120" ht="16" customHeight="1" s="53"/>
-    <row r="121" ht="16" customHeight="1" s="53"/>
-    <row r="122" ht="16" customHeight="1" s="53"/>
-    <row r="123" ht="16" customHeight="1" s="53"/>
-    <row r="124" ht="16" customHeight="1" s="53"/>
-    <row r="125" ht="16" customHeight="1" s="53"/>
-    <row r="126" ht="16" customHeight="1" s="53"/>
-    <row r="127" ht="16" customHeight="1" s="53"/>
-    <row r="128" ht="16" customHeight="1" s="53"/>
-    <row r="129" ht="16" customHeight="1" s="53"/>
-    <row r="130" ht="16" customHeight="1" s="53"/>
-    <row r="131" ht="16" customHeight="1" s="53"/>
-    <row r="132" ht="16" customHeight="1" s="53"/>
-    <row r="133" ht="16" customHeight="1" s="53"/>
-    <row r="134" ht="16" customHeight="1" s="53"/>
-    <row r="135" ht="16" customHeight="1" s="53"/>
-    <row r="136" ht="16" customHeight="1" s="53"/>
-    <row r="137" ht="16" customHeight="1" s="53"/>
-    <row r="138" ht="16" customHeight="1" s="53"/>
-    <row r="139" ht="16" customHeight="1" s="53"/>
-    <row r="140" ht="16" customHeight="1" s="53"/>
-    <row r="141" ht="16" customHeight="1" s="53"/>
-    <row r="142" ht="16" customHeight="1" s="53"/>
-    <row r="143" ht="16" customHeight="1" s="53"/>
-    <row r="144" ht="16" customHeight="1" s="53"/>
-    <row r="145" ht="16" customHeight="1" s="53"/>
-    <row r="146" ht="16" customHeight="1" s="53"/>
-    <row r="147" ht="16" customHeight="1" s="53"/>
-    <row r="148" ht="16" customHeight="1" s="53"/>
-    <row r="149" ht="16" customHeight="1" s="53"/>
-    <row r="150" ht="16" customHeight="1" s="53"/>
-    <row r="151" ht="16" customHeight="1" s="53"/>
-    <row r="152" ht="16" customHeight="1" s="53"/>
-    <row r="153" ht="16" customHeight="1" s="53"/>
-    <row r="154" ht="16" customHeight="1" s="53"/>
-    <row r="155" ht="16" customHeight="1" s="53"/>
-    <row r="156" ht="16" customHeight="1" s="53"/>
-    <row r="157" ht="16" customHeight="1" s="53"/>
-    <row r="158" ht="16" customHeight="1" s="53"/>
-    <row r="159" ht="16" customHeight="1" s="53"/>
-    <row r="160" ht="16" customHeight="1" s="53"/>
-    <row r="161" ht="16" customHeight="1" s="53"/>
-    <row r="162" ht="16" customHeight="1" s="53"/>
-    <row r="163" ht="16" customHeight="1" s="53"/>
-    <row r="164" ht="16" customHeight="1" s="53"/>
-    <row r="165" ht="16" customHeight="1" s="53"/>
-    <row r="166" ht="16" customHeight="1" s="53"/>
-    <row r="167" ht="16" customHeight="1" s="53"/>
-    <row r="168" ht="16" customHeight="1" s="53"/>
-    <row r="169" ht="16" customHeight="1" s="53"/>
-    <row r="170" ht="16" customHeight="1" s="53"/>
-    <row r="171" ht="16" customHeight="1" s="53"/>
-    <row r="172" ht="16" customHeight="1" s="53"/>
-    <row r="173" ht="16" customHeight="1" s="53"/>
-    <row r="174" ht="16" customHeight="1" s="53"/>
-    <row r="175" ht="16" customHeight="1" s="53"/>
-    <row r="176" ht="16" customHeight="1" s="53"/>
-    <row r="177" ht="16" customHeight="1" s="53"/>
-    <row r="178" ht="16" customHeight="1" s="53"/>
-    <row r="179" ht="16" customHeight="1" s="53"/>
-    <row r="180" ht="16" customHeight="1" s="53"/>
-    <row r="181" ht="16" customHeight="1" s="53"/>
-    <row r="182" ht="16" customHeight="1" s="53"/>
-    <row r="183" ht="16" customHeight="1" s="53"/>
-    <row r="184" ht="16" customHeight="1" s="53"/>
-    <row r="185" ht="16" customHeight="1" s="53"/>
-    <row r="186" ht="16" customHeight="1" s="53"/>
-    <row r="187" ht="16" customHeight="1" s="53"/>
-    <row r="188" ht="16" customHeight="1" s="53"/>
-    <row r="189" ht="16" customHeight="1" s="53"/>
-    <row r="190" ht="16" customHeight="1" s="53"/>
-    <row r="191" ht="16" customHeight="1" s="53"/>
-    <row r="192" ht="16" customHeight="1" s="53"/>
-    <row r="193" ht="16" customHeight="1" s="53"/>
-    <row r="194" ht="16" customHeight="1" s="53"/>
-    <row r="195" ht="16" customHeight="1" s="53"/>
-    <row r="196" ht="16" customHeight="1" s="53"/>
-    <row r="197" ht="16" customHeight="1" s="53"/>
-    <row r="198" ht="16" customHeight="1" s="53"/>
-    <row r="199" ht="16" customHeight="1" s="53"/>
-    <row r="200" ht="16" customHeight="1" s="53"/>
-    <row r="201" ht="16" customHeight="1" s="53"/>
-    <row r="202" ht="16" customHeight="1" s="53"/>
-    <row r="203" ht="16" customHeight="1" s="53"/>
-    <row r="204" ht="16" customHeight="1" s="53"/>
-    <row r="205" ht="16" customHeight="1" s="53"/>
-    <row r="206" ht="16" customHeight="1" s="53"/>
-    <row r="207" ht="16" customHeight="1" s="53"/>
-    <row r="208" ht="16" customHeight="1" s="53"/>
-    <row r="209" ht="16" customHeight="1" s="53"/>
-    <row r="210" ht="16" customHeight="1" s="53"/>
-    <row r="211" ht="16" customHeight="1" s="53"/>
-    <row r="212" ht="16" customHeight="1" s="53"/>
-    <row r="213" ht="16" customHeight="1" s="53"/>
-    <row r="214" ht="16" customHeight="1" s="53"/>
-    <row r="215" ht="16" customHeight="1" s="53"/>
-    <row r="216" ht="16" customHeight="1" s="53"/>
-    <row r="217" ht="16" customHeight="1" s="53"/>
-    <row r="218" ht="16" customHeight="1" s="53"/>
-    <row r="219" ht="16" customHeight="1" s="53"/>
-    <row r="220" ht="16" customHeight="1" s="53"/>
-    <row r="221" ht="16" customHeight="1" s="53"/>
-    <row r="222" ht="16" customHeight="1" s="53"/>
-    <row r="223" ht="16" customHeight="1" s="53"/>
-    <row r="224" ht="16" customHeight="1" s="53"/>
-    <row r="225" ht="16" customHeight="1" s="53"/>
-    <row r="226" ht="16" customHeight="1" s="53"/>
-    <row r="227" ht="16" customHeight="1" s="53"/>
-    <row r="228" ht="16" customHeight="1" s="53"/>
-    <row r="229" ht="16" customHeight="1" s="53"/>
-    <row r="230" ht="16" customHeight="1" s="53"/>
-    <row r="231" ht="16" customHeight="1" s="53"/>
-    <row r="232" ht="16" customHeight="1" s="53"/>
-    <row r="233" ht="16" customHeight="1" s="53"/>
-    <row r="234" ht="16" customHeight="1" s="53"/>
-    <row r="235" ht="16" customHeight="1" s="53"/>
-    <row r="236" ht="16" customHeight="1" s="53"/>
-    <row r="237" ht="16" customHeight="1" s="53"/>
-    <row r="238" ht="16" customHeight="1" s="53"/>
-    <row r="239" ht="16" customHeight="1" s="53"/>
-    <row r="240" ht="16" customHeight="1" s="53"/>
-    <row r="241" ht="16" customHeight="1" s="53"/>
-    <row r="242" ht="16" customHeight="1" s="53"/>
-    <row r="243" ht="16" customHeight="1" s="53"/>
-    <row r="244" ht="16" customHeight="1" s="53"/>
-    <row r="245" ht="16" customHeight="1" s="53"/>
-    <row r="246" ht="16" customHeight="1" s="53"/>
-    <row r="247" ht="16" customHeight="1" s="53"/>
-    <row r="248" ht="16" customHeight="1" s="53"/>
-    <row r="249" ht="16" customHeight="1" s="53"/>
-    <row r="250" ht="16" customHeight="1" s="53"/>
-    <row r="251" ht="16" customHeight="1" s="53"/>
-    <row r="252" ht="16" customHeight="1" s="53"/>
-    <row r="253" ht="16" customHeight="1" s="53"/>
-    <row r="254" ht="16" customHeight="1" s="53"/>
-    <row r="255" ht="16" customHeight="1" s="53"/>
-    <row r="256" ht="16" customHeight="1" s="53"/>
-    <row r="257" ht="16" customHeight="1" s="53"/>
-    <row r="258" ht="16" customHeight="1" s="53"/>
-    <row r="259" ht="16" customHeight="1" s="53"/>
-    <row r="260" ht="16" customHeight="1" s="53"/>
-    <row r="261" ht="16" customHeight="1" s="53"/>
-    <row r="262" ht="16" customHeight="1" s="53"/>
+    <row customHeight="1" ht="16" r="66" s="53"/>
+    <row customHeight="1" ht="16" r="67" s="53"/>
+    <row customHeight="1" ht="16" r="68" s="53"/>
+    <row customHeight="1" ht="16" r="69" s="53"/>
+    <row customHeight="1" ht="16" r="70" s="53"/>
+    <row customHeight="1" ht="16" r="71" s="53"/>
+    <row customHeight="1" ht="16" r="72" s="53"/>
+    <row customHeight="1" ht="16" r="73" s="53"/>
+    <row customHeight="1" ht="16" r="74" s="53"/>
+    <row customHeight="1" ht="16" r="75" s="53"/>
+    <row customHeight="1" ht="16" r="76" s="53"/>
+    <row customHeight="1" ht="16" r="77" s="53"/>
+    <row customHeight="1" ht="16" r="78" s="53"/>
+    <row customHeight="1" ht="16" r="79" s="53"/>
+    <row customHeight="1" ht="16" r="80" s="53"/>
+    <row customHeight="1" ht="16" r="81" s="53"/>
+    <row customHeight="1" ht="16" r="82" s="53"/>
+    <row customHeight="1" ht="16" r="83" s="53"/>
+    <row customHeight="1" ht="16" r="84" s="53"/>
+    <row customHeight="1" ht="16" r="85" s="53"/>
+    <row customHeight="1" ht="16" r="86" s="53"/>
+    <row customHeight="1" ht="16" r="87" s="53"/>
+    <row customHeight="1" ht="16" r="88" s="53"/>
+    <row customHeight="1" ht="16" r="89" s="53"/>
+    <row customHeight="1" ht="16" r="90" s="53"/>
+    <row customHeight="1" ht="16" r="91" s="53"/>
+    <row customHeight="1" ht="16" r="92" s="53"/>
+    <row customHeight="1" ht="16" r="93" s="53"/>
+    <row customHeight="1" ht="16" r="94" s="53"/>
+    <row customHeight="1" ht="16" r="95" s="53"/>
+    <row customHeight="1" ht="16" r="96" s="53"/>
+    <row customHeight="1" ht="16" r="97" s="53"/>
+    <row customHeight="1" ht="16" r="98" s="53"/>
+    <row customHeight="1" ht="16" r="99" s="53"/>
+    <row customHeight="1" ht="16" r="100" s="53"/>
+    <row customHeight="1" ht="16" r="101" s="53"/>
+    <row customHeight="1" ht="16" r="102" s="53"/>
+    <row customHeight="1" ht="16" r="103" s="53"/>
+    <row customHeight="1" ht="16" r="104" s="53"/>
+    <row customHeight="1" ht="16" r="105" s="53"/>
+    <row customHeight="1" ht="16" r="106" s="53"/>
+    <row customHeight="1" ht="16" r="107" s="53"/>
+    <row customHeight="1" ht="16" r="108" s="53"/>
+    <row customHeight="1" ht="16" r="109" s="53"/>
+    <row customHeight="1" ht="16" r="110" s="53"/>
+    <row customHeight="1" ht="16" r="111" s="53"/>
+    <row customHeight="1" ht="16" r="112" s="53"/>
+    <row customHeight="1" ht="16" r="113" s="53"/>
+    <row customHeight="1" ht="16" r="114" s="53"/>
+    <row customHeight="1" ht="16" r="115" s="53"/>
+    <row customHeight="1" ht="16" r="116" s="53"/>
+    <row customHeight="1" ht="16" r="117" s="53"/>
+    <row customHeight="1" ht="16" r="118" s="53"/>
+    <row customHeight="1" ht="16" r="119" s="53"/>
+    <row customHeight="1" ht="16" r="120" s="53"/>
+    <row customHeight="1" ht="16" r="121" s="53"/>
+    <row customHeight="1" ht="16" r="122" s="53"/>
+    <row customHeight="1" ht="16" r="123" s="53"/>
+    <row customHeight="1" ht="16" r="124" s="53"/>
+    <row customHeight="1" ht="16" r="125" s="53"/>
+    <row customHeight="1" ht="16" r="126" s="53"/>
+    <row customHeight="1" ht="16" r="127" s="53"/>
+    <row customHeight="1" ht="16" r="128" s="53"/>
+    <row customHeight="1" ht="16" r="129" s="53"/>
+    <row customHeight="1" ht="16" r="130" s="53"/>
+    <row customHeight="1" ht="16" r="131" s="53"/>
+    <row customHeight="1" ht="16" r="132" s="53"/>
+    <row customHeight="1" ht="16" r="133" s="53"/>
+    <row customHeight="1" ht="16" r="134" s="53"/>
+    <row customHeight="1" ht="16" r="135" s="53"/>
+    <row customHeight="1" ht="16" r="136" s="53"/>
+    <row customHeight="1" ht="16" r="137" s="53"/>
+    <row customHeight="1" ht="16" r="138" s="53"/>
+    <row customHeight="1" ht="16" r="139" s="53"/>
+    <row customHeight="1" ht="16" r="140" s="53"/>
+    <row customHeight="1" ht="16" r="141" s="53"/>
+    <row customHeight="1" ht="16" r="142" s="53"/>
+    <row customHeight="1" ht="16" r="143" s="53"/>
+    <row customHeight="1" ht="16" r="144" s="53"/>
+    <row customHeight="1" ht="16" r="145" s="53"/>
+    <row customHeight="1" ht="16" r="146" s="53"/>
+    <row customHeight="1" ht="16" r="147" s="53"/>
+    <row customHeight="1" ht="16" r="148" s="53"/>
+    <row customHeight="1" ht="16" r="149" s="53"/>
+    <row customHeight="1" ht="16" r="150" s="53"/>
+    <row customHeight="1" ht="16" r="151" s="53"/>
+    <row customHeight="1" ht="16" r="152" s="53"/>
+    <row customHeight="1" ht="16" r="153" s="53"/>
+    <row customHeight="1" ht="16" r="154" s="53"/>
+    <row customHeight="1" ht="16" r="155" s="53"/>
+    <row customHeight="1" ht="16" r="156" s="53"/>
+    <row customHeight="1" ht="16" r="157" s="53"/>
+    <row customHeight="1" ht="16" r="158" s="53"/>
+    <row customHeight="1" ht="16" r="159" s="53"/>
+    <row customHeight="1" ht="16" r="160" s="53"/>
+    <row customHeight="1" ht="16" r="161" s="53"/>
+    <row customHeight="1" ht="16" r="162" s="53"/>
+    <row customHeight="1" ht="16" r="163" s="53"/>
+    <row customHeight="1" ht="16" r="164" s="53"/>
+    <row customHeight="1" ht="16" r="165" s="53"/>
+    <row customHeight="1" ht="16" r="166" s="53"/>
+    <row customHeight="1" ht="16" r="167" s="53"/>
+    <row customHeight="1" ht="16" r="168" s="53"/>
+    <row customHeight="1" ht="16" r="169" s="53"/>
+    <row customHeight="1" ht="16" r="170" s="53"/>
+    <row customHeight="1" ht="16" r="171" s="53"/>
+    <row customHeight="1" ht="16" r="172" s="53"/>
+    <row customHeight="1" ht="16" r="173" s="53"/>
+    <row customHeight="1" ht="16" r="174" s="53"/>
+    <row customHeight="1" ht="16" r="175" s="53"/>
+    <row customHeight="1" ht="16" r="176" s="53"/>
+    <row customHeight="1" ht="16" r="177" s="53"/>
+    <row customHeight="1" ht="16" r="178" s="53"/>
+    <row customHeight="1" ht="16" r="179" s="53"/>
+    <row customHeight="1" ht="16" r="180" s="53"/>
+    <row customHeight="1" ht="16" r="181" s="53"/>
+    <row customHeight="1" ht="16" r="182" s="53"/>
+    <row customHeight="1" ht="16" r="183" s="53"/>
+    <row customHeight="1" ht="16" r="184" s="53"/>
+    <row customHeight="1" ht="16" r="185" s="53"/>
+    <row customHeight="1" ht="16" r="186" s="53"/>
+    <row customHeight="1" ht="16" r="187" s="53"/>
+    <row customHeight="1" ht="16" r="188" s="53"/>
+    <row customHeight="1" ht="16" r="189" s="53"/>
+    <row customHeight="1" ht="16" r="190" s="53"/>
+    <row customHeight="1" ht="16" r="191" s="53"/>
+    <row customHeight="1" ht="16" r="192" s="53"/>
+    <row customHeight="1" ht="16" r="193" s="53"/>
+    <row customHeight="1" ht="16" r="194" s="53"/>
+    <row customHeight="1" ht="16" r="195" s="53"/>
+    <row customHeight="1" ht="16" r="196" s="53"/>
+    <row customHeight="1" ht="16" r="197" s="53"/>
+    <row customHeight="1" ht="16" r="198" s="53"/>
+    <row customHeight="1" ht="16" r="199" s="53"/>
+    <row customHeight="1" ht="16" r="200" s="53"/>
+    <row customHeight="1" ht="16" r="201" s="53"/>
+    <row customHeight="1" ht="16" r="202" s="53"/>
+    <row customHeight="1" ht="16" r="203" s="53"/>
+    <row customHeight="1" ht="16" r="204" s="53"/>
+    <row customHeight="1" ht="16" r="205" s="53"/>
+    <row customHeight="1" ht="16" r="206" s="53"/>
+    <row customHeight="1" ht="16" r="207" s="53"/>
+    <row customHeight="1" ht="16" r="208" s="53"/>
+    <row customHeight="1" ht="16" r="209" s="53"/>
+    <row customHeight="1" ht="16" r="210" s="53"/>
+    <row customHeight="1" ht="16" r="211" s="53"/>
+    <row customHeight="1" ht="16" r="212" s="53"/>
+    <row customHeight="1" ht="16" r="213" s="53"/>
+    <row customHeight="1" ht="16" r="214" s="53"/>
+    <row customHeight="1" ht="16" r="215" s="53"/>
+    <row customHeight="1" ht="16" r="216" s="53"/>
+    <row customHeight="1" ht="16" r="217" s="53"/>
+    <row customHeight="1" ht="16" r="218" s="53"/>
+    <row customHeight="1" ht="16" r="219" s="53"/>
+    <row customHeight="1" ht="16" r="220" s="53"/>
+    <row customHeight="1" ht="16" r="221" s="53"/>
+    <row customHeight="1" ht="16" r="222" s="53"/>
+    <row customHeight="1" ht="16" r="223" s="53"/>
+    <row customHeight="1" ht="16" r="224" s="53"/>
+    <row customHeight="1" ht="16" r="225" s="53"/>
+    <row customHeight="1" ht="16" r="226" s="53"/>
+    <row customHeight="1" ht="16" r="227" s="53"/>
+    <row customHeight="1" ht="16" r="228" s="53"/>
+    <row customHeight="1" ht="16" r="229" s="53"/>
+    <row customHeight="1" ht="16" r="230" s="53"/>
+    <row customHeight="1" ht="16" r="231" s="53"/>
+    <row customHeight="1" ht="16" r="232" s="53"/>
+    <row customHeight="1" ht="16" r="233" s="53"/>
+    <row customHeight="1" ht="16" r="234" s="53"/>
+    <row customHeight="1" ht="16" r="235" s="53"/>
+    <row customHeight="1" ht="16" r="236" s="53"/>
+    <row customHeight="1" ht="16" r="237" s="53"/>
+    <row customHeight="1" ht="16" r="238" s="53"/>
+    <row customHeight="1" ht="16" r="239" s="53"/>
+    <row customHeight="1" ht="16" r="240" s="53"/>
+    <row customHeight="1" ht="16" r="241" s="53"/>
+    <row customHeight="1" ht="16" r="242" s="53"/>
+    <row customHeight="1" ht="16" r="243" s="53"/>
+    <row customHeight="1" ht="16" r="244" s="53"/>
+    <row customHeight="1" ht="16" r="245" s="53"/>
+    <row customHeight="1" ht="16" r="246" s="53"/>
+    <row customHeight="1" ht="16" r="247" s="53"/>
+    <row customHeight="1" ht="16" r="248" s="53"/>
+    <row customHeight="1" ht="16" r="249" s="53"/>
+    <row customHeight="1" ht="16" r="250" s="53"/>
+    <row customHeight="1" ht="16" r="251" s="53"/>
+    <row customHeight="1" ht="16" r="252" s="53"/>
+    <row customHeight="1" ht="16" r="253" s="53"/>
+    <row customHeight="1" ht="16" r="254" s="53"/>
+    <row customHeight="1" ht="16" r="255" s="53"/>
+    <row customHeight="1" ht="16" r="256" s="53"/>
+    <row customHeight="1" ht="16" r="257" s="53"/>
+    <row customHeight="1" ht="16" r="258" s="53"/>
+    <row customHeight="1" ht="16" r="259" s="53"/>
+    <row customHeight="1" ht="16" r="260" s="53"/>
+    <row customHeight="1" ht="16" r="261" s="53"/>
+    <row customHeight="1" ht="16" r="262" s="53"/>
   </sheetData>
   <autoFilter ref="A2:F61"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -4885,17 +4889,17 @@
   <dimension ref="A1:T207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -4918,7 +4922,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>区域</t>
@@ -5004,7 +5008,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5047,7 +5051,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5092,7 +5096,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5129,7 +5133,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -5174,7 +5178,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5213,7 +5217,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5250,7 +5254,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5279,7 +5283,7 @@
       <c r="S9" s="14" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -5318,7 +5322,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5355,7 +5359,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5392,7 +5396,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5431,7 +5435,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5468,7 +5472,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -5495,7 +5499,7 @@
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5523,7 +5527,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5551,7 +5555,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -5579,7 +5583,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5609,7 +5613,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5639,7 +5643,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5675,7 +5679,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5703,7 +5707,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -5733,7 +5737,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5771,7 +5775,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5801,7 +5805,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -5833,7 +5837,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5867,7 +5871,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -5899,7 +5903,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5927,7 +5931,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5963,7 +5967,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -5990,7 +5994,7 @@
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6022,7 +6026,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6054,7 +6058,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -6079,7 +6083,7 @@
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6109,7 +6113,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6139,7 +6143,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6173,7 +6177,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6203,7 +6207,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6231,7 +6235,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6259,7 +6263,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6287,7 +6291,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -6315,7 +6319,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6343,7 +6347,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6371,7 +6375,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6399,7 +6403,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -6427,7 +6431,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6465,7 +6469,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6495,7 +6499,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6531,7 +6535,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>华中区</t>
@@ -6565,7 +6569,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6601,7 +6605,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -6633,7 +6637,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="53" s="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -7281,7 +7285,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -7294,17 +7298,17 @@
   <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="6.33203125" customWidth="1" style="53" min="1" max="1"/>
-    <col width="11.83203125" customWidth="1" style="53" min="2" max="2"/>
-    <col width="3.1640625" customWidth="1" style="17" min="3" max="5"/>
-    <col width="3.1640625" customWidth="1" style="53" min="6" max="11"/>
-    <col width="3.83203125" customWidth="1" style="53" min="12" max="14"/>
-    <col width="3.6640625" customWidth="1" style="53" min="15" max="15"/>
-    <col width="7.6640625" customWidth="1" style="53" min="19" max="19"/>
-    <col width="2.83203125" customWidth="1" style="53" min="20" max="20"/>
+    <col customWidth="1" max="1" min="1" style="53" width="6.33203125"/>
+    <col customWidth="1" max="2" min="2" style="53" width="11.83203125"/>
+    <col customWidth="1" max="5" min="3" style="17" width="3.1640625"/>
+    <col customWidth="1" max="11" min="6" style="53" width="3.1640625"/>
+    <col customWidth="1" max="14" min="12" style="53" width="3.83203125"/>
+    <col customWidth="1" max="15" min="15" style="53" width="3.6640625"/>
+    <col customWidth="1" max="19" min="19" style="53" width="7.6640625"/>
+    <col customWidth="1" max="20" min="20" style="53" width="2.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" s="53">
+    <row customHeight="1" ht="22.5" r="1" s="53">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>2025未填写月报次数</t>
@@ -7327,7 +7331,7 @@
       <c r="S1" s="1" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>区域</t>
@@ -7413,7 +7417,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7459,7 +7463,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7496,7 +7500,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7542,7 +7546,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -7588,7 +7592,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7636,7 +7640,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7673,7 +7677,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7710,7 +7714,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -7758,7 +7762,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7804,7 +7808,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7841,7 +7845,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7878,7 +7882,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7924,7 +7928,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -7952,7 +7956,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -7980,7 +7984,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -8008,7 +8012,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -8036,7 +8040,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8064,7 +8068,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8092,7 +8096,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8120,7 +8124,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8148,7 +8152,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -8176,7 +8180,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8204,7 +8208,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8232,7 +8236,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -8260,7 +8264,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8288,7 +8292,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -8318,7 +8322,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8346,7 +8350,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8374,7 +8378,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8402,7 +8406,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8430,7 +8434,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8458,7 +8462,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -8486,7 +8490,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8516,7 +8520,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8544,7 +8548,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8572,7 +8576,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8600,7 +8604,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8628,7 +8632,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8658,7 +8662,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8690,7 +8694,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -8718,7 +8722,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8746,7 +8750,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8774,7 +8778,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8802,7 +8806,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -8830,7 +8834,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8862,7 +8866,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -8894,7 +8898,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -9570,7 +9574,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -9581,16 +9585,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.1640625" customWidth="1" style="53" min="2" max="2"/>
-    <col width="30.6640625" customWidth="1" style="29" min="4" max="4"/>
-    <col width="26.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col hidden="1" width="10" customWidth="1" style="53" min="7" max="8"/>
-    <col width="20" customWidth="1" style="53" min="10" max="10"/>
+    <col customWidth="1" max="2" min="2" style="53" width="13.1640625"/>
+    <col customWidth="1" max="4" min="4" style="29" width="30.6640625"/>
+    <col customWidth="1" max="5" min="5" style="30" width="26.33203125"/>
+    <col customWidth="1" hidden="1" max="8" min="7" style="53" width="10"/>
+    <col customWidth="1" max="10" min="10" style="53" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="1" s="53">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>更新日期</t>
@@ -9600,7 +9604,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="2" s="53">
       <c r="A2" s="27" t="inlineStr">
         <is>
           <t>区域</t>
@@ -9645,7 +9649,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="3" s="53">
       <c r="A3" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9691,7 +9695,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="4" s="53">
       <c r="A4" s="31" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9736,7 +9740,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="5" s="53">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9785,7 +9789,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="6" s="53">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9834,7 +9838,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="7" s="53">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -9876,7 +9880,7 @@
       <c r="L7" s="34" t="n"/>
       <c r="M7" s="35" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="8" s="53">
       <c r="A8" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9911,7 +9915,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="9" s="53">
       <c r="A9" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9951,7 +9955,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="10" s="53">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -9987,7 +9991,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="11" s="53">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10023,7 +10027,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="12" s="53">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10059,7 +10063,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="13" s="53">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10100,7 +10104,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="14" s="53">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10131,7 +10135,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="15" s="53">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>华南三区</t>
@@ -10153,7 +10157,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="16" s="53">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10170,7 +10174,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="17" s="53">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10187,7 +10191,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="18" s="53">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>华南四区</t>
@@ -10209,7 +10213,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="19" s="53">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10226,7 +10230,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="20" s="53">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10244,7 +10248,7 @@
       </c>
       <c r="D20" s="39" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="21" s="53">
       <c r="A21" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10266,7 +10270,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="22" s="53">
       <c r="A22" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10288,7 +10292,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="23" s="53">
       <c r="A23" s="31" t="inlineStr">
         <is>
           <t>华东一区</t>
@@ -10310,7 +10314,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="24" s="53">
       <c r="A24" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10332,7 +10336,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="25" s="53">
       <c r="A25" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10350,7 +10354,7 @@
       </c>
       <c r="D25" s="36" t="n"/>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="26" s="53">
       <c r="A26" s="31" t="inlineStr">
         <is>
           <t>华东二区</t>
@@ -10372,7 +10376,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="27" s="53">
       <c r="A27" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10394,7 +10398,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="28" s="53">
       <c r="A28" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10416,7 +10420,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="29" s="53">
       <c r="A29" s="31" t="inlineStr">
         <is>
           <t>华东三区</t>
@@ -10438,7 +10442,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="30" s="53">
       <c r="A30" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10460,7 +10464,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="31" s="53">
       <c r="A31" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10482,7 +10486,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="32" s="53">
       <c r="A32" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10509,7 +10513,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="33" s="53">
       <c r="A33" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10531,7 +10535,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="34" s="53">
       <c r="A34" s="31" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10553,7 +10557,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="35" s="53">
       <c r="A35" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10575,7 +10579,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="36" s="53">
       <c r="A36" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10597,7 +10601,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="37" s="53">
       <c r="A37" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10619,7 +10623,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="38" s="53">
       <c r="A38" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10641,7 +10645,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="39" s="53">
       <c r="A39" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10658,7 +10662,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="40" s="53">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10680,7 +10684,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="41" s="53">
       <c r="A41" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10698,7 +10702,7 @@
       </c>
       <c r="D41" s="46" t="n"/>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="42" s="53">
       <c r="A42" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10720,7 +10724,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="43" s="53">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10738,7 +10742,7 @@
       </c>
       <c r="D43" s="46" t="n"/>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="44" s="53">
       <c r="A44" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10756,7 +10760,7 @@
       </c>
       <c r="E44" s="46" t="n"/>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="45" s="53">
       <c r="A45" s="31" t="inlineStr">
         <is>
           <t>华北一区</t>
@@ -10778,7 +10782,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="46" s="53">
       <c r="A46" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10800,7 +10804,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="47" s="53">
       <c r="A47" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10822,7 +10826,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="48" s="53">
       <c r="A48" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10844,7 +10848,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="49" s="53">
       <c r="A49" s="31" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -10866,7 +10870,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="50" s="53">
       <c r="A50" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10889,7 +10893,7 @@
       </c>
       <c r="E50" s="49" t="n"/>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="51" s="53">
       <c r="A51" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10911,7 +10915,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="52" s="53">
       <c r="A52" s="31" t="inlineStr">
         <is>
           <t>西南区</t>
@@ -10933,7 +10937,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1" s="53">
+    <row customHeight="1" ht="16" r="53" s="53">
       <c r="A53" s="37" t="inlineStr">
         <is>
           <t>华南二区</t>
@@ -10955,7 +10959,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="54" s="53">
       <c r="A54" s="55" t="inlineStr">
         <is>
           <t>华南一区</t>
@@ -10977,7 +10981,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="55" s="53">
       <c r="A55" s="55" t="inlineStr">
         <is>
           <t>华东四区</t>
@@ -10999,7 +11003,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="56" s="53">
       <c r="A56" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -11021,7 +11025,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="53">
+    <row customHeight="1" ht="16.5" r="57" s="53">
       <c r="A57" s="55" t="inlineStr">
         <is>
           <t>华北二区</t>
@@ -11039,7 +11043,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -11050,18 +11054,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" customHeight="1" defaultColWidth="10.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="6.83203125" customWidth="1" style="23" min="1" max="1"/>
-    <col width="8.83203125" customWidth="1" style="23" min="2" max="2"/>
-    <col width="19.6640625" customWidth="1" style="23" min="3" max="3"/>
-    <col width="13" customWidth="1" style="23" min="4" max="4"/>
-    <col hidden="1" width="30.5" customWidth="1" style="23" min="5" max="6"/>
-    <col width="30.5" customWidth="1" style="23" min="7" max="7"/>
-    <col width="10.83203125" customWidth="1" style="23" min="8" max="26"/>
+    <col customWidth="1" max="1" min="1" style="23" width="6.83203125"/>
+    <col customWidth="1" max="2" min="2" style="23" width="8.83203125"/>
+    <col customWidth="1" max="3" min="3" style="23" width="19.6640625"/>
+    <col customWidth="1" max="4" min="4" style="23" width="13"/>
+    <col customWidth="1" hidden="1" max="6" min="5" style="23" width="30.5"/>
+    <col customWidth="1" max="7" min="7" style="23" width="30.5"/>
+    <col customWidth="1" max="26" min="8" style="23" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="1" s="53">
       <c r="A1" s="21" t="n"/>
       <c r="B1" s="22" t="inlineStr">
         <is>
@@ -11103,7 +11107,7 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="2" s="53">
       <c r="A2" s="24" t="n">
         <v>1</v>
       </c>
@@ -11146,7 +11150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="3" s="53">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -11179,7 +11183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="4" s="53">
       <c r="A4" s="24" t="n">
         <v>3</v>
       </c>
@@ -11217,7 +11221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="5" s="53">
       <c r="A5" s="24" t="n">
         <v>4</v>
       </c>
@@ -11260,7 +11264,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="6" s="53">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -11293,7 +11297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="7" s="53">
       <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
@@ -11322,7 +11326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="8" s="53">
       <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
@@ -11352,7 +11356,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="9" s="53">
       <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
@@ -11377,7 +11381,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="10" s="53">
       <c r="A10" s="24" t="n">
         <v>1</v>
       </c>
@@ -11402,7 +11406,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="11" s="53">
       <c r="A11" s="24" t="n">
         <v>2</v>
       </c>
@@ -11432,7 +11436,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="12" s="53">
       <c r="A12" s="24" t="n">
         <v>3</v>
       </c>
@@ -11457,7 +11461,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="13" s="53">
       <c r="A13" s="24" t="n">
         <v>4</v>
       </c>
@@ -11487,7 +11491,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="14" s="53">
       <c r="A14" s="24" t="n">
         <v>5</v>
       </c>
@@ -11507,7 +11511,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="15" s="53">
       <c r="A15" s="24" t="n">
         <v>6</v>
       </c>
@@ -11537,7 +11541,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="16" s="53">
       <c r="A16" s="24" t="n">
         <v>1</v>
       </c>
@@ -11562,7 +11566,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="17" s="53">
       <c r="A17" s="24" t="n">
         <v>2</v>
       </c>
@@ -11597,7 +11601,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="18" s="53">
       <c r="A18" s="24" t="n">
         <v>3</v>
       </c>
@@ -11632,7 +11636,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="19" s="53">
       <c r="A19" s="24" t="n">
         <v>4</v>
       </c>
@@ -11657,7 +11661,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="20" s="53">
       <c r="A20" s="24" t="n">
         <v>5</v>
       </c>
@@ -11687,7 +11691,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="21" s="53">
       <c r="A21" s="24" t="n">
         <v>6</v>
       </c>
@@ -11717,7 +11721,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="22" s="53">
       <c r="A22" s="24" t="n">
         <v>7</v>
       </c>
@@ -11747,7 +11751,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="23" s="53">
       <c r="A23" s="24" t="n">
         <v>8</v>
       </c>
@@ -11777,7 +11781,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="24" s="53">
       <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
@@ -11807,7 +11811,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="25" s="53">
       <c r="A25" s="24" t="n">
         <v>2</v>
       </c>
@@ -11837,7 +11841,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="26" s="53">
       <c r="A26" s="24" t="n">
         <v>3</v>
       </c>
@@ -11862,7 +11866,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="27" s="53">
       <c r="A27" s="24" t="n">
         <v>4</v>
       </c>
@@ -11892,7 +11896,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="28" s="53">
       <c r="A28" s="24" t="n">
         <v>5</v>
       </c>
@@ -11922,7 +11926,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="29" s="53">
       <c r="A29" s="24" t="n">
         <v>6</v>
       </c>
@@ -11952,7 +11956,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="30" s="53">
       <c r="A30" s="24" t="n">
         <v>7</v>
       </c>
@@ -11987,7 +11991,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="53">
+    <row customHeight="1" ht="15.75" r="31" s="53">
       <c r="A31" s="24" t="n">
         <v>8</v>
       </c>
@@ -12017,7 +12021,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="32" s="53">
       <c r="A32" s="24" t="n">
         <v>1</v>
       </c>
@@ -12047,7 +12051,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="33" s="53">
       <c r="A33" s="24" t="n">
         <v>2</v>
       </c>
@@ -12077,7 +12081,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="34" s="53">
       <c r="A34" s="24" t="n">
         <v>3</v>
       </c>
@@ -12107,7 +12111,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="35" s="53">
       <c r="A35" s="24" t="n">
         <v>4</v>
       </c>
@@ -12137,7 +12141,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="36" s="53">
       <c r="A36" s="24" t="n">
         <v>1</v>
       </c>
@@ -12167,7 +12171,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="37" s="53">
       <c r="A37" s="24" t="n">
         <v>2</v>
       </c>
@@ -12202,7 +12206,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="53">
+    <row customHeight="1" ht="15" r="38" s="53">
       <c r="A38" s="24" t="n">
         <v>3</v>
       </c>
@@ -12233,6 +12237,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D43" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发2次</t>
+          <t>累计未发2次，迟发2次</t>
         </is>
       </c>
       <c r="E43" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D36" s="73" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发3次，迟发1次</t>
         </is>
       </c>
       <c r="E36" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D43" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发2次</t>
+          <t>累计未发2次，迟发3次</t>
         </is>
       </c>
       <c r="E43" s="69" t="n"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D58" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次</t>
+          <t>累计未发3次</t>
         </is>
       </c>
       <c r="E58" s="69" t="n"/>
@@ -4538,7 +4538,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D60" s="68" t="n"/>
+      <c r="D60" s="68" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E60" s="69" t="n"/>
       <c r="F60" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D55" s="70" t="inlineStr">
         <is>
-          <t>累计未发1次</t>
+          <t>累计未发2次</t>
         </is>
       </c>
       <c r="E55" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D48" s="71" t="inlineStr">
         <is>
-          <t>迟发1次</t>
+          <t>累计未发1次，迟发1次</t>
         </is>
       </c>
       <c r="E48" s="69" t="n"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D57" s="68" t="inlineStr">
         <is>
-          <t>累计未发4次</t>
+          <t>累计未发5次</t>
         </is>
       </c>
       <c r="E57" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3467,7 +3467,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D21" s="73" t="n"/>
+      <c r="D21" s="73" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E21" s="69" t="n"/>
       <c r="F21" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="D6" s="68" t="inlineStr">
         <is>
-          <t>累计未发4次</t>
+          <t>累计未发5次</t>
         </is>
       </c>
       <c r="E6" s="69" t="n"/>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="D19" s="68" t="inlineStr">
         <is>
-          <t>累计未发3次</t>
+          <t>累计未发4次</t>
         </is>
       </c>
       <c r="E19" s="69" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D30" s="68" t="inlineStr">
         <is>
-          <t>累计未发1次，迟发3次</t>
+          <t>累计未发2次，迟发3次</t>
         </is>
       </c>
       <c r="E30" s="69" t="n"/>
@@ -3849,7 +3849,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D35" s="71" t="n"/>
+      <c r="D35" s="71" t="inlineStr">
+        <is>
+          <t>累计未发1次</t>
+        </is>
+      </c>
       <c r="E35" s="69" t="n"/>
       <c r="F35" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46264</v>
+        <v>46268</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -2947,7 +2947,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="70" t="n"/>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>迟发1次</t>
+        </is>
+      </c>
       <c r="E7" s="69" t="n"/>
       <c r="F7" s="63" t="inlineStr">
         <is>

--- a/日报及月报发送记录.xlsx
+++ b/日报及月报发送记录.xlsx
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B1" s="52" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
     </row>
     <row customHeight="1" ht="16.5" r="2" s="53">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D30" s="68" t="inlineStr">
         <is>
-          <t>累计未发2次，迟发3次</t>
+          <t>累计未发3次，迟发3次</t>
         </is>
       </c>
       <c r="E30" s="69" t="n"/>
